--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-612.5%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-67.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.9%</t>
+          <t>460.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.1%</t>
+          <t>-513.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-245.4%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-967.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-153.0%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.066790257091379</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.911018010601947</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.316660937105961</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.812838862050731</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.523172713992983</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.72634020995218</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.842516789073484</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.600375506620239</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.274322582223272</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.413986076827728</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.509016576355824</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.308393254176798</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.844679223586277</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.172708786940582</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.20830546848659</v>
+        <v>-5.528909118410009</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.033745849214698</v>
+        <v>0.9055043892453303</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.5633091254843285</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.573432851125337</v>
+        <v>-5.894036501048756</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8869494111650305</v>
+        <v>0.7587079511956629</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.859619909783341</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.982021628306015</v>
+        <v>-6.302625278229435</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7222754443075186</v>
+        <v>0.5940339843381501</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.268208686964019</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.258597728621847</v>
+        <v>-6.579201378545267</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.606830436652646</v>
+        <v>0.478588976683278</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.268208686964019</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.674989602908845</v>
+        <v>-6.995593252832265</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4382677375467243</v>
+        <v>0.3100262775773563</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.268208686964019</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.919261003635914</v>
+        <v>-7.239864653559335</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3508178679245755</v>
+        <v>0.2225764079552075</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.268208686964019</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.124512022872675</v>
+        <v>-7.445115672796095</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2648170253755668</v>
+        <v>0.1365755654061984</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.268208686964019</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.288091901057058</v>
+        <v>-7.608695550980478</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1977899941568144</v>
+        <v>0.069548534187446</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.268208686964019</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.584753242867255</v>
+        <v>-7.905356892790675</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.08290443336194331</v>
+        <v>-0.04533702660742467</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.336951822697898</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.771472951176558</v>
+        <v>-8.092076601099977</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.004190245503819412</v>
+        <v>-0.1240512144655486</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.336951822697898</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.154474339919188</v>
+        <v>-8.475077989842609</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.149112411314817</v>
+        <v>-0.277353871284185</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.336951822697898</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.336344130904223</v>
+        <v>-8.656947780827643</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2192888117374006</v>
+        <v>-0.3475302717067685</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.518821613682933</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.695874453408225</v>
+        <v>-9.016478103331645</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3577506374409509</v>
+        <v>-0.4859920974103193</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.518821613682933</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.746223516862447</v>
+        <v>-9.066827166785867</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3699742428654624</v>
+        <v>-0.4982157028348304</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.569170677137155</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.843842794283843</v>
+        <v>-9.164446444207263</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4059802032122519</v>
+        <v>-0.5342216631816199</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.666789954558552</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.991368882289485</v>
+        <v>-9.311972532212906</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4620970820929369</v>
+        <v>-0.5903385420623048</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.814316042564195</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.195627057619349</v>
+        <v>-9.516230707542769</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5382871551062403</v>
+        <v>-0.6665286150756082</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.941954987178184</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.229279896127823</v>
+        <v>-9.549883546051243</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5472657360251936</v>
+        <v>-0.6755071959945615</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.042368355095221</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.155810064460374</v>
+        <v>-9.476413714383794</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5025061018647925</v>
+        <v>-0.6307475618341609</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.968898523427773</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.330934481846917</v>
+        <v>-9.651538131770337</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5580006480718933</v>
+        <v>-0.6862421080412613</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.144022940814317</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.565386575861407</v>
+        <v>-9.885990225784827</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6590006505792849</v>
+        <v>-0.7872421105486533</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.144022940814317</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.669761306887853</v>
+        <v>-9.990364956811273</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7074227337638397</v>
+        <v>-0.8356641937332081</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.248397671840763</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.72254746248818</v>
+        <v>-10.0431511124116</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7274214061654143</v>
+        <v>-0.8556628661347823</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.34407315842316</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.848584255856469</v>
+        <v>-10.16918790577989</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7751423948836154</v>
+        <v>-0.9033838548529833</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.318821535613417</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.791512483960538</v>
+        <v>-10.11211613388396</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.748323350438842</v>
+        <v>-0.87656481040821</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.318821535613417</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.933184325684659</v>
+        <v>-10.25378797560808</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8064673140272318</v>
+        <v>-0.9347087739965998</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.318821535613417</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.883593481259824</v>
+        <v>-10.20419713118324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.771577566092426</v>
+        <v>-0.899819026061794</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.269230691188584</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.734675146787968</v>
+        <v>-10.05527879671139</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7250613659503662</v>
+        <v>-0.8533028259197342</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.23798110045341</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.508829994068556</v>
+        <v>-9.829433643991976</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6251442318263929</v>
+        <v>-0.7533856917957609</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.196054424866247</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.384251337730964</v>
+        <v>-9.704854987654384</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5741736247352973</v>
+        <v>-0.7024150847046653</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.196054424866247</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.437146625775251</v>
+        <v>-9.757750275698671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5926979657909044</v>
+        <v>-0.7209394257602724</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.191099078777801</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.365013450487369</v>
+        <v>-9.68561710041079</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5581109914371152</v>
+        <v>-0.6863524514064832</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.191099078777801</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.293647057877722</v>
+        <v>-9.614250707801142</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5393016967871214</v>
+        <v>-0.6675431567564898</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.119732686168153</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.200188023892498</v>
+        <v>-9.520791673815918</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5118015645059395</v>
+        <v>-0.6400430244753075</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.119732686168153</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.9329462230241</v>
+        <v>-9.25354987294752</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4067394046579538</v>
+        <v>-0.5349808646273222</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.119732686168153</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.835039184347609</v>
+        <v>-9.155642834271029</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3678769041608185</v>
+        <v>-0.4961183641301865</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.051746936307596</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.811085643371651</v>
+        <v>-9.131689293295072</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3576269816249416</v>
+        <v>-0.48586844159431</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.027793395331639</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.547025705048855</v>
+        <v>-8.867629354972275</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2652633224575753</v>
+        <v>-0.3935047824269433</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.763733457008843</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.839946081544016</v>
+        <v>-8.160549731467437</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01478149328405909</v>
+        <v>-0.1134599666853093</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.763733457008843</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.799761783177826</v>
+        <v>-8.120365433101247</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.03119883651837663</v>
+        <v>-0.09704262345099179</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.723549158642652</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.636361912238463</v>
+        <v>-7.956965562161884</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09592560611487855</v>
+        <v>-0.03231585385448987</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.56014928770329</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.402880690008865</v>
+        <v>-7.723484339932286</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1972425238445705</v>
+        <v>0.06900106387520211</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.326668065473691</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.25321429900135</v>
+        <v>-7.573817948924771</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2542168699346172</v>
+        <v>0.1259754099652488</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.233764574231155</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.120938825370463</v>
+        <v>-7.441542475293884</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3024945461339992</v>
+        <v>0.1742530861646308</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.101489100600269</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.965200492810721</v>
+        <v>-7.285804142734142</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3676049398455326</v>
+        <v>0.2393634798761641</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.9457507680405269</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.71620069412714</v>
+        <v>-7.036804344050561</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4801112005426238</v>
+        <v>0.3518697405732554</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.9457507680405269</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.821790683900245</v>
+        <v>-7.142394333823666</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3098992750341631</v>
+        <v>0.1816578150647947</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.051340757813631</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.840525586018842</v>
+        <v>-7.161129235942263</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3509496560638108</v>
+        <v>0.2227081960944424</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.056936767473763</v>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.872572683826192</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.692585544611243</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2902467499386829</v>
+        <v>0.06694058169857975</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.345667881157804</v>
+        <v>2.25060317288707</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.863858697572714</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.639616022357254</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3027205725868001</v>
+        <v>0.07941440434669689</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.36873560825672</v>
+        <v>2.273670899985985</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.856898085477621</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.596067615586564</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3131793231999831</v>
+        <v>0.08987315495987991</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.361774996161627</v>
+        <v>2.266710287890892</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.871360439858764</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.353919222132705</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4245010349626694</v>
+        <v>0.2011948667225663</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.37623735054277</v>
+        <v>2.281172642272035</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.865892560317959</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.245660085010184</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4623368102708731</v>
+        <v>0.23903064203077</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.370769471001965</v>
+        <v>2.27570476273123</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.863390654328536</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.122368950193053</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5091513582083023</v>
+        <v>0.2858451899681991</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.44224224590282</v>
+        <v>2.347177537632085</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.871091632565862</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.10121975128961</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5253120160070051</v>
+        <v>0.3020058477669023</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.462632743482211</v>
+        <v>2.367568035211477</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.866872340912912</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.857454309306165</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6185989011474335</v>
+        <v>0.3952927329073304</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.458413451829262</v>
+        <v>2.363348743558527</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.868996654832928</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.75569148902887</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6614283431783674</v>
+        <v>0.4381221749382647</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.468469206784735</v>
+        <v>2.373404498514001</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.861738729816631</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.505841095079796</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7541105757416995</v>
+        <v>0.5308044075015967</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.461211281768437</v>
+        <v>2.366146573497703</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.865337853337279</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.329949002612363</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8280665362493211</v>
+        <v>0.604760368009218</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.464810405289086</v>
+        <v>2.369745697018351</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.878665359391833</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.158502539589899</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9099726275128601</v>
+        <v>0.6866664592727574</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.581005789157117</v>
+        <v>2.485941080886383</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.87768583700813</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.08421297385156</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9387089314244927</v>
+        <v>0.71540276318439</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624600006216418</v>
+        <v>2.529535297945683</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.882380638062447</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.020577231617626</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9688580293723841</v>
+        <v>0.7455518611322809</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.667476252611096</v>
+        <v>2.572411544340361</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.863574896846243</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.909150472291706</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9946229918865477</v>
+        <v>0.7713168236464445</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.648670511394891</v>
+        <v>2.553605803124157</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.86531797347112</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.668719975486845</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.092538267233369</v>
+        <v>0.869232098993266</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.794671886102685</v>
+        <v>2.699607177831951</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.86924728730594</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.596477407315651</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.125364608336667</v>
+        <v>0.9020584400965641</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.798601199937505</v>
+        <v>2.703536491666771</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.86992587122328</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.543479085034263</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.147242521166562</v>
+        <v>0.9239363529264593</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832481539256008</v>
+        <v>2.737416830985274</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.866923942443274</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.434674199554536</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.187762546578447</v>
+        <v>0.9644563783383435</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829479610476002</v>
+        <v>2.734414902205268</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.868502979453888</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.214653401517525</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.277349902803865</v>
+        <v>1.054043734563762</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915790554527404</v>
+        <v>2.82072584625667</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.884397162255711</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.081785712454248</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.346391161230999</v>
+        <v>1.123084992990896</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.931684737329228</v>
+        <v>2.836620029058493</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.885543006696013</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.961612629089749</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.395606239017101</v>
+        <v>1.172300070776998</v>
       </c>
       <c r="F1931" t="n">
         <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004934431788229</v>
+        <v>2.909869723517494</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.895631109257453</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.816940483990011</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.463563199618436</v>
+        <v>1.240257031378333</v>
       </c>
       <c r="F1932" t="n">
         <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.101825821409511</v>
+        <v>3.006761113138777</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.881668600658879</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.876815311347704</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.425650760076784</v>
+        <v>1.202344591836682</v>
       </c>
       <c r="F1933" t="n">
         <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.051938416396322</v>
+        <v>2.956873708125587</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.896957769893088</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.756995080436866</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.488868021675328</v>
+        <v>1.265561853435225</v>
       </c>
       <c r="F1934" t="n">
         <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06722758563053</v>
+        <v>2.972162877359796</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.804601969215529</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.759464786898672</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.395524338413047</v>
+        <v>1.172218170172944</v>
       </c>
       <c r="F1935" t="n">
         <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.973389961075888</v>
+        <v>2.878325252805154</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.72386383070083</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.827834973222682</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.287438125368745</v>
+        <v>1.064131957128641</v>
       </c>
       <c r="F1936" t="n">
         <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.898217241982918</v>
+        <v>2.803152533712184</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.714300539332722</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.841623026069729</v>
+        <v>-4.162226675993152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.272359612861817</v>
+        <v>1.049053444621714</v>
       </c>
       <c r="F1937" t="n">
         <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88865395061481</v>
+        <v>2.793589242344075</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.634074812643843</v>
+        <v>2.539010104373109</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.872616185398434</v>
+        <v>-4.193219835321857</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.084671914170722</v>
+        <v>0.8613657459306185</v>
       </c>
       <c r="F1938" t="n">
         <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.713363515655197</v>
+        <v>2.618298807384462</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.638642044635631</v>
+        <v>2.543577336364896</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.697141925605965</v>
+        <v>-4.017745575529387</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.159428850079497</v>
+        <v>0.9361226818393942</v>
       </c>
       <c r="F1939" t="n">
         <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717930747646984</v>
+        <v>2.62286603937625</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.614384073396838</v>
+        <v>2.519319365126103</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.808078178247214</v>
+        <v>-4.128681828170636</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.090796377784205</v>
+        <v>0.8674902095441017</v>
       </c>
       <c r="F1940" t="n">
         <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.693672776408191</v>
+        <v>2.598608068137457</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.617515458616743</v>
+        <v>2.522450750346009</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.774414632774932</v>
+        <v>-4.095018282698354</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.107393181193023</v>
+        <v>0.8840870129529201</v>
       </c>
       <c r="F1941" t="n">
         <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717002288911466</v>
+        <v>2.621937580640732</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.627687845048876</v>
+        <v>2.532623136778141</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.714562013571209</v>
+        <v>-4.035165663494631</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.141506615306645</v>
+        <v>0.9182004470665417</v>
       </c>
       <c r="F1942" t="n">
         <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727174675343599</v>
+        <v>2.632109967072864</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.622634115622736</v>
+        <v>2.527569407352002</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.628318550544831</v>
+        <v>-3.948922200468253</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.170950271091056</v>
+        <v>0.947644102850953</v>
       </c>
       <c r="F1943" t="n">
         <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722120945917459</v>
+        <v>2.627056237646725</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.614409891067262</v>
+        <v>2.519345182796527</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.673625369943811</v>
+        <v>-3.994229019867233</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.14460331877599</v>
+        <v>0.9212971505358867</v>
       </c>
       <c r="F1944" t="n">
         <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689410623556446</v>
+        <v>2.594345915285711</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.614961764100363</v>
+        <v>2.519897055829629</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.702658474646113</v>
+        <v>-4.023262124569534</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.133541949928171</v>
+        <v>0.9102357816880677</v>
       </c>
       <c r="F1945" t="n">
         <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689962496589547</v>
+        <v>2.594897788318813</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.544234455991729</v>
+        <v>2.449169747720994</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.609847993195253</v>
+        <v>-3.930451643118675</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.09993883439988</v>
+        <v>0.8766326661597772</v>
       </c>
       <c r="F1946" t="n">
         <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674921477351428</v>
+        <v>2.579856769080694</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.54610793191633</v>
+        <v>2.451043223645595</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.654237462524681</v>
+        <v>-3.974841112448102</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.08405652259271</v>
+        <v>0.8607503543526069</v>
       </c>
       <c r="F1947" t="n">
         <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650161271678373</v>
+        <v>2.555096563407639</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.541183640428053</v>
+        <v>2.446118932157318</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.541566244288431</v>
+        <v>-3.862169894211852</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.124200718398933</v>
+        <v>0.9008945501588301</v>
       </c>
       <c r="F1948" t="n">
         <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.712839711131846</v>
+        <v>2.617775002861112</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.54667493625872</v>
+        <v>2.451610227987985</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.429189243105758</v>
+        <v>-3.74979289302918</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.174642814702669</v>
+        <v>0.9513366464625663</v>
       </c>
       <c r="F1949" t="n">
         <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.718331006962513</v>
+        <v>2.623266298691779</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.558172138027259</v>
+        <v>2.463107429756525</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.456969641007111</v>
+        <v>-3.777573290930533</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.175027857310667</v>
+        <v>0.9517216890705642</v>
       </c>
       <c r="F1950" t="n">
         <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71315996999024</v>
+        <v>2.618095261719506</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.396527858027912</v>
+        <v>2.301463149757178</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.53997092203239</v>
+        <v>-3.860574571955812</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9801830649012087</v>
+        <v>0.7568768966611059</v>
       </c>
       <c r="F1951" t="n">
         <v>0.2397421687444617</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.540373159274589</v>
+        <v>2.445308451003855</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.516677518747118</v>
+        <v>2.421612810476383</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.648585000475721</v>
+        <v>-3.969188650399143</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.056887094243082</v>
+        <v>0.833580926002979</v>
       </c>
       <c r="F1952" t="n">
         <v>0.2397421687444617</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.660522819993795</v>
+        <v>2.565458111723061</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.531190544849441</v>
+        <v>2.436125836578706</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.613175962227579</v>
+        <v>-3.933779612151</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.085563735644662</v>
+        <v>0.8622575674045592</v>
       </c>
       <c r="F1953" t="n">
         <v>0.2397421687444617</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.675035846096118</v>
+        <v>2.579971137825384</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.528609986191809</v>
+        <v>2.433545277921075</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.574792299669427</v>
+        <v>-3.895395949592849</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.098336642010291</v>
+        <v>0.8750304737701882</v>
       </c>
       <c r="F1954" t="n">
         <v>0.2781258313026129</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.695485484973378</v>
+        <v>2.600420776702643</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.525339015037112</v>
+        <v>2.430274306766377</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.397675969634261</v>
+        <v>-3.718279619557683</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.16591220286966</v>
+        <v>0.9426060346295571</v>
       </c>
       <c r="F1955" t="n">
         <v>0.2781258313026129</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.69221451381868</v>
+        <v>2.597149805547946</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.526022406799025</v>
+        <v>2.430957698528291</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.442768214467807</v>
+        <v>-3.763371864391228</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.148558696698155</v>
+        <v>0.9252525284580519</v>
       </c>
       <c r="F1956" t="n">
         <v>0.2162297881332231</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.655760279678959</v>
+        <v>2.560695571408225</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.519809382105439</v>
+        <v>2.424744673834705</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.263392793229039</v>
+        <v>-3.58399644315246</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.214095840500076</v>
+        <v>0.9907896722599734</v>
       </c>
       <c r="F1957" t="n">
         <v>0.3730065463039418</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.743613309887805</v>
+        <v>2.64854860161707</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.500616837437029</v>
+        <v>2.405552129166295</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.308407006749646</v>
+        <v>-3.629010656673067</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.176897610423423</v>
+        <v>0.9535914421833207</v>
       </c>
       <c r="F1958" t="n">
         <v>0.3426576509893372</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.706211428030632</v>
+        <v>2.611146719759897</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.506308399775975</v>
+        <v>2.41124369150524</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.575411517022081</v>
+        <v>-3.896015166945502</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.075787368653395</v>
+        <v>0.8524812004132922</v>
       </c>
       <c r="F1959" t="n">
         <v>0.1482946129463886</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.595285167543808</v>
+        <v>2.500220459273074</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.505512321672476</v>
+        <v>2.410447613401742</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.676609298459254</v>
+        <v>-3.997212948382675</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.034512177975027</v>
+        <v>0.8112060097349247</v>
       </c>
       <c r="F1960" t="n">
         <v>0.07988579940106943</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553443801313118</v>
+        <v>2.458379093042384</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.503112283226793</v>
+        <v>2.408047574956059</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.670098331844941</v>
+        <v>-3.990701981768362</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.034716526175069</v>
+        <v>0.8114103579349665</v>
       </c>
       <c r="F1961" t="n">
         <v>0.07988579940106943</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551043762867435</v>
+        <v>2.455979054596701</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.499637002435038</v>
+        <v>2.404572294164304</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.651060204137644</v>
+        <v>-3.971663854061065</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.038856496466233</v>
+        <v>0.8155503282261303</v>
       </c>
       <c r="F1962" t="n">
         <v>0.02170218806987489</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.512658315276963</v>
+        <v>2.417593607006228</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.677218871373718</v>
+        <v>2.582154163102984</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.682186835288262</v>
+        <v>-4.002790485211683</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.203987712944666</v>
+        <v>0.9806815447045636</v>
       </c>
       <c r="F1963" t="n">
         <v>0.02170218806987489</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.690240184215644</v>
+        <v>2.595175475944909</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.678052200359852</v>
+        <v>2.582987492089118</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.696053596622179</v>
+        <v>-4.0166572465456</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.199274337397233</v>
+        <v>0.9759681691571302</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.01615572866394804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668358763161483</v>
+        <v>2.573294054890749</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.684060730756778</v>
+        <v>2.588996022486044</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.651249425082249</v>
+        <v>-3.97185307500567</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.223204536410131</v>
+        <v>0.9998983681700282</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.01615572866394804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674367293558409</v>
+        <v>2.579302585287675</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.7632133785488</v>
+        <v>2.668148670278065</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.503506454847247</v>
+        <v>-3.824110104770668</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.361454372296154</v>
+        <v>1.138148204056051</v>
       </c>
       <c r="F1966" t="n">
         <v>0.1516516285709351</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.854204355691361</v>
+        <v>2.759139647420627</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.766007000080281</v>
+        <v>2.670942291809546</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.605521137378468</v>
+        <v>-3.926124787301889</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.323442120815146</v>
+        <v>1.100135952575044</v>
       </c>
       <c r="F1967" t="n">
         <v>0.1516516285709351</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.856997977222842</v>
+        <v>2.761933268952108</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.766669348471939</v>
+        <v>2.671604640201205</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.599368431325684</v>
+        <v>-3.919972081249105</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.326565551627918</v>
+        <v>1.103259383387816</v>
       </c>
       <c r="F1968" t="n">
         <v>0.1578043346237194</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.861351949246171</v>
+        <v>2.766287240975437</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.765749825212049</v>
+        <v>2.670685116941315</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.616177729476185</v>
+        <v>-3.936781379399606</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.318922309107828</v>
+        <v>1.095616140867725</v>
       </c>
       <c r="F1969" t="n">
         <v>0.1409950364732178</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85034684709598</v>
+        <v>2.755282138825246</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.83208537900887</v>
+        <v>2.737020670738136</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.553879730700063</v>
+        <v>-3.874483380623484</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.410177062415098</v>
+        <v>1.186870894174995</v>
       </c>
       <c r="F1970" t="n">
         <v>0.1409950364732178</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.916682400892801</v>
+        <v>2.821617692622067</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.634377380722997</v>
+        <v>2.539312672452263</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.352089533034905</v>
+        <v>-3.672693182958326</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.293185143195288</v>
+        <v>1.069878974955185</v>
       </c>
       <c r="F1971" t="n">
         <v>0.3390132286423722</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.837785317908421</v>
+        <v>2.742720609637686</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.704667613045173</v>
+        <v>2.609602904774438</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.278711435946169</v>
+        <v>-3.59931508586959</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.392826614352958</v>
+        <v>1.169520446112855</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4123913257311087</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.952102408483838</v>
+        <v>2.857037700213104</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.719295349161216</v>
+        <v>2.624230640890482</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.376451980571143</v>
+        <v>-3.697055630494564</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.368358132619012</v>
+        <v>1.145051964378909</v>
       </c>
       <c r="F1973" t="n">
         <v>0.3965020475981285</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.957196577720094</v>
+        <v>2.862131869449359</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.717831329985888</v>
+        <v>2.622766621715154</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.552789740694072</v>
+        <v>-3.873393390617494</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.296359009394512</v>
+        <v>1.073052841154409</v>
       </c>
       <c r="F1974" t="n">
         <v>0.2201642874751991</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.849929902471008</v>
+        <v>2.754865194200273</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.716322948025816</v>
+        <v>2.621258239755082</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.476367694262146</v>
+        <v>-3.796971344185567</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.325419446007211</v>
+        <v>1.102113277767108</v>
       </c>
       <c r="F1975" t="n">
         <v>0.2201642874751991</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.848421520510936</v>
+        <v>2.753356812240202</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.716185815461253</v>
+        <v>2.621121107190518</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.431994562623577</v>
+        <v>-3.752598212546998</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.343031566098075</v>
+        <v>1.119725397857972</v>
       </c>
       <c r="F1976" t="n">
         <v>0.2645374191137677</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.874908266929514</v>
+        <v>2.779843558658779</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.710579609599843</v>
+        <v>2.615514901329109</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.30916034173641</v>
+        <v>-3.629763991659831</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.386559048591532</v>
+        <v>1.163252880351429</v>
       </c>
       <c r="F1977" t="n">
         <v>0.2645374191137677</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.869302061068104</v>
+        <v>2.77423735279737</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.716961366627648</v>
+        <v>2.621896658356913</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.261504611175354</v>
+        <v>-3.582108261098775</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.412003097843759</v>
+        <v>1.188696929603656</v>
       </c>
       <c r="F1978" t="n">
         <v>0.3121931496748234</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.904277256432542</v>
+        <v>2.809212548161808</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.721853740002373</v>
+        <v>2.626789031731638</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.1609864526766</v>
+        <v>-3.481590102600021</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.457102734617985</v>
+        <v>1.233796566377883</v>
       </c>
       <c r="F1979" t="n">
         <v>0.4127113081735779</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.969480524906519</v>
+        <v>2.874415816635785</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.708608412478245</v>
+        <v>2.61354370420751</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.221653043078989</v>
+        <v>-3.54225669300241</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.419590770932902</v>
+        <v>1.196284602692799</v>
       </c>
       <c r="F1980" t="n">
         <v>0.3310129914550443</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.907216207351272</v>
+        <v>2.812151499080537</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.712706115088873</v>
+        <v>2.617641406818139</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.176814641470591</v>
+        <v>-3.497418291394012</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.44162383418689</v>
+        <v>1.218317665946787</v>
       </c>
       <c r="F1981" t="n">
         <v>0.3355564243999137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.914039969728822</v>
+        <v>2.818975261458088</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.716867054719951</v>
+        <v>2.621802346449217</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.277573277227589</v>
+        <v>-3.59817692715101</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.405481319515169</v>
+        <v>1.182175151275066</v>
       </c>
       <c r="F1982" t="n">
         <v>0.2467308556729083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.864905568123697</v>
+        <v>2.769840859852962</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.722746657247789</v>
+        <v>2.627681948977054</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.233370440141689</v>
+        <v>-3.55397409006511</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.429042056877366</v>
+        <v>1.205735888637263</v>
       </c>
       <c r="F1983" t="n">
         <v>0.2909336927588088</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.897306872903074</v>
+        <v>2.80224216463234</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.721156657717036</v>
+        <v>2.626091949446302</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.270349467805132</v>
+        <v>-3.590953117728553</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.412660446281236</v>
+        <v>1.189354278041133</v>
       </c>
       <c r="F1984" t="n">
         <v>0.3279075945501393</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.91790121444712</v>
+        <v>2.822836506176386</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.772404422900076</v>
+        <v>2.677339714629341</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.11205805026586</v>
+        <v>-3.432661700189281</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.527224778479985</v>
+        <v>1.303918610239882</v>
       </c>
       <c r="F1985" t="n">
         <v>0.3279075945501393</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.96914897963016</v>
+        <v>2.874084271359425</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.770845127494329</v>
+        <v>2.675780419223595</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.072127377087969</v>
+        <v>-3.39273102701139</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.541637752345394</v>
+        <v>1.318331584105291</v>
       </c>
       <c r="F1986" t="n">
         <v>0.3678382677280296</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.991548088131147</v>
+        <v>2.896483379860412</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.765793355732599</v>
+        <v>2.670728647461865</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.021095284365441</v>
+        <v>-3.341698934288862</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.556998817672675</v>
+        <v>1.333692649432572</v>
       </c>
       <c r="F1987" t="n">
         <v>0.4188703604505576</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.017115572002933</v>
+        <v>2.922050863732199</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.782980759825304</v>
+        <v>2.687916051554569</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.955871103238236</v>
+        <v>-3.276474753161657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.600275894216262</v>
+        <v>1.37696972597616</v>
       </c>
       <c r="F1988" t="n">
         <v>0.4840945415777632</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.073437484771962</v>
+        <v>2.978372776501228</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.778941732124584</v>
+        <v>2.68387702385385</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.918444083167102</v>
+        <v>-3.239047733090523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.611207674543996</v>
+        <v>1.387901506303893</v>
       </c>
       <c r="F1989" t="n">
         <v>0.4893460796069449</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.072549379888752</v>
+        <v>2.977484671618017</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.780198524455824</v>
+        <v>2.68513381618509</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.93855573920181</v>
+        <v>-3.259159389125232</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.604419804461353</v>
+        <v>1.38111363622125</v>
       </c>
       <c r="F1990" t="n">
         <v>0.5003734246043641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.080422579218443</v>
+        <v>2.985357870947709</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.940756295477035</v>
+        <v>2.845691587206301</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.884810924774606</v>
+        <v>-3.205414574698027</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.786475501253446</v>
+        <v>1.563169333013343</v>
       </c>
       <c r="F1991" t="n">
         <v>0.510436734044826</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.247018335903931</v>
+        <v>3.151953627633197</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.060869204694852</v>
+        <v>2.965804496424118</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.861019356168463</v>
+        <v>-3.181623006091884</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.91610503791372</v>
+        <v>1.692798869673617</v>
       </c>
       <c r="F1992" t="n">
         <v>0.5342283026509683</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.381406186285434</v>
+        <v>3.2863414780147</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.052577180708711</v>
+        <v>2.957512472437977</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.834935271904655</v>
+        <v>-3.155538921828076</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.918246647633102</v>
+        <v>1.694940479392999</v>
       </c>
       <c r="F1993" t="n">
         <v>0.5342283026509683</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.373114162299293</v>
+        <v>3.278049454028559</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.050770376292491</v>
+        <v>2.955705668021757</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.756804091055709</v>
+        <v>-3.07740774097913</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.94769231555646</v>
+        <v>1.724386147316358</v>
       </c>
       <c r="F1994" t="n">
         <v>0.6084051135346529</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.415813444413283</v>
+        <v>3.320748736142549</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.068324782019282</v>
+        <v>2.973260073748548</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.747911629662426</v>
+        <v>-3.068515279585847</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.968803705840565</v>
+        <v>1.745497537600462</v>
       </c>
       <c r="F1995" t="n">
         <v>0.6084051135346529</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.433367850140074</v>
+        <v>3.33830314186934</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.060179829423866</v>
+        <v>2.965115121153132</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.916387746632303</v>
+        <v>-3.236991396555724</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.893268306457198</v>
+        <v>1.669962138217095</v>
       </c>
       <c r="F1996" t="n">
         <v>0.5804572778180721</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.40845419611471</v>
+        <v>3.313389487843975</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.041449526611728</v>
+        <v>2.946384818340994</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.21858821777072</v>
+        <v>-2.539191867694141</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.153657815189693</v>
+        <v>1.93035164694959</v>
       </c>
       <c r="F1997" t="n">
         <v>0.5101092184476614</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.347515057680325</v>
+        <v>3.252450349409591</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.032113549108633</v>
+        <v>2.937048840837898</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.195867114087568</v>
+        <v>-2.516470764010989</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.153410279159858</v>
+        <v>1.930104110919756</v>
       </c>
       <c r="F1998" t="n">
         <v>0.5101092184476614</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.33817908017723</v>
+        <v>3.243114371906495</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.191019674959802</v>
+        <v>3.095954966689067</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.194142070797524</v>
+        <v>-2.514745720720945</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.313006422327045</v>
+        <v>2.089700254086942</v>
       </c>
       <c r="F1999" t="n">
         <v>0.5118342617377052</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.498120232002425</v>
+        <v>3.403055523731691</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.228097497453448</v>
+        <v>3.133032789182714</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.348923077575779</v>
+        <v>-2.6695267274992</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.28817184210939</v>
+        <v>2.064865673869287</v>
       </c>
       <c r="F2000" t="n">
         <v>0.4784665876832291</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.515177450063386</v>
+        <v>3.420112741792652</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.224772853442993</v>
+        <v>3.129708145172259</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.297487744191119</v>
+        <v>-2.61809139411454</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.305421331452798</v>
+        <v>2.082115163212696</v>
       </c>
       <c r="F2001" t="n">
         <v>0.5299019210678888</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.542714006083727</v>
+        <v>3.447649297812993</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.234779007087735</v>
+        <v>3.139714298817001</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.270536519864631</v>
+        <v>-2.591140169788052</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.326207974828135</v>
+        <v>2.102901806588032</v>
       </c>
       <c r="F2002" t="n">
         <v>0.544782267095608</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.5616483673451</v>
+        <v>3.466583659074366</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.418882139232695</v>
+        <v>3.32381743096196</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.406489527920948</v>
+        <v>-2.727093177844369</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.455929903750568</v>
+        <v>2.232623735510466</v>
       </c>
       <c r="F2003" t="n">
         <v>0.544782267095608</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.74575149949006</v>
+        <v>3.650686791219325</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.410998834135688</v>
+        <v>3.315934125864954</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.42889764572582</v>
+        <v>-2.749501295649241</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.439083351531613</v>
+        <v>2.21577718329151</v>
       </c>
       <c r="F2004" t="n">
         <v>0.544782267095608</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.737868194393053</v>
+        <v>3.642803486122319</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.413052833685325</v>
+        <v>3.317988125414591</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.576903413205219</v>
+        <v>-2.89750706312864</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.381935044089491</v>
+        <v>2.158628875849388</v>
       </c>
       <c r="F2005" t="n">
         <v>0.4580552582320665</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.687885988624565</v>
+        <v>3.592821280353831</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.469306551407172</v>
+        <v>3.374241843136438</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.586344339093749</v>
+        <v>-2.90694798901717</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.434412391455925</v>
+        <v>2.211106223215823</v>
       </c>
       <c r="F2006" t="n">
         <v>0.5804823757754579</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.817595976872447</v>
+        <v>3.722531268601713</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.472197645952473</v>
+        <v>3.377132937681739</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.585057575554193</v>
+        <v>-2.905661225477614</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.437818191417049</v>
+        <v>2.214512023176946</v>
       </c>
       <c r="F2007" t="n">
         <v>0.5817691393150145</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.821259129541482</v>
+        <v>3.726194421270748</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.470309458846248</v>
+        <v>3.375244750575514</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.586614629543484</v>
+        <v>-2.907218279466905</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.435307182715108</v>
+        <v>2.212001014475005</v>
       </c>
       <c r="F2008" t="n">
         <v>0.5817691393150145</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.819370942435258</v>
+        <v>3.724306234164523</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.465129688449111</v>
+        <v>3.370064980178376</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.593886515066949</v>
+        <v>-2.91449016499037</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.427218658108584</v>
+        <v>2.203912489868482</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5744972537915498</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.809828040724041</v>
+        <v>3.714763332453307</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.463563698659263</v>
+        <v>3.368498990388529</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.592045496008697</v>
+        <v>-2.912649145932118</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.426389075942037</v>
+        <v>2.203082907701934</v>
       </c>
       <c r="F2010" t="n">
         <v>0.5757654804630182</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.809022986937074</v>
+        <v>3.71395827866634</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.476637105525182</v>
+        <v>3.381572397254447</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.598954201508378</v>
+        <v>-2.919557851431799</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.436699000608083</v>
+        <v>2.213392832367981</v>
       </c>
       <c r="F2011" t="n">
         <v>0.5757654804630182</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.822096393802993</v>
+        <v>3.727031685532259</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.476637105525182</v>
+        <v>3.381572397254447</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.600515844323238</v>
+        <v>-2.921119494246659</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.436074343482139</v>
+        <v>2.212768175242037</v>
       </c>
       <c r="F2012" t="n">
         <v>0.5757654804630182</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.822096393802993</v>
+        <v>3.727031685532259</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.475161146652184</v>
+        <v>3.380096438381449</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.628416631432711</v>
+        <v>-2.949020281356132</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.423438069765352</v>
+        <v>2.200131901525249</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5411685563200834</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.799862280444234</v>
+        <v>3.7047975721735</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.471925590629382</v>
+        <v>3.376860882358648</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.631449628945385</v>
+        <v>-2.952053278868806</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.418989314737481</v>
+        <v>2.195683146497379</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5381355588074095</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.794806925913829</v>
+        <v>3.699742217643094</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.538631550219886</v>
+        <v>3.443566841949152</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.651510950221891</v>
+        <v>-2.972114600145312</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.477670745817382</v>
+        <v>2.25436457757728</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5180742375309024</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.849476092738428</v>
+        <v>3.754411384467693</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.678943269221733</v>
+        <v>3.583878560950999</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.908231768216715</v>
+        <v>-3.228835418140136</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.5152941376213</v>
+        <v>2.291987969381197</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4096596633870876</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.924739067253986</v>
+        <v>3.829674358983252</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.747923538367373</v>
+        <v>3.652858830096639</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.062218185992856</v>
+        <v>-3.382821835916277</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.522679839656483</v>
+        <v>2.29937367141638</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4096596633870876</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.993719336399626</v>
+        <v>3.898654628128892</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.838704482970035</v>
+        <v>3.768882736649164</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.733974740487494</v>
+        <v>3.63891003221676</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.335732350494276</v>
+        <v>-3.515355296735239</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.399325375976036</v>
+        <v>2.232411489208917</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4096596633870876</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.979770538519746</v>
+        <v>3.884705830249013</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>61.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.9%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.4%</t>
+          <t>459.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-513.1%</t>
+          <t>-483.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.0%</t>
+          <t>-131.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-111.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-183.0%</t>
+          <t>-177.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-44.8%</t>
         </is>
       </c>
     </row>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.872572683826192</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.013189194534664</v>
+        <v>-6.90235661232586</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.06694058169857975</v>
+        <v>0.2063383228528357</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.036615851565205</v>
+        <v>-0.9826659762561126</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.25060317288707</v>
+        <v>2.37803780634326</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.863858697572714</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.960219672280675</v>
+        <v>-6.849387090071872</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07941440434669689</v>
+        <v>0.2188121455009528</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9296964540021238</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.273670899985985</v>
+        <v>2.401105533442175</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.856898085477621</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.916671265509985</v>
+        <v>-6.805838683301181</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08987315495987991</v>
+        <v>0.2292708961141359</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9296964540021238</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.266710287890892</v>
+        <v>2.394144921347082</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.871360439858764</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.674522872056126</v>
+        <v>-6.563690289847323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2011948667225663</v>
+        <v>0.3405926078768222</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9296964540021238</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.281172642272035</v>
+        <v>2.408607275728225</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.865892560317959</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.566263734933605</v>
+        <v>-6.455431152724802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.23903064203077</v>
+        <v>0.3784283831850259</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9296964540021238</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.27570476273123</v>
+        <v>2.40313939618742</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.863390654328536</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.442972600116474</v>
+        <v>-6.332140017907671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2858451899681991</v>
+        <v>0.425242931122455</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8603551944940857</v>
+        <v>-0.8064053191849933</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.347177537632085</v>
+        <v>2.474612171088275</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.871091632565862</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.421823401213031</v>
+        <v>-6.310990819004227</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3020058477669023</v>
+        <v>0.4414035889211578</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.7852561202815499</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.367568035211477</v>
+        <v>2.495002668667667</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.866872340912912</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.178057959229586</v>
+        <v>-6.067225377020783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3952927329073304</v>
+        <v>0.5346904740615863</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.7852561202815499</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.363348743558527</v>
+        <v>2.490783377014717</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.868996654832928</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.076295138952291</v>
+        <v>-5.965462556743488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4381221749382647</v>
+        <v>0.5775199160925202</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7720370518891212</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.373404498514001</v>
+        <v>2.50083913197019</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.861738729816631</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.826444745003217</v>
+        <v>-5.715612162794414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5308044075015967</v>
+        <v>0.6702021486558523</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7720370518891212</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.366146573497703</v>
+        <v>2.493581206953893</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.865337853337279</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.650552652535785</v>
+        <v>-5.539720070326981</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.604760368009218</v>
+        <v>0.7441581091634739</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7720370518891212</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.369745697018351</v>
+        <v>2.497180330474541</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.878665359391833</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.479106189513321</v>
+        <v>-5.368273607304517</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6866664592727574</v>
+        <v>0.8260642004270133</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6545404641757505</v>
+        <v>-0.6005905888666581</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.485941080886383</v>
+        <v>2.613375714342573</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.87768583700813</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.404816623774982</v>
+        <v>-5.293984041566178</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.71540276318439</v>
+        <v>0.854800504338646</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5802508984374113</v>
+        <v>-0.5263010231283187</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.529535297945683</v>
+        <v>2.656969931401873</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.882380638062447</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.341180881541048</v>
+        <v>-5.230348299332244</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7455518611322809</v>
+        <v>0.8849496022865369</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.4626652808943842</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.572411544340361</v>
+        <v>2.699846177796551</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.863574896846243</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-5.118921540006323</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7713168236464445</v>
+        <v>0.9107145648007005</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.4626652808943842</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.553605803124157</v>
+        <v>2.681040436580347</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.86531797347112</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-4.878491043201463</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.869232098993266</v>
+        <v>1.008629840147522</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.2222347840895239</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.699607177831951</v>
+        <v>2.827041811288141</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.86924728730594</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-4.806248475030269</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9020584400965641</v>
+        <v>1.04145618125082</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.2222347840895239</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.703536491666771</v>
+        <v>2.830971125122961</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.86992587122328</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.753250152748881</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9239363529264593</v>
+        <v>1.063334094080715</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.1668985250875851</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.737416830985274</v>
+        <v>2.864851464441464</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.866923942443274</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.644445267269154</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9644563783383435</v>
+        <v>1.103854119492599</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.1668985250875851</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.734414902205268</v>
+        <v>2.861849535661458</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.868502979453888</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.424424469232143</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.054043734563762</v>
+        <v>1.193441475718018</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.07962855532869739</v>
+        <v>-0.02567868001960483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.82072584625667</v>
+        <v>2.94816047971286</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.884397162255711</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.291556780168865</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.123084992990896</v>
+        <v>1.262482734145152</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.07962855532869739</v>
+        <v>-0.02567868001960483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.836620029058493</v>
+        <v>2.964054662514683</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.885543006696013</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.171383696804367</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.172300070776998</v>
+        <v>1.311697811931254</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.04054452803580155</v>
+        <v>0.09449440334489412</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.909869723517494</v>
+        <v>3.037304356973684</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.895631109257453</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-4.026711551704629</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.240257031378333</v>
+        <v>1.379654772532589</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.185216673135539</v>
+        <v>0.2391665484446315</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.006761113138777</v>
+        <v>3.134195746594967</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.881668600658879</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-4.086586379062322</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.202344591836682</v>
+        <v>1.341742332990937</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.1792917210869394</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.956873708125587</v>
+        <v>3.084308341581777</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.896957769893088</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-3.966766148151484</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.265561853435225</v>
+        <v>1.404959594589481</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.1792917210869394</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.972162877359796</v>
+        <v>3.099597510815986</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.804601969215529</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-3.96923585461329</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.172218170172944</v>
+        <v>1.3116159113272</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1228721393160407</v>
+        <v>0.1768220146251333</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.878325252805154</v>
+        <v>3.005759886261344</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.72386383070083</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-4.0376060409373</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.064131957128641</v>
+        <v>1.203529698282898</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1860977136613482</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.803152533712184</v>
+        <v>2.930587167168374</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.714300539332722</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162226675993152</v>
+        <v>-4.051394093784347</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.049053444621714</v>
+        <v>1.18845118577597</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1860977136613482</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.793589242344075</v>
+        <v>2.921023875800265</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.539010104373109</v>
+        <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193219835321857</v>
+        <v>-4.082387253113052</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8613657459306185</v>
+        <v>1.000763487084875</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1860977136613482</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.618298807384462</v>
+        <v>2.745733440840652</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.543577336364896</v>
+        <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017745575529387</v>
+        <v>-3.906912993320583</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9361226818393942</v>
+        <v>1.07552042299365</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1860977136613482</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.62286603937625</v>
+        <v>2.75030067283244</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.519319365126103</v>
+        <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128681828170636</v>
+        <v>-4.017849245961831</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8674902095441017</v>
+        <v>1.006887950698358</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1860977136613482</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.598608068137457</v>
+        <v>2.726042701593647</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.522450750346009</v>
+        <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.095018282698354</v>
+        <v>-3.98418570048955</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8840870129529201</v>
+        <v>1.023484754107176</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.21976125913363</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.621937580640732</v>
+        <v>2.749372214096922</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.532623136778141</v>
+        <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.035165663494631</v>
+        <v>-3.924333081285826</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9182004470665417</v>
+        <v>1.057598188220798</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.21976125913363</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.632109967072864</v>
+        <v>2.759544600529054</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.527569407352002</v>
+        <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.948922200468253</v>
+        <v>-3.838089618259449</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.947644102850953</v>
+        <v>1.087041844005209</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.21976125913363</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.627056237646725</v>
+        <v>2.754490871102914</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.519345182796527</v>
+        <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.994229019867233</v>
+        <v>-3.883396437658429</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9212971505358867</v>
+        <v>1.060694891690143</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.1789510961243992</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.594345915285711</v>
+        <v>2.721780548741901</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.519897055829629</v>
+        <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.023262124569534</v>
+        <v>-3.91242954236073</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9102357816880677</v>
+        <v>1.049633522842324</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.1789510961243992</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.594897788318813</v>
+        <v>2.722332421775003</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.449169747720994</v>
+        <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.930451643118675</v>
+        <v>-3.819619060909871</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8766326661597772</v>
+        <v>1.016030407314033</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.217811702266166</v>
+        <v>0.2717615775752586</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.579856769080694</v>
+        <v>2.707291402536884</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.451043223645595</v>
+        <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974841112448102</v>
+        <v>-3.864008530239299</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8607503543526069</v>
+        <v>1.000148095506863</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1734222329367384</v>
+        <v>0.2273721082458309</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.555096563407639</v>
+        <v>2.682531196863828</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.446118932157318</v>
+        <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862169894211852</v>
+        <v>-3.751337312003049</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9008945501588301</v>
+        <v>1.040292291313086</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.3400433264820811</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.617775002861112</v>
+        <v>2.745209636317302</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.451610227987985</v>
+        <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.74979289302918</v>
+        <v>-3.638960310820376</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9513366464625663</v>
+        <v>1.090734387616822</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.3400433264820811</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.623266298691779</v>
+        <v>2.750700932147969</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.463107429756525</v>
+        <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777573290930533</v>
+        <v>-3.666740708721729</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9517216890705642</v>
+        <v>1.09111943022482</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2583130532716355</v>
+        <v>0.3122629285807281</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.618095261719506</v>
+        <v>2.745529895175696</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.301463149757178</v>
+        <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.860574571955812</v>
+        <v>-3.749741989747008</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7568768966611059</v>
+        <v>0.8962746378153617</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.2936920440535543</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.445308451003855</v>
+        <v>2.572743084460045</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.421612810476383</v>
+        <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.969188650399143</v>
+        <v>-3.858356068190339</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.833580926002979</v>
+        <v>0.9729786671572347</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.2936920440535543</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.565458111723061</v>
+        <v>2.692892745179251</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.436125836578706</v>
+        <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.933779612151</v>
+        <v>-3.822947029942196</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8622575674045592</v>
+        <v>1.001655308558815</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.2936920440535543</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.579971137825384</v>
+        <v>2.707405771281574</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.433545277921075</v>
+        <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.895395949592849</v>
+        <v>-3.784563367384045</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8750304737701882</v>
+        <v>1.014428214924444</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.3320757066117055</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.600420776702643</v>
+        <v>2.727855410158833</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.430274306766377</v>
+        <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.718279619557683</v>
+        <v>-3.607447037348879</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9426060346295571</v>
+        <v>1.082003775783813</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.3320757066117055</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.597149805547946</v>
+        <v>2.724584439004135</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.430957698528291</v>
+        <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.763371864391228</v>
+        <v>-3.652539282182425</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9252525284580519</v>
+        <v>1.064650269612308</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2162297881332231</v>
+        <v>0.2701796634423157</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.560695571408225</v>
+        <v>2.688130204864414</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.424744673834705</v>
+        <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.58399644315246</v>
+        <v>-3.473163860943657</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9907896722599734</v>
+        <v>1.130187413414229</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3730065463039418</v>
+        <v>0.4269564216130344</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.64854860161707</v>
+        <v>2.77598323507326</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.405552129166295</v>
+        <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.629010656673067</v>
+        <v>-3.518178074464263</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9535914421833207</v>
+        <v>1.092989183337576</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3426576509893372</v>
+        <v>0.3966075262984298</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.611146719759897</v>
+        <v>2.738581353216087</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.41124369150524</v>
+        <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.896015166945502</v>
+        <v>-3.785182584736699</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8524812004132922</v>
+        <v>0.991878941567548</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1482946129463886</v>
+        <v>0.2022444882554812</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.500220459273074</v>
+        <v>2.627655092729264</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.410447613401742</v>
+        <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.997212948382675</v>
+        <v>-3.886380366173872</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8112060097349247</v>
+        <v>0.9506037508891803</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.133835674710162</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.458379093042384</v>
+        <v>2.585813726498574</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.408047574956059</v>
+        <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.990701981768362</v>
+        <v>-3.879869399559559</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8114103579349665</v>
+        <v>0.950808099089222</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.133835674710162</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.455979054596701</v>
+        <v>2.58341368805289</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.404572294164304</v>
+        <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.971663854061065</v>
+        <v>-3.860831271852262</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8155503282261303</v>
+        <v>0.9549480693803858</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.07565206337896746</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.417593607006228</v>
+        <v>2.545028240462419</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.582154163102984</v>
+        <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.002790485211683</v>
+        <v>-3.89195790300288</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9806815447045636</v>
+        <v>1.120079285858819</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.07565206337896746</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.595175475944909</v>
+        <v>2.722610109401099</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.582987492089118</v>
+        <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.0166572465456</v>
+        <v>-3.905824664336797</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9759681691571302</v>
+        <v>1.115365910311386</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.03779414664514452</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.573294054890749</v>
+        <v>2.700728688346939</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.588996022486044</v>
+        <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.97185307500567</v>
+        <v>-3.861020492796867</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9998983681700282</v>
+        <v>1.139296109324284</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.03779414664514452</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.579302585287675</v>
+        <v>2.706737218743865</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.668148670278065</v>
+        <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.824110104770668</v>
+        <v>-3.713277522561865</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.138148204056051</v>
+        <v>1.277545945210306</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.2056015038800277</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.759139647420627</v>
+        <v>2.886574280876816</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.670942291809546</v>
+        <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.926124787301889</v>
+        <v>-3.815292205093086</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.100135952575044</v>
+        <v>1.239533693729299</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.2056015038800277</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.761933268952108</v>
+        <v>2.889367902408297</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.671604640201205</v>
+        <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.919972081249105</v>
+        <v>-3.809139499040302</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.103259383387816</v>
+        <v>1.242657124542071</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1578043346237194</v>
+        <v>0.211754209932812</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.766287240975437</v>
+        <v>2.893721874431626</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.670685116941315</v>
+        <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.936781379399606</v>
+        <v>-3.825948797190803</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.095616140867725</v>
+        <v>1.235013882021981</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.1949449117823103</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.755282138825246</v>
+        <v>2.882716772281436</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.737020670738136</v>
+        <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.874483380623484</v>
+        <v>-3.763650798414681</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.186870894174995</v>
+        <v>1.326268635329251</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.1949449117823103</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.821617692622067</v>
+        <v>2.949052326078257</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.539312672452263</v>
+        <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.672693182958326</v>
+        <v>-3.561860600749523</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.069878974955185</v>
+        <v>1.209276716109441</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3390132286423722</v>
+        <v>0.3929631039514647</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.742720609637686</v>
+        <v>2.870155243093877</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.609602904774438</v>
+        <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.59931508586959</v>
+        <v>-3.488482503660787</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.169520446112855</v>
+        <v>1.308918187267111</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4123913257311087</v>
+        <v>0.4663412010402013</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.857037700213104</v>
+        <v>2.984472333669294</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.624230640890482</v>
+        <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.697055630494564</v>
+        <v>-3.586223048285761</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.145051964378909</v>
+        <v>1.284449705533165</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3965020475981285</v>
+        <v>0.4504519229072211</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.862131869449359</v>
+        <v>2.989566502905549</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.622766621715154</v>
+        <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.873393390617494</v>
+        <v>-3.76256080840869</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.073052841154409</v>
+        <v>1.212450582308664</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.2741141627842917</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.754865194200273</v>
+        <v>2.882299827656463</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.621258239755082</v>
+        <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.796971344185567</v>
+        <v>-3.686138761976764</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.102113277767108</v>
+        <v>1.241511018921364</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.2741141627842917</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.753356812240202</v>
+        <v>2.880791445696392</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.621121107190518</v>
+        <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.752598212546998</v>
+        <v>-3.641765630338195</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.119725397857972</v>
+        <v>1.259123139012227</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.3184872944228603</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.779843558658779</v>
+        <v>2.907278192114969</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.615514901329109</v>
+        <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.629763991659831</v>
+        <v>-3.518931409451028</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.163252880351429</v>
+        <v>1.302650621505685</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.3184872944228603</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.77423735279737</v>
+        <v>2.90167198625356</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.621896658356913</v>
+        <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.582108261098775</v>
+        <v>-3.471275678889972</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.188696929603656</v>
+        <v>1.328094670757912</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3121931496748234</v>
+        <v>0.3661430249839159</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.809212548161808</v>
+        <v>2.936647181617998</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.626789031731638</v>
+        <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.481590102600021</v>
+        <v>-3.370757520391217</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.233796566377883</v>
+        <v>1.373194307532138</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4127113081735779</v>
+        <v>0.4666611834826705</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.874415816635785</v>
+        <v>3.001850450091975</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61354370420751</v>
+        <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.54225669300241</v>
+        <v>-3.431424110793607</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.196284602692799</v>
+        <v>1.335682343847055</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3310129914550443</v>
+        <v>0.3849628667641368</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.812151499080537</v>
+        <v>2.939586132536727</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.617641406818139</v>
+        <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.497418291394012</v>
+        <v>-3.386585709185209</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.218317665946787</v>
+        <v>1.357715407101043</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3355564243999137</v>
+        <v>0.3895062997090063</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.818975261458088</v>
+        <v>2.946409894914277</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.621802346449217</v>
+        <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.59817692715101</v>
+        <v>-3.487344344942207</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.182175151275066</v>
+        <v>1.321572892429321</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2467308556729083</v>
+        <v>0.3006807309820009</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.769840859852962</v>
+        <v>2.897275493309152</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.627681948977054</v>
+        <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.55397409006511</v>
+        <v>-3.443141507856307</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.205735888637263</v>
+        <v>1.345133629791519</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.2909336927588088</v>
+        <v>0.3448835680679013</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.80224216463234</v>
+        <v>2.92967679808853</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.626091949446302</v>
+        <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.590953117728553</v>
+        <v>-3.48012053551975</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.189354278041133</v>
+        <v>1.328752019195389</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3818574698592319</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.822836506176386</v>
+        <v>2.950271139632576</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.677339714629341</v>
+        <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.432661700189281</v>
+        <v>-3.321829117980478</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.303918610239882</v>
+        <v>1.443316351394137</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3818574698592319</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.874084271359425</v>
+        <v>3.001518904815615</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.675780419223595</v>
+        <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.39273102701139</v>
+        <v>-3.281898444802587</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.318331584105291</v>
+        <v>1.457729325259547</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.3678382677280296</v>
+        <v>0.4217881430371222</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.896483379860412</v>
+        <v>3.023918013316603</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.670728647461865</v>
+        <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.341698934288862</v>
+        <v>-3.230866352080059</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.333692649432572</v>
+        <v>1.473090390586828</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4188703604505576</v>
+        <v>0.4728202357596502</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.922050863732199</v>
+        <v>3.049485497188389</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.687916051554569</v>
+        <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.276474753161657</v>
+        <v>-3.165642170952854</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.37696972597616</v>
+        <v>1.516367467130415</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.4840945415777632</v>
+        <v>0.5380444168868558</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.978372776501228</v>
+        <v>3.105807409957417</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.68387702385385</v>
+        <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.239047733090523</v>
+        <v>-3.12821515088172</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.387901506303893</v>
+        <v>1.527299247458149</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.4893460796069449</v>
+        <v>0.5432959549160374</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.977484671618017</v>
+        <v>3.104919305074207</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.68513381618509</v>
+        <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.259159389125232</v>
+        <v>-3.148326806916428</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.38111363622125</v>
+        <v>1.520511377375506</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5003734246043641</v>
+        <v>0.5543232999134566</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.985357870947709</v>
+        <v>3.112792504403899</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.845691587206301</v>
+        <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.205414574698027</v>
+        <v>-3.094581992489223</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.563169333013343</v>
+        <v>1.702567074167598</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.510436734044826</v>
+        <v>0.5643866093539186</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.151953627633197</v>
+        <v>3.279388261089387</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.965804496424118</v>
+        <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.181623006091884</v>
+        <v>-3.070790423883081</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.692798869673617</v>
+        <v>1.832196610827873</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5342283026509683</v>
+        <v>0.5881781779600609</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.2863414780147</v>
+        <v>3.413776111470889</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.957512472437977</v>
+        <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.155538921828076</v>
+        <v>-3.044706339619273</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.694940479392999</v>
+        <v>1.834338220547255</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5342283026509683</v>
+        <v>0.5881781779600609</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.278049454028559</v>
+        <v>3.405484087484748</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.955705668021757</v>
+        <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.07740774097913</v>
+        <v>-2.966575158770326</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.724386147316358</v>
+        <v>1.863783888470613</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6084051135346529</v>
+        <v>0.6623549888437454</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.320748736142549</v>
+        <v>3.448183369598739</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.973260073748548</v>
+        <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.068515279585847</v>
+        <v>-2.957682697377043</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.745497537600462</v>
+        <v>1.884895278754718</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6084051135346529</v>
+        <v>0.6623549888437454</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.33830314186934</v>
+        <v>3.46573777532553</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.965115121153132</v>
+        <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.236991396555724</v>
+        <v>-3.126158814346921</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.669962138217095</v>
+        <v>1.809359879371351</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5804572778180721</v>
+        <v>0.6344071531271647</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.313389487843975</v>
+        <v>3.440824121300165</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.946384818340994</v>
+        <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.539191867694141</v>
+        <v>-2.428359285485338</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.93035164694959</v>
+        <v>2.069749388103846</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5101092184476614</v>
+        <v>0.564059093756754</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.252450349409591</v>
+        <v>3.379884982865781</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.937048840837898</v>
+        <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.516470764010989</v>
+        <v>-2.405638181802185</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.930104110919756</v>
+        <v>2.069501852074011</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5101092184476614</v>
+        <v>0.564059093756754</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.243114371906495</v>
+        <v>3.370549005362685</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.095954966689067</v>
+        <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.514745720720945</v>
+        <v>-2.403913138512142</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.089700254086942</v>
+        <v>2.229097995241198</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5118342617377052</v>
+        <v>0.5657841370467978</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.403055523731691</v>
+        <v>3.53049015718788</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.133032789182714</v>
+        <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.6695267274992</v>
+        <v>-2.558694145290397</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.064865673869287</v>
+        <v>2.204263415023542</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.4784665876832291</v>
+        <v>0.5324164629923216</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.420112741792652</v>
+        <v>3.547547375248842</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.129708145172259</v>
+        <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.61809139411454</v>
+        <v>-2.507258811905737</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.082115163212696</v>
+        <v>2.221512904366951</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5299019210678888</v>
+        <v>0.5838517963769813</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.447649297812993</v>
+        <v>3.575083931269182</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.139714298817001</v>
+        <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.591140169788052</v>
+        <v>-2.480307587579249</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.102901806588032</v>
+        <v>2.242299547742288</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.544782267095608</v>
+        <v>0.5987321424047004</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.466583659074366</v>
+        <v>3.594018292530555</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32381743096196</v>
+        <v>3.418882139232695</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.727093177844369</v>
+        <v>-2.616260595635565</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.232623735510466</v>
+        <v>2.372021476664721</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.544782267095608</v>
+        <v>0.5987321424047004</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.650686791219325</v>
+        <v>3.778121424675515</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.315934125864954</v>
+        <v>3.410998834135688</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.749501295649241</v>
+        <v>-2.638668713440437</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.21577718329151</v>
+        <v>2.355174924445766</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.544782267095608</v>
+        <v>0.5987321424047004</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.642803486122319</v>
+        <v>3.770238119578508</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.317988125414591</v>
+        <v>3.413052833685325</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.89750706312864</v>
+        <v>-2.786674480919837</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.158628875849388</v>
+        <v>2.298026617003643</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4580552582320665</v>
+        <v>0.512005133541159</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.592821280353831</v>
+        <v>3.720255913810021</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.374241843136438</v>
+        <v>3.469306551407172</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.90694798901717</v>
+        <v>-2.796115406808367</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.211106223215823</v>
+        <v>2.350503964370079</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.5804823757754579</v>
+        <v>0.6344322510845504</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.722531268601713</v>
+        <v>3.849965902057903</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.377132937681739</v>
+        <v>3.472197645952473</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.905661225477614</v>
+        <v>-2.794828643268811</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.214512023176946</v>
+        <v>2.353909764331202</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5817691393150145</v>
+        <v>0.635719014624107</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.726194421270748</v>
+        <v>3.853629054726938</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.375244750575514</v>
+        <v>3.470309458846248</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.907218279466905</v>
+        <v>-2.796385697258102</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.212001014475005</v>
+        <v>2.35139875562926</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5817691393150145</v>
+        <v>0.635719014624107</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.724306234164523</v>
+        <v>3.851740867620713</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.370064980178376</v>
+        <v>3.465129688449111</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.91449016499037</v>
+        <v>-2.803657582781566</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.203912489868482</v>
+        <v>2.343310231022737</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5744972537915498</v>
+        <v>0.6284471291006422</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.714763332453307</v>
+        <v>3.842197965909496</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.368498990388529</v>
+        <v>3.463563698659263</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.912649145932118</v>
+        <v>-2.801816563723315</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.203082907701934</v>
+        <v>2.34248064885619</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6297153557721106</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.71395827866634</v>
+        <v>3.841392912122529</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.381572397254447</v>
+        <v>3.476637105525182</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.919557851431799</v>
+        <v>-2.808725269222996</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.213392832367981</v>
+        <v>2.352790573522236</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6297153557721106</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.727031685532259</v>
+        <v>3.854466318988448</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.381572397254447</v>
+        <v>3.476637105525182</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.921119494246659</v>
+        <v>-2.810286912037856</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.212768175242037</v>
+        <v>2.352165916396292</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6297153557721106</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.727031685532259</v>
+        <v>3.854466318988448</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.380096438381449</v>
+        <v>3.475161146652184</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.949020281356132</v>
+        <v>-2.838187699147328</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.200131901525249</v>
+        <v>2.339529642679505</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5411685563200834</v>
+        <v>0.5951184316291758</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.7047975721735</v>
+        <v>3.83223220562969</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.376860882358648</v>
+        <v>3.471925590629382</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.952053278868806</v>
+        <v>-2.841220696660002</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.195683146497379</v>
+        <v>2.335080887651634</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5381355588074095</v>
+        <v>0.5920854341165018</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.699742217643094</v>
+        <v>3.827176851099284</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.443566841949152</v>
+        <v>3.538631550219886</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.972114600145312</v>
+        <v>-2.861282017936509</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.25436457757728</v>
+        <v>2.393762318731535</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5180742375309024</v>
+        <v>0.5720241128399948</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.754411384467693</v>
+        <v>3.881846017923883</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.583878560950999</v>
+        <v>3.678943269221733</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.228835418140136</v>
+        <v>-3.118002835931333</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.291987969381197</v>
+        <v>2.431385710535452</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4636095386961799</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.829674358983252</v>
+        <v>3.957108992439442</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.652858830096639</v>
+        <v>3.747923538367373</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.382821835916277</v>
+        <v>-3.271989253707474</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.29937367141638</v>
+        <v>2.438771412570636</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4636095386961799</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.898654628128892</v>
+        <v>4.026089261585081</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.768882736649164</v>
+        <v>3.753435936199363</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.63891003221676</v>
+        <v>3.733974740487494</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.515355296735239</v>
+        <v>-3.221467349879808</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.232411489208917</v>
+        <v>2.445031376221824</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4636095386961799</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.884705830249013</v>
+        <v>4.012140463705202</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-66.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.1%</t>
+          <t>460.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-483.7%</t>
+          <t>-481.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-131.7%</t>
+          <t>-130.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-111.7%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-177.6%</t>
+          <t>-183.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-48.0%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.90235661232586</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2063383228528357</v>
+        <v>0.1620052899693145</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.9826659762561126</v>
+        <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.37803780634326</v>
+        <v>2.345667881157804</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.849387090071872</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2188121455009528</v>
+        <v>0.1744791126174317</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9296964540021238</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.401105533442175</v>
+        <v>2.36873560825672</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.805838683301181</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2292708961141359</v>
+        <v>0.1849378632306147</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9296964540021238</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.394144921347082</v>
+        <v>2.361774996161627</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.563690289847323</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3405926078768222</v>
+        <v>0.296259574993301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9296964540021238</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.408607275728225</v>
+        <v>2.37623735054277</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.455431152724802</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3784283831850259</v>
+        <v>0.3340953503015047</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9296964540021238</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.40313939618742</v>
+        <v>2.370769471001965</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.332140017907671</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.425242931122455</v>
+        <v>0.3809098982389338</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8064053191849933</v>
+        <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.474612171088275</v>
+        <v>2.44224224590282</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.310990819004227</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4414035889211578</v>
+        <v>0.3970705560376366</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7852561202815499</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.495002668667667</v>
+        <v>2.462632743482211</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.067225377020783</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5346904740615863</v>
+        <v>0.4903574411780647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7852561202815499</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.490783377014717</v>
+        <v>2.458413451829262</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.965462556743488</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5775199160925202</v>
+        <v>0.533186883208999</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7720370518891212</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.50083913197019</v>
+        <v>2.468469206784735</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.715612162794414</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6702021486558523</v>
+        <v>0.6258691157723311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7720370518891212</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.493581206953893</v>
+        <v>2.461211281768437</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.539720070326981</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7441581091634739</v>
+        <v>0.6998250762799523</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7720370518891212</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.497180330474541</v>
+        <v>2.464810405289086</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.368273607304517</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8260642004270133</v>
+        <v>0.7817311675434917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6005905888666581</v>
+        <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.613375714342573</v>
+        <v>2.581005789157117</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.293984041566178</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.854800504338646</v>
+        <v>0.8104674714551243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5263010231283187</v>
+        <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.656969931401873</v>
+        <v>2.624600006216418</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.230348299332244</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8849496022865369</v>
+        <v>0.8406165694030152</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.4626652808943842</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.699846177796551</v>
+        <v>2.667476252611096</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.118921540006323</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9107145648007005</v>
+        <v>0.8663815319171788</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.4626652808943842</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.681040436580347</v>
+        <v>2.648670511394891</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.878491043201463</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.008629840147522</v>
+        <v>0.9642968072640004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2222347840895239</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.827041811288141</v>
+        <v>2.794671886102685</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.806248475030269</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04145618125082</v>
+        <v>0.9971231483672984</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2222347840895239</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.830971125122961</v>
+        <v>2.798601199937505</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.753250152748881</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.063334094080715</v>
+        <v>1.019001061197194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1668985250875851</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.864851464441464</v>
+        <v>2.832481539256008</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.644445267269154</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.103854119492599</v>
+        <v>1.059521086609078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1668985250875851</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.861849535661458</v>
+        <v>2.829479610476002</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.424424469232143</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.193441475718018</v>
+        <v>1.149108442834496</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.02567868001960483</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.94816047971286</v>
+        <v>2.915790554527404</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.291556780168865</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.262482734145152</v>
+        <v>1.218149701261631</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.02567868001960483</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.964054662514683</v>
+        <v>2.931684737329228</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.171383696804367</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.311697811931254</v>
+        <v>1.267364779047732</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.09449440334489412</v>
+        <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.037304356973684</v>
+        <v>3.004934431788229</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.026711551704629</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.379654772532589</v>
+        <v>1.335321739649067</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.2391665484446315</v>
+        <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.134195746594967</v>
+        <v>3.101825821409511</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.086586379062322</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.341742332990937</v>
+        <v>1.297409300107416</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1792917210869394</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.084308341581777</v>
+        <v>3.051938416396322</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.966766148151484</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.404959594589481</v>
+        <v>1.360626561705959</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1792917210869394</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.099597510815986</v>
+        <v>3.06722758563053</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.96923585461329</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.3116159113272</v>
+        <v>1.267282878443678</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1768220146251333</v>
+        <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.005759886261344</v>
+        <v>2.973389961075888</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.0376060409373</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.203529698282898</v>
+        <v>1.159196665399375</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1860977136613482</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.930587167168374</v>
+        <v>2.898217241982918</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.051394093784347</v>
+        <v>-4.026680381377224</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.18845118577597</v>
+        <v>1.198336670738819</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1860977136613482</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.921023875800265</v>
+        <v>2.88865395061481</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.082387253113052</v>
+        <v>-4.057673540705929</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.000763487084875</v>
+        <v>1.010648972047724</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1860977136613482</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.745733440840652</v>
+        <v>2.713363515655197</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.906912993320583</v>
+        <v>-3.88219928091346</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.07552042299365</v>
+        <v>1.085405907956499</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1860977136613482</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.75030067283244</v>
+        <v>2.717930747646984</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.017849245961831</v>
+        <v>-3.993135533554709</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.006887950698358</v>
+        <v>1.016773435661207</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1860977136613482</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.726042701593647</v>
+        <v>2.693672776408191</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.98418570048955</v>
+        <v>-3.959471988082427</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.023484754107176</v>
+        <v>1.033370239070025</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.21976125913363</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.749372214096922</v>
+        <v>2.717002288911466</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.924333081285826</v>
+        <v>-3.899619368878704</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.057598188220798</v>
+        <v>1.067483673183647</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.21976125913363</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.759544600529054</v>
+        <v>2.727174675343599</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.838089618259449</v>
+        <v>-3.813375905852326</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.087041844005209</v>
+        <v>1.096927328968058</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.21976125913363</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.754490871102914</v>
+        <v>2.722120945917459</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.883396437658429</v>
+        <v>-3.858682725251306</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.060694891690143</v>
+        <v>1.070580376652992</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1789510961243992</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.721780548741901</v>
+        <v>2.689410623556446</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.91242954236073</v>
+        <v>-3.887715829953608</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.049633522842324</v>
+        <v>1.059519007805173</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1789510961243992</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.722332421775003</v>
+        <v>2.689962496589547</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.819619060909871</v>
+        <v>-3.794905348502748</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.016030407314033</v>
+        <v>1.025915892276882</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.2717615775752586</v>
+        <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.707291402536884</v>
+        <v>2.674921477351428</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.864008530239299</v>
+        <v>-3.839294817832176</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.000148095506863</v>
+        <v>1.010033580469712</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2273721082458309</v>
+        <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.682531196863828</v>
+        <v>2.650161271678373</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.751337312003049</v>
+        <v>-3.726623599595926</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.040292291313086</v>
+        <v>1.050177776275935</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3400433264820811</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.745209636317302</v>
+        <v>2.712839711131846</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.638960310820376</v>
+        <v>-3.614246598413253</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.090734387616822</v>
+        <v>1.100619872579671</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3400433264820811</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.750700932147969</v>
+        <v>2.718331006962513</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.666740708721729</v>
+        <v>-3.642026996314606</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.09111943022482</v>
+        <v>1.101004915187669</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3122629285807281</v>
+        <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.745529895175696</v>
+        <v>2.71315996999024</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.749741989747008</v>
+        <v>-3.725028277339885</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8962746378153617</v>
+        <v>0.9061601227782108</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2936920440535543</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.572743084460045</v>
+        <v>2.540373159274589</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.858356068190339</v>
+        <v>-3.833642355783216</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9729786671572347</v>
+        <v>0.9828641521200838</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2936920440535543</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.692892745179251</v>
+        <v>2.660522819993795</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.822947029942196</v>
+        <v>-3.798233317535074</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.001655308558815</v>
+        <v>1.011540793521664</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2936920440535543</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.707405771281574</v>
+        <v>2.675035846096118</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.784563367384045</v>
+        <v>-3.759849654976922</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.014428214924444</v>
+        <v>1.024313699887293</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3320757066117055</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.727855410158833</v>
+        <v>2.695485484973378</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.607447037348879</v>
+        <v>-3.582733324941756</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.082003775783813</v>
+        <v>1.091889260746662</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3320757066117055</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.724584439004135</v>
+        <v>2.69221451381868</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.652539282182425</v>
+        <v>-3.627825569775302</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.064650269612308</v>
+        <v>1.074535754575157</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2701796634423157</v>
+        <v>0.2162297881332231</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.688130204864414</v>
+        <v>2.655760279678959</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.473163860943657</v>
+        <v>-3.448450148536534</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.130187413414229</v>
+        <v>1.140072898377078</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4269564216130344</v>
+        <v>0.3730065463039418</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.77598323507326</v>
+        <v>2.743613309887805</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.518178074464263</v>
+        <v>-3.493464362057141</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.092989183337576</v>
+        <v>1.102874668300426</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3966075262984298</v>
+        <v>0.3426576509893372</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.738581353216087</v>
+        <v>2.706211428030632</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.785182584736699</v>
+        <v>-3.760468872329576</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.991878941567548</v>
+        <v>1.001764426530397</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2022444882554812</v>
+        <v>0.1482946129463886</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.627655092729264</v>
+        <v>2.595285167543808</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.886380366173872</v>
+        <v>-3.861666653766749</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9506037508891803</v>
+        <v>0.9604892358520294</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.133835674710162</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.585813726498574</v>
+        <v>2.553443801313118</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.879869399559559</v>
+        <v>-3.855155687152436</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.950808099089222</v>
+        <v>0.9606935840520712</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.133835674710162</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.58341368805289</v>
+        <v>2.551043762867435</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.860831271852262</v>
+        <v>-3.836117559445139</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9549480693803858</v>
+        <v>0.9648335543432349</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.07565206337896746</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.545028240462419</v>
+        <v>2.512658315276963</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.89195790300288</v>
+        <v>-3.867244190595757</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.120079285858819</v>
+        <v>1.129964770821668</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.07565206337896746</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.722610109401099</v>
+        <v>2.690240184215644</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.905824664336797</v>
+        <v>-3.881110951929674</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.115365910311386</v>
+        <v>1.125251395274235</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.03779414664514452</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.700728688346939</v>
+        <v>2.668358763161483</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.861020492796867</v>
+        <v>-3.836306780389744</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.139296109324284</v>
+        <v>1.149181594287133</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.03779414664514452</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.706737218743865</v>
+        <v>2.674367293558409</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.713277522561865</v>
+        <v>-3.688563810154742</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.277545945210306</v>
+        <v>1.287431430173156</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2056015038800277</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886574280876816</v>
+        <v>2.854204355691361</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.815292205093086</v>
+        <v>-3.790578492685963</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.239533693729299</v>
+        <v>1.249419178692148</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2056015038800277</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889367902408297</v>
+        <v>2.856997977222842</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.809139499040302</v>
+        <v>-3.784425786633179</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.242657124542071</v>
+        <v>1.25254260950492</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.211754209932812</v>
+        <v>0.1578043346237194</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893721874431626</v>
+        <v>2.861351949246171</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.825948797190803</v>
+        <v>-3.80123508478368</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.235013882021981</v>
+        <v>1.24489936698483</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1949449117823103</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882716772281436</v>
+        <v>2.85034684709598</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.763650798414681</v>
+        <v>-3.738937086007558</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.326268635329251</v>
+        <v>1.3361541202921</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1949449117823103</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.949052326078257</v>
+        <v>2.916682400892801</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.561860600749523</v>
+        <v>-3.5371468883424</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.209276716109441</v>
+        <v>1.21916220107229</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3929631039514647</v>
+        <v>0.3390132286423722</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.870155243093877</v>
+        <v>2.837785317908421</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.488482503660787</v>
+        <v>-3.463768791253664</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.308918187267111</v>
+        <v>1.31880367222996</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4663412010402013</v>
+        <v>0.4123913257311087</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.984472333669294</v>
+        <v>2.952102408483838</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.586223048285761</v>
+        <v>-3.561509335878638</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.284449705533165</v>
+        <v>1.294335190496014</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4504519229072211</v>
+        <v>0.3965020475981285</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.989566502905549</v>
+        <v>2.957196577720094</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.76256080840869</v>
+        <v>-3.737847096001568</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.212450582308664</v>
+        <v>1.222336067271514</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2741141627842917</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.882299827656463</v>
+        <v>2.849929902471008</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.686138761976764</v>
+        <v>-3.661425049569641</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.241511018921364</v>
+        <v>1.251396503884213</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2741141627842917</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.880791445696392</v>
+        <v>2.848421520510936</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.641765630338195</v>
+        <v>-3.617051917931072</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.259123139012227</v>
+        <v>1.269008623975076</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3184872944228603</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.907278192114969</v>
+        <v>2.874908266929514</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.518931409451028</v>
+        <v>-3.494217697043905</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.302650621505685</v>
+        <v>1.312536106468534</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3184872944228603</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.90167198625356</v>
+        <v>2.869302061068104</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.471275678889972</v>
+        <v>-3.446561966482849</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.328094670757912</v>
+        <v>1.337980155720761</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3661430249839159</v>
+        <v>0.3121931496748234</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.936647181617998</v>
+        <v>2.904277256432542</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.370757520391217</v>
+        <v>-3.346043807984095</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.373194307532138</v>
+        <v>1.383079792494987</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4666611834826705</v>
+        <v>0.4127113081735779</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.001850450091975</v>
+        <v>2.969480524906519</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.431424110793607</v>
+        <v>-3.406710398386484</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.335682343847055</v>
+        <v>1.345567828809904</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3849628667641368</v>
+        <v>0.3310129914550443</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.939586132536727</v>
+        <v>2.907216207351272</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.386585709185209</v>
+        <v>-3.361871996778086</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.357715407101043</v>
+        <v>1.367600892063892</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3895062997090063</v>
+        <v>0.3355564243999137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.946409894914277</v>
+        <v>2.914039969728822</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.487344344942207</v>
+        <v>-3.462630632535084</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.321572892429321</v>
+        <v>1.33145837739217</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3006807309820009</v>
+        <v>0.2467308556729083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.897275493309152</v>
+        <v>2.864905568123697</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.443141507856307</v>
+        <v>-3.418427795449184</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.345133629791519</v>
+        <v>1.355019114754368</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3448835680679013</v>
+        <v>0.2909336927588088</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.92967679808853</v>
+        <v>2.897306872903074</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.48012053551975</v>
+        <v>-3.455406823112627</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.328752019195389</v>
+        <v>1.338637504158238</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3818574698592319</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.950271139632576</v>
+        <v>2.91790121444712</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.321829117980478</v>
+        <v>-3.297115405573355</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.443316351394137</v>
+        <v>1.453201836356987</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3818574698592319</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.001518904815615</v>
+        <v>2.96914897963016</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.281898444802587</v>
+        <v>-3.257184732395464</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.457729325259547</v>
+        <v>1.467614810222396</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.4217881430371222</v>
+        <v>0.3678382677280296</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.023918013316603</v>
+        <v>2.991548088131147</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.230866352080059</v>
+        <v>-3.206152639672936</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.473090390586828</v>
+        <v>1.482975875549677</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4728202357596502</v>
+        <v>0.4188703604505576</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.049485497188389</v>
+        <v>3.017115572002933</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.165642170952854</v>
+        <v>-3.140928458545731</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.516367467130415</v>
+        <v>1.526252952093264</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.5380444168868558</v>
+        <v>0.4840945415777632</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.105807409957417</v>
+        <v>3.073437484771962</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.12821515088172</v>
+        <v>-3.103501438474597</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.527299247458149</v>
+        <v>1.537184732420998</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.5432959549160374</v>
+        <v>0.4893460796069449</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.104919305074207</v>
+        <v>3.072549379888752</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.148326806916428</v>
+        <v>-3.123613094509305</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.520511377375506</v>
+        <v>1.530396862338355</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5543232999134566</v>
+        <v>0.5003734246043641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.112792504403899</v>
+        <v>3.080422579218443</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.094581992489223</v>
+        <v>-3.069868280082101</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.702567074167598</v>
+        <v>1.712452559130448</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.5643866093539186</v>
+        <v>0.510436734044826</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.279388261089387</v>
+        <v>3.247018335903931</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.070790423883081</v>
+        <v>-3.046076711475958</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.832196610827873</v>
+        <v>1.842082095790722</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5881781779600609</v>
+        <v>0.5342283026509683</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.413776111470889</v>
+        <v>3.381406186285434</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.044706339619273</v>
+        <v>-3.01999262721215</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.834338220547255</v>
+        <v>1.844223705510104</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5881781779600609</v>
+        <v>0.5342283026509683</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.405484087484748</v>
+        <v>3.373114162299293</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.966575158770326</v>
+        <v>-2.941861446363204</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.863783888470613</v>
+        <v>1.873669373433462</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6623549888437454</v>
+        <v>0.6084051135346529</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.448183369598739</v>
+        <v>3.415813444413283</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.957682697377043</v>
+        <v>-2.932968984969921</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.884895278754718</v>
+        <v>1.894780763717567</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6623549888437454</v>
+        <v>0.6084051135346529</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.46573777532553</v>
+        <v>3.433367850140074</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.126158814346921</v>
+        <v>-3.101445101939798</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.809359879371351</v>
+        <v>1.8192453643342</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.6344071531271647</v>
+        <v>0.5804572778180721</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.440824121300165</v>
+        <v>3.40845419611471</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.428359285485338</v>
+        <v>-2.403645573078215</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.069749388103846</v>
+        <v>2.079634873066695</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.564059093756754</v>
+        <v>0.5101092184476614</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.379884982865781</v>
+        <v>3.347515057680325</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.405638181802185</v>
+        <v>-2.380924469395063</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.069501852074011</v>
+        <v>2.07938733703686</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.564059093756754</v>
+        <v>0.5101092184476614</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.370549005362685</v>
+        <v>3.33817908017723</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.403913138512142</v>
+        <v>-2.379199426105019</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.229097995241198</v>
+        <v>2.238983480204047</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5657841370467978</v>
+        <v>0.5118342617377052</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.53049015718788</v>
+        <v>3.498120232002425</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.558694145290397</v>
+        <v>-2.533980432883274</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.204263415023542</v>
+        <v>2.214148899986391</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.5324164629923216</v>
+        <v>0.4784665876832291</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.547547375248842</v>
+        <v>3.515177450063386</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.507258811905737</v>
+        <v>-2.482545099498614</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.221512904366951</v>
+        <v>2.2313983893298</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5838517963769813</v>
+        <v>0.5299019210678888</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.575083931269182</v>
+        <v>3.542714006083727</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.480307587579249</v>
+        <v>-2.455593875172126</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.242299547742288</v>
+        <v>2.252185032705137</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.5987321424047004</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.594018292530555</v>
+        <v>3.5616483673451</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.418882139232695</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.616260595635565</v>
+        <v>-2.591546883228443</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.372021476664721</v>
+        <v>2.38190696162757</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.5987321424047004</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.778121424675515</v>
+        <v>3.74575149949006</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.410998834135688</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.638668713440437</v>
+        <v>-2.613955001033315</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.355174924445766</v>
+        <v>2.365060409408615</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.5987321424047004</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.770238119578508</v>
+        <v>3.737868194393053</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.413052833685325</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.786674480919837</v>
+        <v>-2.761960768512714</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.298026617003643</v>
+        <v>2.307912101966492</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.512005133541159</v>
+        <v>0.4580552582320665</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.720255913810021</v>
+        <v>3.687885988624565</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.469306551407172</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.796115406808367</v>
+        <v>-2.771401694401244</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.350503964370079</v>
+        <v>2.360389449332928</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.6344322510845504</v>
+        <v>0.5804823757754579</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.849965902057903</v>
+        <v>3.817595976872447</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.472197645952473</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.794828643268811</v>
+        <v>-2.770114930861688</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.353909764331202</v>
+        <v>2.363795249294051</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.635719014624107</v>
+        <v>0.5817691393150145</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.853629054726938</v>
+        <v>3.821259129541482</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.470309458846248</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.796385697258102</v>
+        <v>-2.771671984850979</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.35139875562926</v>
+        <v>2.361284240592109</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.635719014624107</v>
+        <v>0.5817691393150145</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.851740867620713</v>
+        <v>3.819370942435258</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.465129688449111</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.803657582781566</v>
+        <v>-2.778943870374444</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.343310231022737</v>
+        <v>2.353195715985586</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6284471291006422</v>
+        <v>0.5744972537915498</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.842197965909496</v>
+        <v>3.809828040724041</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.463563698659263</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.801816563723315</v>
+        <v>-2.777102851316192</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.34248064885619</v>
+        <v>2.352366133819039</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6297153557721106</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.841392912122529</v>
+        <v>3.809022986937074</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.476637105525182</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.808725269222996</v>
+        <v>-2.784011556815873</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.352790573522236</v>
+        <v>2.362676058485085</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6297153557721106</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.854466318988448</v>
+        <v>3.822096393802993</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.476637105525182</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.810286912037856</v>
+        <v>-2.785573199630733</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.352165916396292</v>
+        <v>2.362051401359142</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6297153557721106</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.854466318988448</v>
+        <v>3.822096393802993</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.475161146652184</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.838187699147328</v>
+        <v>-2.813473986740206</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.339529642679505</v>
+        <v>2.349415127642354</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5951184316291758</v>
+        <v>0.5411685563200834</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.83223220562969</v>
+        <v>3.799862280444234</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.471925590629382</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.841220696660002</v>
+        <v>-2.81650698425288</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.335080887651634</v>
+        <v>2.344966372614484</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5920854341165018</v>
+        <v>0.5381355588074095</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.827176851099284</v>
+        <v>3.794806925913829</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.538631550219886</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.861282017936509</v>
+        <v>-2.836568305529386</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.393762318731535</v>
+        <v>2.403647803694384</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5720241128399948</v>
+        <v>0.5180742375309024</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.881846017923883</v>
+        <v>3.849476092738428</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.678943269221733</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.118002835931333</v>
+        <v>-3.09328912352421</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.431385710535452</v>
+        <v>2.441271195498302</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4636095386961799</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.957108992439442</v>
+        <v>3.924739067253986</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.747923538367373</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.271989253707474</v>
+        <v>-3.247275541300351</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.438771412570636</v>
+        <v>2.448656897533485</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4636095386961799</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.026089261585081</v>
+        <v>3.993719336399626</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.753435936199363</v>
+        <v>3.777059612218702</v>
       </c>
       <c r="C2018" t="n">
         <v>3.733974740487494</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.221467349879808</v>
+        <v>-3.196753637472685</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.445031376221824</v>
+        <v>2.454916861184673</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4636095386961799</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.012140463705202</v>
+        <v>3.979770538519746</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-65.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.5%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-481.2%</t>
+          <t>-473.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-130.7%</t>
+          <t>-137.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-111.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-183.0%</t>
+          <t>-177.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-68.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2018"/>
+  <dimension ref="A1:G2019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.872572683826192</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.013189194534664</v>
+        <v>-6.903604769460788</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1620052899693145</v>
+        <v>0.1107743517281299</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.036615851565205</v>
+        <v>-0.981686558855107</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.345667881157804</v>
+        <v>2.283560748513128</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.863858697572714</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.960219672280675</v>
+        <v>-6.8506352472068</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1744791126174317</v>
+        <v>0.123248174376247</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9287170366011182</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.36873560825672</v>
+        <v>2.306628475612044</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.856898085477621</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.916671265509985</v>
+        <v>-6.807086840436109</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1849378632306147</v>
+        <v>0.13370692498943</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9287170366011182</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.361774996161627</v>
+        <v>2.299667863516951</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.871360439858764</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.674522872056126</v>
+        <v>-6.564938446982251</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.296259574993301</v>
+        <v>0.2450286367521164</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9287170366011182</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.37623735054277</v>
+        <v>2.314130217898094</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.865892560317959</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.566263734933605</v>
+        <v>-6.456679309859729</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3340953503015047</v>
+        <v>0.2828644120603201</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.9287170366011182</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.370769471001965</v>
+        <v>2.308662338357289</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.863390654328536</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.442972600116474</v>
+        <v>-6.333388175042598</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3809098982389338</v>
+        <v>0.3296789599977492</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8603551944940857</v>
+        <v>-0.8054259017839877</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.44224224590282</v>
+        <v>2.380135113258144</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.871091632565862</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.421823401213031</v>
+        <v>-6.312238976139155</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3970705560376366</v>
+        <v>0.3458396177964524</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.7842767028805443</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.462632743482211</v>
+        <v>2.400525610837535</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.866872340912912</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.178057959229586</v>
+        <v>-6.068473534155711</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4903574411780647</v>
+        <v>0.4391265029368809</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.7842767028805443</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.458413451829262</v>
+        <v>2.396306319184586</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.868996654832928</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.076295138952291</v>
+        <v>-5.966710713878416</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.533186883208999</v>
+        <v>0.4819559449678148</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7710576344881156</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.468469206784735</v>
+        <v>2.40636207414006</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.861738729816631</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.826444745003217</v>
+        <v>-5.716860319929341</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6258691157723311</v>
+        <v>0.5746381775311469</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7710576344881156</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.461211281768437</v>
+        <v>2.399104149123762</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.865337853337279</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.650552652535785</v>
+        <v>-5.540968227461908</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6998250762799523</v>
+        <v>0.6485941380387685</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.7710576344881156</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.464810405289086</v>
+        <v>2.40270327264441</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.878665359391833</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.479106189513321</v>
+        <v>-5.369521764439445</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7817311675434917</v>
+        <v>0.730500229302308</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6545404641757505</v>
+        <v>-0.5996111714656525</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.581005789157117</v>
+        <v>2.518898656512442</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.87768583700813</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.404816623774982</v>
+        <v>-5.295232198701106</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8104674714551243</v>
+        <v>0.7592365332139406</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5802508984374113</v>
+        <v>-0.5253216057273131</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624600006216418</v>
+        <v>2.562492873571742</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.882380638062447</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.341180881541048</v>
+        <v>-5.231596456467171</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8406165694030152</v>
+        <v>0.7893856311618315</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.4616858634933786</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.667476252611096</v>
+        <v>2.60536911996642</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.863574896846243</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-5.120169697141251</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8663815319171788</v>
+        <v>0.8151505936759951</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.4616858634933786</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.648670511394891</v>
+        <v>2.586563378750216</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.86531797347112</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-4.879739200336391</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9642968072640004</v>
+        <v>0.9130658690228166</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.2212553666885183</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.794671886102685</v>
+        <v>2.73256475345801</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.86924728730594</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-4.807496632165196</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9971231483672984</v>
+        <v>0.9458922101261147</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.2212553666885183</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.798601199937505</v>
+        <v>2.73649406729283</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.86992587122328</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.754498309883808</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019001061197194</v>
+        <v>0.9677701229560098</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.1659191076865795</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832481539256008</v>
+        <v>2.770374406611333</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.866923942443274</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.645693424404081</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.059521086609078</v>
+        <v>1.008290148367894</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.1659191076865795</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829479610476002</v>
+        <v>2.767372477831326</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.868502979453888</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.425672626367071</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.149108442834496</v>
+        <v>1.097877504593312</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.07962855532869739</v>
+        <v>-0.02469926261859923</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915790554527404</v>
+        <v>2.853683421882729</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.884397162255711</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.292804937303793</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.218149701261631</v>
+        <v>1.166918763020447</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.07962855532869739</v>
+        <v>-0.02469926261859923</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.931684737329228</v>
+        <v>2.869577604684552</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.885543006696013</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.172631853939294</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267364779047732</v>
+        <v>1.216133840806548</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.04054452803580155</v>
+        <v>0.09547382074589972</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004934431788229</v>
+        <v>2.942827299143553</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.895631109257453</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-4.027959708839557</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.335321739649067</v>
+        <v>1.284090801407883</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.185216673135539</v>
+        <v>0.2401459658456371</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.101825821409511</v>
+        <v>3.039718688764836</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.881668600658879</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-4.087834536197249</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.297409300107416</v>
+        <v>1.246178361866232</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.180271138487945</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.051938416396322</v>
+        <v>2.989831283751646</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.896957769893088</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-3.968014305286412</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360626561705959</v>
+        <v>1.309395623464775</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.180271138487945</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06722758563053</v>
+        <v>3.005120452985855</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.804601969215529</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-3.970484011748218</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267282878443678</v>
+        <v>1.216051940202495</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1228721393160407</v>
+        <v>0.1778014320261389</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.973389961075888</v>
+        <v>2.911282828431212</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.72386383070083</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-4.038854198072228</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.159196665399375</v>
+        <v>1.107965727158192</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1870771310623538</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.898217241982918</v>
+        <v>2.836110109338243</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.714300539332722</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.026680381377224</v>
+        <v>-3.948569739694335</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.198336670738819</v>
+        <v>1.13451621914124</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1870771310623538</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88865395061481</v>
+        <v>2.826546817970134</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.634074812643843</v>
+        <v>2.539010104373109</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.057673540705929</v>
+        <v>-3.979562899023041</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.010648972047724</v>
+        <v>0.9468285204501452</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1870771310623538</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.713363515655197</v>
+        <v>2.651256383010521</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.638642044635631</v>
+        <v>2.543577336364896</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.88219928091346</v>
+        <v>-3.804088639230571</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.085405907956499</v>
+        <v>1.021585456358921</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1870771310623538</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717930747646984</v>
+        <v>2.655823615002309</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.614384073396838</v>
+        <v>2.519319365126103</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.993135533554709</v>
+        <v>-3.91502489187182</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.016773435661207</v>
+        <v>0.9529529840636282</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.1870771310623538</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.693672776408191</v>
+        <v>2.631565643763516</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.617515458616743</v>
+        <v>2.522450750346009</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.959471988082427</v>
+        <v>-3.881361346399538</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.033370239070025</v>
+        <v>0.9695497874724466</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.2207406765346356</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717002288911466</v>
+        <v>2.65489515626679</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.627687845048876</v>
+        <v>2.532623136778141</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.899619368878704</v>
+        <v>-3.821508727195815</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.067483673183647</v>
+        <v>1.003663221586068</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.2207406765346356</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727174675343599</v>
+        <v>2.665067542698923</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.622634115622736</v>
+        <v>2.527569407352002</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.813375905852326</v>
+        <v>-3.735265264169437</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.096927328968058</v>
+        <v>1.033106877370479</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.2207406765346356</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722120945917459</v>
+        <v>2.660013813272783</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.614409891067262</v>
+        <v>2.519345182796527</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.858682725251306</v>
+        <v>-3.780572083568417</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.070580376652992</v>
+        <v>1.006759925055413</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.1799305135254048</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689410623556446</v>
+        <v>2.62730349091177</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.614961764100363</v>
+        <v>2.519897055829629</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.887715829953608</v>
+        <v>-3.809605188270719</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.059519007805173</v>
+        <v>0.995698556207594</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.1799305135254048</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689962496589547</v>
+        <v>2.627855363944872</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.544234455991729</v>
+        <v>2.449169747720994</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.794905348502748</v>
+        <v>-3.71679470681986</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.025915892276882</v>
+        <v>0.9620954406793032</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.217811702266166</v>
+        <v>0.2727409949762642</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674921477351428</v>
+        <v>2.612814344706753</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.54610793191633</v>
+        <v>2.451043223645595</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.839294817832176</v>
+        <v>-3.761184176149287</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.010033580469712</v>
+        <v>0.9462131288721332</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1734222329367384</v>
+        <v>0.2283515256468365</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650161271678373</v>
+        <v>2.588054139033698</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.541183640428053</v>
+        <v>2.446118932157318</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.726623599595926</v>
+        <v>-3.648512957913037</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.050177776275935</v>
+        <v>0.9863573246783561</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.3410227438830867</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.712839711131846</v>
+        <v>2.650732578487171</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.54667493625872</v>
+        <v>2.451610227987985</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.614246598413253</v>
+        <v>-3.536135956730365</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.100619872579671</v>
+        <v>1.036799420982092</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.3410227438830867</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.718331006962513</v>
+        <v>2.656223874317838</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.558172138027259</v>
+        <v>2.463107429756525</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.642026996314606</v>
+        <v>-3.563916354631718</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.101004915187669</v>
+        <v>1.03718446359009</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2583130532716355</v>
+        <v>0.3132423459817337</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71315996999024</v>
+        <v>2.651052837345565</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.396527858027912</v>
+        <v>2.301463149757178</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.725028277339885</v>
+        <v>-3.646917635656997</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9061601227782108</v>
+        <v>0.8423396711806319</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.2946714614545599</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.540373159274589</v>
+        <v>2.478266026629914</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.516677518747118</v>
+        <v>2.421612810476383</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.833642355783216</v>
+        <v>-3.755531714100328</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9828641521200838</v>
+        <v>0.9190437005225052</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.2946714614545599</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.660522819993795</v>
+        <v>2.59841568734912</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.531190544849441</v>
+        <v>2.436125836578706</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.798233317535074</v>
+        <v>-3.720122675852185</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.011540793521664</v>
+        <v>0.9477203419240852</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.2946714614545599</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.675035846096118</v>
+        <v>2.612928713451443</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.528609986191809</v>
+        <v>2.433545277921075</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.759849654976922</v>
+        <v>-3.681739013294034</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.024313699887293</v>
+        <v>0.9604932482897144</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.3330551240127111</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.695485484973378</v>
+        <v>2.633378352328702</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.525339015037112</v>
+        <v>2.430274306766377</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.582733324941756</v>
+        <v>-3.504622683258868</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.091889260746662</v>
+        <v>1.028068809149083</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.3330551240127111</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.69221451381868</v>
+        <v>2.630107381174005</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.526022406799025</v>
+        <v>2.430957698528291</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.627825569775302</v>
+        <v>-3.549714928092413</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.074535754575157</v>
+        <v>1.010715302977578</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2162297881332231</v>
+        <v>0.2711590808433213</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.655760279678959</v>
+        <v>2.593653147034284</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.519809382105439</v>
+        <v>2.424744673834705</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.448450148536534</v>
+        <v>-3.370339506853646</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.140072898377078</v>
+        <v>1.076252446779499</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3730065463039418</v>
+        <v>0.42793583901404</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.743613309887805</v>
+        <v>2.681506177243129</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.500616837437029</v>
+        <v>2.405552129166295</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.493464362057141</v>
+        <v>-3.415353720374252</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.102874668300426</v>
+        <v>1.039054216702847</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3426576509893372</v>
+        <v>0.3975869436994354</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.706211428030632</v>
+        <v>2.644104295385956</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.506308399775975</v>
+        <v>2.41124369150524</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.760468872329576</v>
+        <v>-3.682358230646687</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.001764426530397</v>
+        <v>0.9379439749328182</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1482946129463886</v>
+        <v>0.2032239056564868</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.595285167543808</v>
+        <v>2.533178034899133</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.505512321672476</v>
+        <v>2.410447613401742</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.861666653766749</v>
+        <v>-3.78355601208386</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9604892358520294</v>
+        <v>0.8966687842544505</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.1348150921111676</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553443801313118</v>
+        <v>2.491336668668443</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.503112283226793</v>
+        <v>2.408047574956059</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.855155687152436</v>
+        <v>-3.777045045469547</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9606935840520712</v>
+        <v>0.8968731324544923</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.1348150921111676</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551043762867435</v>
+        <v>2.48893663022276</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.499637002435038</v>
+        <v>2.404572294164304</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.836117559445139</v>
+        <v>-3.75800691776225</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9648335543432349</v>
+        <v>0.9010131027456563</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.07663148077997306</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.512658315276963</v>
+        <v>2.450551182632287</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.677218871373718</v>
+        <v>2.582154163102984</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.867244190595757</v>
+        <v>-3.789133548912868</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.129964770821668</v>
+        <v>1.06614431922409</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.07663148077997306</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.690240184215644</v>
+        <v>2.628133051570968</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.678052200359852</v>
+        <v>2.582987492089118</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.881110951929674</v>
+        <v>-3.803000310246786</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.125251395274235</v>
+        <v>1.061430943676656</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.03877356404615012</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668358763161483</v>
+        <v>2.606251630516808</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.684060730756778</v>
+        <v>2.588996022486044</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.836306780389744</v>
+        <v>-3.758196138706856</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.149181594287133</v>
+        <v>1.085361142689554</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.03877356404615012</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674367293558409</v>
+        <v>2.612260160913734</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.7632133785488</v>
+        <v>2.668148670278065</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.688563810154742</v>
+        <v>-3.610453168471853</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.287431430173156</v>
+        <v>1.223610978575577</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.2065809212810333</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.854204355691361</v>
+        <v>2.792097223046686</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.766007000080281</v>
+        <v>2.670942291809546</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.790578492685963</v>
+        <v>-3.712467851003074</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.249419178692148</v>
+        <v>1.185598727094569</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.2065809212810333</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.856997977222842</v>
+        <v>2.794890844578167</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.766669348471939</v>
+        <v>2.671604640201205</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.784425786633179</v>
+        <v>-3.70631514495029</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.25254260950492</v>
+        <v>1.188722157907341</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1578043346237194</v>
+        <v>0.2127336273338176</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.861351949246171</v>
+        <v>2.799244816601496</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.765749825212049</v>
+        <v>2.670685116941315</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.80123508478368</v>
+        <v>-3.723124443100791</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.24489936698483</v>
+        <v>1.181078915387251</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.1959243291833159</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85034684709598</v>
+        <v>2.788239714451305</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.83208537900887</v>
+        <v>2.737020670738136</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.738937086007558</v>
+        <v>-3.66082644432467</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.3361541202921</v>
+        <v>1.272333668694521</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.1959243291833159</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.916682400892801</v>
+        <v>2.854575268248126</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.634377380722997</v>
+        <v>2.539312672452263</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.5371468883424</v>
+        <v>-3.459036246659512</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.21916220107229</v>
+        <v>1.155341749474711</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3390132286423722</v>
+        <v>0.3939425213524703</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.837785317908421</v>
+        <v>2.775678185263745</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.704667613045173</v>
+        <v>2.609602904774438</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.463768791253664</v>
+        <v>-3.385658149570775</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.31880367222996</v>
+        <v>1.254983220632381</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4123913257311087</v>
+        <v>0.4673206184412069</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.952102408483838</v>
+        <v>2.889995275839162</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.719295349161216</v>
+        <v>2.624230640890482</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.561509335878638</v>
+        <v>-3.48339869419575</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.294335190496014</v>
+        <v>1.230514738898435</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3965020475981285</v>
+        <v>0.4514313403082267</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.957196577720094</v>
+        <v>2.895089445075418</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.717831329985888</v>
+        <v>2.622766621715154</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.737847096001568</v>
+        <v>-3.659736454318679</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.222336067271514</v>
+        <v>1.158515615673935</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.2750935801852973</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.849929902471008</v>
+        <v>2.787822769826332</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.716322948025816</v>
+        <v>2.621258239755082</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.661425049569641</v>
+        <v>-3.583314407886752</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.251396503884213</v>
+        <v>1.187576052286634</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.2750935801852973</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.848421520510936</v>
+        <v>2.786314387866261</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.716185815461253</v>
+        <v>2.621121107190518</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.617051917931072</v>
+        <v>-3.538941276248183</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.269008623975076</v>
+        <v>1.205188172377498</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.3194667118238659</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.874908266929514</v>
+        <v>2.812801134284838</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.710579609599843</v>
+        <v>2.615514901329109</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.494217697043905</v>
+        <v>-3.416107055361016</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.312536106468534</v>
+        <v>1.248715654870955</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.3194667118238659</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.869302061068104</v>
+        <v>2.807194928423429</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.716961366627648</v>
+        <v>2.621896658356913</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.446561966482849</v>
+        <v>-3.368451324799961</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.337980155720761</v>
+        <v>1.274159704123182</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3121931496748234</v>
+        <v>0.3671224423849215</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.904277256432542</v>
+        <v>2.842170123787866</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.721853740002373</v>
+        <v>2.626789031731638</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.346043807984095</v>
+        <v>-3.267933166301206</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.383079792494987</v>
+        <v>1.319259340897409</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4127113081735779</v>
+        <v>0.4676406008836761</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.969480524906519</v>
+        <v>2.907373392261844</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.708608412478245</v>
+        <v>2.61354370420751</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.406710398386484</v>
+        <v>-3.328599756703595</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.345567828809904</v>
+        <v>1.281747377212325</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3310129914550443</v>
+        <v>0.3859422841651424</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.907216207351272</v>
+        <v>2.845109074706596</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.712706115088873</v>
+        <v>2.617641406818139</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.361871996778086</v>
+        <v>-3.283761355095197</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.367600892063892</v>
+        <v>1.303780440466313</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3355564243999137</v>
+        <v>0.3904857171100119</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.914039969728822</v>
+        <v>2.851932837084147</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.716867054719951</v>
+        <v>2.621802346449217</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.462630632535084</v>
+        <v>-3.384519990852195</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.33145837739217</v>
+        <v>1.267637925794592</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2467308556729083</v>
+        <v>0.3016601483830065</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.864905568123697</v>
+        <v>2.802798435479021</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.722746657247789</v>
+        <v>2.627681948977054</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.418427795449184</v>
+        <v>-3.340317153766295</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.355019114754368</v>
+        <v>1.291198663156789</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.2909336927588088</v>
+        <v>0.3458629854689069</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.897306872903074</v>
+        <v>2.835199740258399</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.721156657717036</v>
+        <v>2.626091949446302</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.455406823112627</v>
+        <v>-3.377296181429738</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.338637504158238</v>
+        <v>1.274817052560659</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3828368872602375</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.91790121444712</v>
+        <v>2.855794081802444</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.772404422900076</v>
+        <v>2.677339714629341</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.297115405573355</v>
+        <v>-3.219004763890466</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.453201836356987</v>
+        <v>1.389381384759408</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3828368872602375</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.96914897963016</v>
+        <v>2.907041846985484</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.770845127494329</v>
+        <v>2.675780419223595</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.257184732395464</v>
+        <v>-3.179074090712576</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.467614810222396</v>
+        <v>1.403794358624817</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.3678382677280296</v>
+        <v>0.4227675604381278</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.991548088131147</v>
+        <v>2.929440955486471</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.765793355732599</v>
+        <v>2.670728647461865</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.206152639672936</v>
+        <v>-3.128041997990048</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.482975875549677</v>
+        <v>1.419155423952098</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4188703604505576</v>
+        <v>0.4737996531606558</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.017115572002933</v>
+        <v>2.955008439358258</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.782980759825304</v>
+        <v>2.687916051554569</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.140928458545731</v>
+        <v>-3.062817816862842</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.526252952093264</v>
+        <v>1.462432500495685</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.4840945415777632</v>
+        <v>0.5390238342878614</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.073437484771962</v>
+        <v>3.011330352127287</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.778941732124584</v>
+        <v>2.68387702385385</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.103501438474597</v>
+        <v>-3.025390796791708</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.537184732420998</v>
+        <v>1.473364280823419</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.4893460796069449</v>
+        <v>0.544275372317043</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.072549379888752</v>
+        <v>3.010442247244076</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.780198524455824</v>
+        <v>2.68513381618509</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.123613094509305</v>
+        <v>-3.045502452826417</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.530396862338355</v>
+        <v>1.466576410740776</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5003734246043641</v>
+        <v>0.5553027173144622</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.080422579218443</v>
+        <v>3.018315446573768</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.940756295477035</v>
+        <v>2.845691587206301</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.069868280082101</v>
+        <v>-2.991757638399212</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.712452559130448</v>
+        <v>1.648632107532869</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.510436734044826</v>
+        <v>0.5653660267549242</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.247018335903931</v>
+        <v>3.184911203259256</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.060869204694852</v>
+        <v>2.965804496424118</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.046076711475958</v>
+        <v>-2.96796606979307</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.842082095790722</v>
+        <v>1.778261644193143</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5342283026509683</v>
+        <v>0.5891575953610665</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.381406186285434</v>
+        <v>3.319299053640759</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.052577180708711</v>
+        <v>2.957512472437977</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.01999262721215</v>
+        <v>-2.941881985529262</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.844223705510104</v>
+        <v>1.780403253912525</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5342283026509683</v>
+        <v>0.5891575953610665</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.373114162299293</v>
+        <v>3.311007029654617</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.050770376292491</v>
+        <v>2.955705668021757</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.941861446363204</v>
+        <v>-2.863750804680315</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.873669373433462</v>
+        <v>1.809848921835884</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6084051135346529</v>
+        <v>0.663334406244751</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.415813444413283</v>
+        <v>3.353706311768608</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.068324782019282</v>
+        <v>2.973260073748548</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.932968984969921</v>
+        <v>-2.854858343287032</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.894780763717567</v>
+        <v>1.830960312119988</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6084051135346529</v>
+        <v>0.663334406244751</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.433367850140074</v>
+        <v>3.371260717495399</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.060179829423866</v>
+        <v>2.965115121153132</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.101445101939798</v>
+        <v>-3.02333446025691</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.8192453643342</v>
+        <v>1.755424912736621</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5804572778180721</v>
+        <v>0.6353865705281703</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.40845419611471</v>
+        <v>3.346347063470034</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.041449526611728</v>
+        <v>2.946384818340994</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.403645573078215</v>
+        <v>-2.325534931395326</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.079634873066695</v>
+        <v>2.015814421469116</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5101092184476614</v>
+        <v>0.5650385111577596</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.347515057680325</v>
+        <v>3.28540792503565</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.032113549108633</v>
+        <v>2.937048840837898</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.380924469395063</v>
+        <v>-2.302813827712174</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.07938733703686</v>
+        <v>2.015566885439282</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5101092184476614</v>
+        <v>0.5650385111577596</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.33817908017723</v>
+        <v>3.276071947532554</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.191019674959802</v>
+        <v>3.095954966689067</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.379199426105019</v>
+        <v>-2.30108878442213</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.238983480204047</v>
+        <v>2.175163028606468</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5118342617377052</v>
+        <v>0.5667635544478034</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.498120232002425</v>
+        <v>3.43601309935775</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.228097497453448</v>
+        <v>3.133032789182714</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.533980432883274</v>
+        <v>-2.455869791200385</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.214148899986391</v>
+        <v>2.150328448388813</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.4784665876832291</v>
+        <v>0.5333958803933272</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.515177450063386</v>
+        <v>3.45307031741871</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.224772853442993</v>
+        <v>3.129708145172259</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.482545099498614</v>
+        <v>-2.404434457815726</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.2313983893298</v>
+        <v>2.167577937732222</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5299019210678888</v>
+        <v>0.5848312137779869</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.542714006083727</v>
+        <v>3.480606873439052</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.234779007087735</v>
+        <v>3.139714298817001</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.455593875172126</v>
+        <v>-2.377483233489238</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.252185032705137</v>
+        <v>2.188364581107558</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.544782267095608</v>
+        <v>0.599711559805706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.5616483673451</v>
+        <v>3.499541234700424</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.418882139232695</v>
+        <v>3.32381743096196</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.591546883228443</v>
+        <v>-2.513436241545554</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.38190696162757</v>
+        <v>2.318086510029992</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.544782267095608</v>
+        <v>0.599711559805706</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.74575149949006</v>
+        <v>3.683644366845384</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.410998834135688</v>
+        <v>3.315934125864954</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.613955001033315</v>
+        <v>-2.535844359350426</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.365060409408615</v>
+        <v>2.301239957811036</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.544782267095608</v>
+        <v>0.599711559805706</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.737868194393053</v>
+        <v>3.675761061748378</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.413052833685325</v>
+        <v>3.317988125414591</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.761960768512714</v>
+        <v>-2.683850126829825</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.307912101966492</v>
+        <v>2.244091650368913</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4580552582320665</v>
+        <v>0.5129845509421646</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.687885988624565</v>
+        <v>3.62577885597989</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.469306551407172</v>
+        <v>3.374241843136438</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.771401694401244</v>
+        <v>-2.693291052718355</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.360389449332928</v>
+        <v>2.296568997735349</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.5804823757754579</v>
+        <v>0.635411668485556</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.817595976872447</v>
+        <v>3.755488844227772</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.472197645952473</v>
+        <v>3.377132937681739</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.770114930861688</v>
+        <v>-2.692004289178799</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.363795249294051</v>
+        <v>2.299974797696472</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5817691393150145</v>
+        <v>0.6366984320251126</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.821259129541482</v>
+        <v>3.759151996896807</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.470309458846248</v>
+        <v>3.375244750575514</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.771671984850979</v>
+        <v>-2.69356134316809</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.361284240592109</v>
+        <v>2.297463788994531</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5817691393150145</v>
+        <v>0.6366984320251126</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.819370942435258</v>
+        <v>3.757263809790582</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.465129688449111</v>
+        <v>3.370064980178376</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.778943870374444</v>
+        <v>-2.700833228691555</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.353195715985586</v>
+        <v>2.289375264388007</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5744972537915498</v>
+        <v>0.6294265465016478</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.809828040724041</v>
+        <v>3.747720908079365</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.463563698659263</v>
+        <v>3.368498990388529</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.777102851316192</v>
+        <v>-2.698992209633304</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.352366133819039</v>
+        <v>2.28854568222146</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6306947731731162</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.809022986937074</v>
+        <v>3.746915854292399</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.476637105525182</v>
+        <v>3.381572397254447</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.784011556815873</v>
+        <v>-2.705900915132984</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.362676058485085</v>
+        <v>2.298855606887506</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6306947731731162</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.822096393802993</v>
+        <v>3.759989261158317</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.476637105525182</v>
+        <v>3.381572397254447</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.785573199630733</v>
+        <v>-2.707462557947844</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.362051401359142</v>
+        <v>2.298230949761563</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5757654804630182</v>
+        <v>0.6306947731731162</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.822096393802993</v>
+        <v>3.759989261158317</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.475161146652184</v>
+        <v>3.380096438381449</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.813473986740206</v>
+        <v>-2.735363345057317</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.349415127642354</v>
+        <v>2.285594676044775</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5411685563200834</v>
+        <v>0.5960978490301814</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.799862280444234</v>
+        <v>3.737755147799558</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.471925590629382</v>
+        <v>3.376860882358648</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.81650698425288</v>
+        <v>-2.738396342569991</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.344966372614484</v>
+        <v>2.281145921016904</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5381355588074095</v>
+        <v>0.5930648515175074</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.794806925913829</v>
+        <v>3.732699793269153</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.538631550219886</v>
+        <v>3.443566841949152</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.836568305529386</v>
+        <v>-2.758457663846498</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.403647803694384</v>
+        <v>2.339827352096806</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5180742375309024</v>
+        <v>0.5730035302410004</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.849476092738428</v>
+        <v>3.787368960093752</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.678943269221733</v>
+        <v>3.583878560950999</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.09328912352421</v>
+        <v>-3.015178481841322</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.441271195498302</v>
+        <v>2.377450743900723</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4645889560971855</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.924739067253986</v>
+        <v>3.86263193460931</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.747923538367373</v>
+        <v>3.652858830096639</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.247275541300351</v>
+        <v>-3.169164899617462</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.448656897533485</v>
+        <v>2.384836445935907</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4645889560971855</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.993719336399626</v>
+        <v>3.93161220375495</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,45 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.777059612218702</v>
+        <v>3.619937176808533</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.733974740487494</v>
+        <v>3.63891003221676</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.196753637472685</v>
+        <v>-3.118642995789796</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.454916861184673</v>
+        <v>2.391096409587094</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4096596633870876</v>
+        <v>0.4645889560971855</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.979770538519746</v>
+        <v>3.917663405875071</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="2" t="n">
+        <v>45481</v>
+      </c>
+      <c r="B2019" t="n">
+        <v>3.785045226119627</v>
+      </c>
+      <c r="C2019" t="n">
+        <v>3.787650820640552</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>-3.118642995789796</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>2.391096409587094</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>0.4645889560971855</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>3.78071461762692</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.7%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-473.4%</t>
+          <t>-495.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-137.1%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-111.5%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-177.5%</t>
+          <t>-193.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.872572683826192</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.903604769460788</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1107743517281299</v>
+        <v>0.1620052899693145</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.981686558855107</v>
+        <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.283560748513128</v>
+        <v>2.345667881157804</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.863858697572714</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.8506352472068</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.123248174376247</v>
+        <v>0.1744791126174317</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9287170366011182</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.306628475612044</v>
+        <v>2.36873560825672</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.856898085477621</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.807086840436109</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.13370692498943</v>
+        <v>0.1849378632306147</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9287170366011182</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.299667863516951</v>
+        <v>2.361774996161627</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.871360439858764</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.564938446982251</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2450286367521164</v>
+        <v>0.296259574993301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9287170366011182</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.314130217898094</v>
+        <v>2.37623735054277</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.865892560317959</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.456679309859729</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2828644120603201</v>
+        <v>0.3340953503015047</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9287170366011182</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.308662338357289</v>
+        <v>2.370769471001965</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.863390654328536</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.333388175042598</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3296789599977492</v>
+        <v>0.3809098982389338</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8054259017839877</v>
+        <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.380135113258144</v>
+        <v>2.44224224590282</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.871091632565862</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.312238976139155</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3458396177964524</v>
+        <v>0.3970705560376366</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7842767028805443</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.400525610837535</v>
+        <v>2.462632743482211</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.866872340912912</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.068473534155711</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4391265029368809</v>
+        <v>0.4903574411780647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7842767028805443</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.396306319184586</v>
+        <v>2.458413451829262</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.868996654832928</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.966710713878416</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4819559449678148</v>
+        <v>0.533186883208999</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7710576344881156</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.40636207414006</v>
+        <v>2.468469206784735</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.861738729816631</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.716860319929341</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5746381775311469</v>
+        <v>0.6258691157723311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7710576344881156</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.399104149123762</v>
+        <v>2.461211281768437</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.865337853337279</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.540968227461908</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6485941380387685</v>
+        <v>0.6998250762799523</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7710576344881156</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.40270327264441</v>
+        <v>2.464810405289086</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.878665359391833</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.369521764439445</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.730500229302308</v>
+        <v>0.7817311675434917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5996111714656525</v>
+        <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.518898656512442</v>
+        <v>2.581005789157117</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.87768583700813</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.295232198701106</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7592365332139406</v>
+        <v>0.8104674714551243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5253216057273131</v>
+        <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.562492873571742</v>
+        <v>2.624600006216418</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.882380638062447</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.231596456467171</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7893856311618315</v>
+        <v>0.8406165694030152</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.4616858634933786</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.60536911996642</v>
+        <v>2.667476252611096</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.863574896846243</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.120169697141251</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8151505936759951</v>
+        <v>0.8663815319171788</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.4616858634933786</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.586563378750216</v>
+        <v>2.648670511394891</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.86531797347112</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.879739200336391</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9130658690228166</v>
+        <v>0.9642968072640004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2212553666885183</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.73256475345801</v>
+        <v>2.794671886102685</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.86924728730594</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.807496632165196</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9458922101261147</v>
+        <v>0.9971231483672984</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2212553666885183</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.73649406729283</v>
+        <v>2.798601199937505</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.86992587122328</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.754498309883808</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9677701229560098</v>
+        <v>1.019001061197194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1659191076865795</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.770374406611333</v>
+        <v>2.832481539256008</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.866923942443274</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.645693424404081</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.008290148367894</v>
+        <v>1.059521086609078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1659191076865795</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.767372477831326</v>
+        <v>2.829479610476002</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.868502979453888</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.425672626367071</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.097877504593312</v>
+        <v>1.149108442834496</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.02469926261859923</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.853683421882729</v>
+        <v>2.915790554527404</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.884397162255711</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.292804937303793</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.166918763020447</v>
+        <v>1.218149701261631</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.02469926261859923</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.869577604684552</v>
+        <v>2.931684737329228</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.885543006696013</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.172631853939294</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.216133840806548</v>
+        <v>1.267364779047732</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.09547382074589972</v>
+        <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.942827299143553</v>
+        <v>3.004934431788229</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.895631109257453</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.027959708839557</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.284090801407883</v>
+        <v>1.335321739649067</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.2401459658456371</v>
+        <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.039718688764836</v>
+        <v>3.101825821409511</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.881668600658879</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.087834536197249</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.246178361866232</v>
+        <v>1.297409300107416</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.180271138487945</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.989831283751646</v>
+        <v>3.051938416396322</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.896957769893088</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.968014305286412</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.309395623464775</v>
+        <v>1.360626561705959</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.180271138487945</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.005120452985855</v>
+        <v>3.06722758563053</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.804601969215529</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.970484011748218</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.216051940202495</v>
+        <v>1.267282878443678</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1778014320261389</v>
+        <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.911282828431212</v>
+        <v>2.973389961075888</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.72386383070083</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.038854198072228</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.107965727158192</v>
+        <v>1.159196665399375</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1870771310623538</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.836110109338243</v>
+        <v>2.898217241982918</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.714300539332722</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.948569739694335</v>
+        <v>-4.162226675993152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.13451621914124</v>
+        <v>1.144118152892448</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1870771310623538</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.826546817970134</v>
+        <v>2.88865395061481</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.539010104373109</v>
+        <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.979562899023041</v>
+        <v>-4.193219835321857</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9468285204501452</v>
+        <v>0.9564304542013529</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1870771310623538</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.651256383010521</v>
+        <v>2.713363515655197</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.543577336364896</v>
+        <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.804088639230571</v>
+        <v>-4.017745575529387</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.021585456358921</v>
+        <v>1.031187390110128</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1870771310623538</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.655823615002309</v>
+        <v>2.717930747646984</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.519319365126103</v>
+        <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.91502489187182</v>
+        <v>-4.128681828170636</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9529529840636282</v>
+        <v>0.962554917814836</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1870771310623538</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.631565643763516</v>
+        <v>2.693672776408191</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.522450750346009</v>
+        <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.881361346399538</v>
+        <v>-4.095018282698354</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9695497874724466</v>
+        <v>0.9791517212236545</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.2207406765346356</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.65489515626679</v>
+        <v>2.717002288911466</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.532623136778141</v>
+        <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.821508727195815</v>
+        <v>-4.035165663494631</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.003663221586068</v>
+        <v>1.013265155337276</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.2207406765346356</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.665067542698923</v>
+        <v>2.727174675343599</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.527569407352002</v>
+        <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.735265264169437</v>
+        <v>-3.948922200468253</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.033106877370479</v>
+        <v>1.042708811121687</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.2207406765346356</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.660013813272783</v>
+        <v>2.722120945917459</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.519345182796527</v>
+        <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.780572083568417</v>
+        <v>-3.994229019867233</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.006759925055413</v>
+        <v>1.016361858806621</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1799305135254048</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.62730349091177</v>
+        <v>2.689410623556446</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.519897055829629</v>
+        <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.809605188270719</v>
+        <v>-4.023262124569534</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.995698556207594</v>
+        <v>1.005300489958802</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1799305135254048</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.627855363944872</v>
+        <v>2.689962496589547</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.449169747720994</v>
+        <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.71679470681986</v>
+        <v>-3.930451643118675</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9620954406793032</v>
+        <v>0.9716973744305115</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.2727409949762642</v>
+        <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.612814344706753</v>
+        <v>2.674921477351428</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.451043223645595</v>
+        <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.761184176149287</v>
+        <v>-3.974841112448102</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9462131288721332</v>
+        <v>0.9558150626233413</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2283515256468365</v>
+        <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.588054139033698</v>
+        <v>2.650161271678373</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.446118932157318</v>
+        <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.648512957913037</v>
+        <v>-3.862169894211852</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9863573246783561</v>
+        <v>0.9959592584295645</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3410227438830867</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.650732578487171</v>
+        <v>2.712839711131846</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.451610227987985</v>
+        <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.536135956730365</v>
+        <v>-3.74979289302918</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.036799420982092</v>
+        <v>1.046401354733301</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3410227438830867</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.656223874317838</v>
+        <v>2.718331006962513</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.463107429756525</v>
+        <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.563916354631718</v>
+        <v>-3.777573290930533</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.03718446359009</v>
+        <v>1.046786397341299</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3132423459817337</v>
+        <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.651052837345565</v>
+        <v>2.71315996999024</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.301463149757178</v>
+        <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.646917635656997</v>
+        <v>-3.860574571955812</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8423396711806319</v>
+        <v>0.8519416049318402</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2946714614545599</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.478266026629914</v>
+        <v>2.540373159274589</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.421612810476383</v>
+        <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.755531714100328</v>
+        <v>-3.969188650399143</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9190437005225052</v>
+        <v>0.9286456342737133</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2946714614545599</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.59841568734912</v>
+        <v>2.660522819993795</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.436125836578706</v>
+        <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.720122675852185</v>
+        <v>-3.933779612151</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9477203419240852</v>
+        <v>0.9573222756752935</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2946714614545599</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.612928713451443</v>
+        <v>2.675035846096118</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.433545277921075</v>
+        <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.681739013294034</v>
+        <v>-3.895395949592849</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9604932482897144</v>
+        <v>0.9700951820409225</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3330551240127111</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.633378352328702</v>
+        <v>2.695485484973378</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.430274306766377</v>
+        <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.504622683258868</v>
+        <v>-3.718279619557683</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.028068809149083</v>
+        <v>1.037670742900291</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3330551240127111</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.630107381174005</v>
+        <v>2.69221451381868</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.430957698528291</v>
+        <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.549714928092413</v>
+        <v>-3.763371864391228</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.010715302977578</v>
+        <v>1.020317236728786</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2711590808433213</v>
+        <v>0.2162297881332231</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.593653147034284</v>
+        <v>2.655760279678959</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.424744673834705</v>
+        <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.370339506853646</v>
+        <v>-3.58399644315246</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.076252446779499</v>
+        <v>1.085854380530708</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.42793583901404</v>
+        <v>0.3730065463039418</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.681506177243129</v>
+        <v>2.743613309887805</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.405552129166295</v>
+        <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.415353720374252</v>
+        <v>-3.629010656673067</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.039054216702847</v>
+        <v>1.048656150454055</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3975869436994354</v>
+        <v>0.3426576509893372</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.644104295385956</v>
+        <v>2.706211428030632</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.41124369150524</v>
+        <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.682358230646687</v>
+        <v>-3.896015166945502</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9379439749328182</v>
+        <v>0.9475459086840265</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2032239056564868</v>
+        <v>0.1482946129463886</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.533178034899133</v>
+        <v>2.595285167543808</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.410447613401742</v>
+        <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.78355601208386</v>
+        <v>-3.997212948382675</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8966687842544505</v>
+        <v>0.9062707180056591</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1348150921111676</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.491336668668443</v>
+        <v>2.553443801313118</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.408047574956059</v>
+        <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.777045045469547</v>
+        <v>-3.990701981768362</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8968731324544923</v>
+        <v>0.9064750662057008</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1348150921111676</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.48893663022276</v>
+        <v>2.551043762867435</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.404572294164304</v>
+        <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.75800691776225</v>
+        <v>-3.971663854061065</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9010131027456563</v>
+        <v>0.9106150364968646</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.07663148077997306</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.450551182632287</v>
+        <v>2.512658315276963</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.582154163102984</v>
+        <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.789133548912868</v>
+        <v>-4.002790485211683</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.06614431922409</v>
+        <v>1.075746252975298</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.07663148077997306</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.628133051570968</v>
+        <v>2.690240184215644</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.582987492089118</v>
+        <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.803000310246786</v>
+        <v>-4.0166572465456</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.061430943676656</v>
+        <v>1.071032877427865</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.03877356404615012</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.606251630516808</v>
+        <v>2.668358763161483</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.588996022486044</v>
+        <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.758196138706856</v>
+        <v>-3.97185307500567</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.085361142689554</v>
+        <v>1.094963076440763</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.03877356404615012</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.612260160913734</v>
+        <v>2.674367293558409</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.668148670278065</v>
+        <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.610453168471853</v>
+        <v>-3.824110104770668</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.223610978575577</v>
+        <v>1.233212912326785</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2065809212810333</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.792097223046686</v>
+        <v>2.854204355691361</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.670942291809546</v>
+        <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.712467851003074</v>
+        <v>-3.926124787301889</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.185598727094569</v>
+        <v>1.195200660845778</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2065809212810333</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.794890844578167</v>
+        <v>2.856997977222842</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.671604640201205</v>
+        <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.70631514495029</v>
+        <v>-3.919972081249105</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.188722157907341</v>
+        <v>1.19832409165855</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2127336273338176</v>
+        <v>0.1578043346237194</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.799244816601496</v>
+        <v>2.861351949246171</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.670685116941315</v>
+        <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.723124443100791</v>
+        <v>-3.936781379399606</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.181078915387251</v>
+        <v>1.19068084913846</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1959243291833159</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.788239714451305</v>
+        <v>2.85034684709598</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.737020670738136</v>
+        <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.66082644432467</v>
+        <v>-3.874483380623484</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.272333668694521</v>
+        <v>1.281935602445729</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1959243291833159</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.854575268248126</v>
+        <v>2.916682400892801</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.539312672452263</v>
+        <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.459036246659512</v>
+        <v>-3.681145631965912</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.155341749474711</v>
+        <v>1.161562703622885</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3939425213524703</v>
+        <v>0.2364178041160324</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.775678185263745</v>
+        <v>2.776228063192617</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.609602904774438</v>
+        <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.385658149570775</v>
+        <v>-3.607767534877176</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.254983220632381</v>
+        <v>1.261204174780555</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4673206184412069</v>
+        <v>0.309795901204769</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.889995275839162</v>
+        <v>2.890545153768034</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.624230640890482</v>
+        <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.48339869419575</v>
+        <v>-3.70550807950215</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.230514738898435</v>
+        <v>1.236735693046609</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4514313403082267</v>
+        <v>0.2939066230717888</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.895089445075418</v>
+        <v>2.89563932300429</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.622766621715154</v>
+        <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.659736454318679</v>
+        <v>-3.881845839625079</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.158515615673935</v>
+        <v>1.164736569822109</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2750935801852973</v>
+        <v>0.1175688629488594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.787822769826332</v>
+        <v>2.788372647755204</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.621258239755082</v>
+        <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.583314407886752</v>
+        <v>-3.805423793193153</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.187576052286634</v>
+        <v>1.193797006434808</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2750935801852973</v>
+        <v>0.1175688629488594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.786314387866261</v>
+        <v>2.786864265795132</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.621121107190518</v>
+        <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.538941276248183</v>
+        <v>-3.761050661554584</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.205188172377498</v>
+        <v>1.211409126525672</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3194667118238659</v>
+        <v>0.161941994587428</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.812801134284838</v>
+        <v>2.81335101221371</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.615514901329109</v>
+        <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.416107055361016</v>
+        <v>-3.638216440667417</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.248715654870955</v>
+        <v>1.254936609019129</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3194667118238659</v>
+        <v>0.161941994587428</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.807194928423429</v>
+        <v>2.8077448063523</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.621896658356913</v>
+        <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.368451324799961</v>
+        <v>-3.590560710106361</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.274159704123182</v>
+        <v>1.280380658271356</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3671224423849215</v>
+        <v>0.2095977251484836</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.842170123787866</v>
+        <v>2.842720001716738</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.626789031731638</v>
+        <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.267933166301206</v>
+        <v>-3.490042551607607</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.319259340897409</v>
+        <v>1.325480295045583</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4676406008836761</v>
+        <v>0.3101158836472382</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.907373392261844</v>
+        <v>2.907923270190716</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61354370420751</v>
+        <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.328599756703595</v>
+        <v>-3.550709142009996</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.281747377212325</v>
+        <v>1.287968331360499</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3859422841651424</v>
+        <v>0.2284175669287045</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.845109074706596</v>
+        <v>2.845658952635468</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.617641406818139</v>
+        <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.283761355095197</v>
+        <v>-3.505870740401598</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.303780440466313</v>
+        <v>1.310001394614487</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3904857171100119</v>
+        <v>0.232960999873574</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.851932837084147</v>
+        <v>2.852482715013018</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.621802346449217</v>
+        <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.384519990852195</v>
+        <v>-3.606629376158596</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.267637925794592</v>
+        <v>1.273858879942766</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3016601483830065</v>
+        <v>0.1441354311465686</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.802798435479021</v>
+        <v>2.803348313407893</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.627681948977054</v>
+        <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.340317153766295</v>
+        <v>-3.562426539072696</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.291198663156789</v>
+        <v>1.297419617304963</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3458629854689069</v>
+        <v>0.188338268232469</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.835199740258399</v>
+        <v>2.83574961818727</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.626091949446302</v>
+        <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.377296181429738</v>
+        <v>-3.599405566736139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.274817052560659</v>
+        <v>1.281038006708833</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3828368872602375</v>
+        <v>0.2253121700237996</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.855794081802444</v>
+        <v>2.856343959731316</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.677339714629341</v>
+        <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.219004763890466</v>
+        <v>-3.441114149196867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.389381384759408</v>
+        <v>1.395602338907582</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3828368872602375</v>
+        <v>0.2253121700237996</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.907041846985484</v>
+        <v>2.907591724914356</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.675780419223595</v>
+        <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.179074090712576</v>
+        <v>-3.401183476018976</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.403794358624817</v>
+        <v>1.410015312772991</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.4227675604381278</v>
+        <v>0.2652428432016899</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.929440955486471</v>
+        <v>2.929990833415343</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.670728647461865</v>
+        <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.128041997990048</v>
+        <v>-3.350151383296448</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.419155423952098</v>
+        <v>1.425376378100272</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4737996531606558</v>
+        <v>0.3162749359242178</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.955008439358258</v>
+        <v>2.95555831728713</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.687916051554569</v>
+        <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.062817816862842</v>
+        <v>-3.284927202169243</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.462432500495685</v>
+        <v>1.468653454643859</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.5390238342878614</v>
+        <v>0.3814991170514235</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.011330352127287</v>
+        <v>3.011880230056158</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.68387702385385</v>
+        <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.025390796791708</v>
+        <v>-3.247500182098109</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.473364280823419</v>
+        <v>1.479585234971593</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.544275372317043</v>
+        <v>0.3867506550806051</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.010442247244076</v>
+        <v>3.010992125172947</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.68513381618509</v>
+        <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.045502452826417</v>
+        <v>-3.267611838132817</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.466576410740776</v>
+        <v>1.47279736488895</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.5553027173144622</v>
+        <v>0.3977780000780243</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.018315446573768</v>
+        <v>3.018865324502639</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.845691587206301</v>
+        <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.991757638399212</v>
+        <v>-3.213867023705613</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.648632107532869</v>
+        <v>1.654853061681043</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.5653660267549242</v>
+        <v>0.4078413095184863</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.184911203259256</v>
+        <v>3.185461081188127</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.965804496424118</v>
+        <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.96796606979307</v>
+        <v>-3.19007545509947</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.778261644193143</v>
+        <v>1.784482598341317</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5891575953610665</v>
+        <v>0.4316328781246286</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.319299053640759</v>
+        <v>3.31984893156963</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.957512472437977</v>
+        <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.941881985529262</v>
+        <v>-3.163991370835662</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.780403253912525</v>
+        <v>1.786624208060699</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5891575953610665</v>
+        <v>0.4316328781246286</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.311007029654617</v>
+        <v>3.311556907583489</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.955705668021757</v>
+        <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.863750804680315</v>
+        <v>-3.085860189986716</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.809848921835884</v>
+        <v>1.816069875984057</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.663334406244751</v>
+        <v>0.5058096890083131</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.353706311768608</v>
+        <v>3.354256189697479</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.973260073748548</v>
+        <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.854858343287032</v>
+        <v>-3.076967728593432</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.830960312119988</v>
+        <v>1.837181266268162</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.663334406244751</v>
+        <v>0.5058096890083131</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.371260717495399</v>
+        <v>3.37181059542427</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.965115121153132</v>
+        <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.02333446025691</v>
+        <v>-3.24544384556331</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.755424912736621</v>
+        <v>1.761645866884795</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.6353865705281703</v>
+        <v>0.4778618532917324</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.346347063470034</v>
+        <v>3.346896941398906</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.946384818340994</v>
+        <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.325534931395326</v>
+        <v>-2.547644316701727</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.015814421469116</v>
+        <v>2.02203537561729</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5650385111577596</v>
+        <v>0.4075137939213216</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.28540792503565</v>
+        <v>3.285957802964521</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.937048840837898</v>
+        <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.302813827712174</v>
+        <v>-2.524923213018575</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.015566885439282</v>
+        <v>2.021787839587455</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5650385111577596</v>
+        <v>0.4075137939213216</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.276071947532554</v>
+        <v>3.276621825461426</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.095954966689067</v>
+        <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.30108878442213</v>
+        <v>-2.523198169728531</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.175163028606468</v>
+        <v>2.181383982754642</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5667635544478034</v>
+        <v>0.4092388372113654</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.43601309935775</v>
+        <v>3.436562977286621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.133032789182714</v>
+        <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.455869791200385</v>
+        <v>-2.677979176506786</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.150328448388813</v>
+        <v>2.156549402536987</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.5333958803933272</v>
+        <v>0.3758711631568893</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.45307031741871</v>
+        <v>3.453620195347582</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.129708145172259</v>
+        <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.404434457815726</v>
+        <v>-2.626543843122126</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.167577937732222</v>
+        <v>2.173798891880396</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5848312137779869</v>
+        <v>0.427306496541549</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.480606873439052</v>
+        <v>3.481156751367923</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.139714298817001</v>
+        <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.377483233489238</v>
+        <v>-2.599592618795638</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.188364581107558</v>
+        <v>2.194585535255732</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.599711559805706</v>
+        <v>0.4421868425692681</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.499541234700424</v>
+        <v>3.500091112629296</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32381743096196</v>
+        <v>3.168530093129822</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.513436241545554</v>
+        <v>-2.735545626851954</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.318086510029992</v>
+        <v>2.073955418075293</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.599711559805706</v>
+        <v>0.4421868425692681</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.683644366845384</v>
+        <v>3.433842198671383</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.315934125864954</v>
+        <v>3.160646788032815</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.535844359350426</v>
+        <v>-2.757953744656827</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.301239957811036</v>
+        <v>2.057108865856337</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.599711559805706</v>
+        <v>0.4421868425692681</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.675761061748378</v>
+        <v>3.425958893574376</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.317988125414591</v>
+        <v>3.162700787582452</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.683850126829825</v>
+        <v>-2.905959512136226</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.244091650368913</v>
+        <v>1.999960558414215</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.5129845509421646</v>
+        <v>0.3554598337057266</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.62577885597989</v>
+        <v>3.375976687805888</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.374241843136438</v>
+        <v>3.218954505304299</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.693291052718355</v>
+        <v>-2.915400438024756</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.296568997735349</v>
+        <v>2.05243790578065</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.635411668485556</v>
+        <v>0.4778869512491181</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.755488844227772</v>
+        <v>3.505686676053771</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.377132937681739</v>
+        <v>3.2218455998496</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.692004289178799</v>
+        <v>-2.9141136744852</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.299974797696472</v>
+        <v>2.055843705741773</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.6366984320251126</v>
+        <v>0.4791737147886747</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.759151996896807</v>
+        <v>3.509349828722805</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.375244750575514</v>
+        <v>3.219957412743375</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.69356134316809</v>
+        <v>-2.915670728474491</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.297463788994531</v>
+        <v>2.053332697039832</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.6366984320251126</v>
+        <v>0.4791737147886747</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.757263809790582</v>
+        <v>3.50746164161658</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.370064980178376</v>
+        <v>3.214777642346238</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.700833228691555</v>
+        <v>-2.922942613997956</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.289375264388007</v>
+        <v>2.045244172433308</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6294265465016478</v>
+        <v>0.4719018292652099</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.747720908079365</v>
+        <v>3.497918739905364</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.368498990388529</v>
+        <v>3.21321165255639</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.698992209633304</v>
+        <v>-2.921101594939704</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.28854568222146</v>
+        <v>2.044414590266761</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6306947731731162</v>
+        <v>0.4731700559366783</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.746915854292399</v>
+        <v>3.497113686118397</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.381572397254447</v>
+        <v>3.226285059422309</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.705900915132984</v>
+        <v>-2.928010300439385</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.298855606887506</v>
+        <v>2.054724514932808</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6306947731731162</v>
+        <v>0.4731700559366783</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.759989261158317</v>
+        <v>3.510187092984316</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.381572397254447</v>
+        <v>3.226285059422309</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.707462557947844</v>
+        <v>-2.929571943254245</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.298230949761563</v>
+        <v>2.054099857806864</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6306947731731162</v>
+        <v>0.4731700559366783</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.759989261158317</v>
+        <v>3.510187092984316</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.380096438381449</v>
+        <v>3.224809100549311</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.735363345057317</v>
+        <v>-2.957472730363718</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.285594676044775</v>
+        <v>2.041463584090076</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5960978490301814</v>
+        <v>0.4385731317937435</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.737755147799558</v>
+        <v>3.487952979625557</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.376860882358648</v>
+        <v>3.221573544526509</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.738396342569991</v>
+        <v>-2.960505727876392</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.281145921016904</v>
+        <v>2.037014829062206</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5930648515175074</v>
+        <v>0.4355401342810696</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.732699793269153</v>
+        <v>3.482897625095152</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.443566841949152</v>
+        <v>3.288279504117013</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.758457663846498</v>
+        <v>-2.980567049152898</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.339827352096806</v>
+        <v>2.095696260142106</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5730035302410004</v>
+        <v>0.4154788130045626</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.787368960093752</v>
+        <v>3.537566791919751</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.583878560950999</v>
+        <v>3.42859122311886</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.015178481841322</v>
+        <v>-3.237287867147722</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.377450743900723</v>
+        <v>2.133319651946024</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4645889560971855</v>
+        <v>0.3070642388607478</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.86263193460931</v>
+        <v>3.612829766435309</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.652858830096639</v>
+        <v>3.4975714922645</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.169164899617462</v>
+        <v>-3.391274284923863</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.384836445935907</v>
+        <v>2.140705353981208</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4645889560971855</v>
+        <v>0.3070642388607478</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.93161220375495</v>
+        <v>3.681810035580949</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808533</v>
+        <v>3.619937176808535</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.63891003221676</v>
+        <v>3.483622694384621</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.118642995789796</v>
+        <v>-3.340752381096197</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.391096409587094</v>
+        <v>2.146965317632395</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4645889560971855</v>
+        <v>0.3070642388607478</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.917663405875071</v>
+        <v>3.66786123770107</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.785045226119627</v>
+        <v>3.378158895445228</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.787650820640552</v>
+        <v>3.620213592794636</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.118642995789796</v>
+        <v>-3.340752381096197</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.391096409587094</v>
+        <v>2.146965317632395</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4645889560971855</v>
+        <v>0.3070642388607478</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.78071461762692</v>
+        <v>3.613277389781004</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>60.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-65.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.6%</t>
+          <t>-469.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-125.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-121.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-193.3%</t>
+          <t>-168.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-45.4%</t>
         </is>
       </c>
     </row>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.757750275698671</v>
+        <v>-9.499286340927609</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7209394257602724</v>
+        <v>-0.6175538518518477</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.191099078777801</v>
+        <v>-2.041116997397713</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.867857661566263</v>
+        <v>1.957846910394316</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.68561710041079</v>
+        <v>-9.427153165639728</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6863524514064832</v>
+        <v>-0.582966877498059</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.191099078777801</v>
+        <v>-2.041116997397713</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.8735913658049</v>
+        <v>1.963580614632952</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.614250707801142</v>
+        <v>-9.355786773030081</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6675431567564898</v>
+        <v>-0.5641575828480652</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.119732686168153</v>
+        <v>-1.969750604788065</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.906673938976823</v>
+        <v>1.996663187804876</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.520791673815918</v>
+        <v>-9.262327739044856</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6400430244753075</v>
+        <v>-0.5366574505668829</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.119732686168153</v>
+        <v>-1.969750604788065</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.896790457663916</v>
+        <v>1.986779706491968</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.25354987294752</v>
+        <v>-8.995085938176459</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5349808646273222</v>
+        <v>-0.4315952907188976</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.119732686168153</v>
+        <v>-1.969750604788065</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.894955897164542</v>
+        <v>1.984945145992595</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.155642834271029</v>
+        <v>-8.897178899499968</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4961183641301865</v>
+        <v>-0.3927327902217619</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.051746936307596</v>
+        <v>-1.901764854927509</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.935447032107415</v>
+        <v>2.025436280935468</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.131689293295072</v>
+        <v>-8.87322535852401</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.48586844159431</v>
+        <v>-0.3824828676858854</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.027793395331639</v>
+        <v>-1.877811313951551</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.950487662838483</v>
+        <v>2.040476911666536</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.867629354972275</v>
+        <v>-8.609165420201213</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3935047824269433</v>
+        <v>-0.2901192085185187</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.763733457008843</v>
+        <v>-1.613751375628755</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.095663309670408</v>
+        <v>2.185652558498461</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.160549731467437</v>
+        <v>-7.902085796696375</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1134599666853093</v>
+        <v>-0.01007439277688427</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.763733457008843</v>
+        <v>-1.613751375628755</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.092876276010108</v>
+        <v>2.182865524838161</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.120365433101247</v>
+        <v>-7.861901498330185</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.09704262345099179</v>
+        <v>0.006342950457433272</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.723549158642652</v>
+        <v>-1.573567077262564</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.117330478917664</v>
+        <v>2.207319727745716</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.956965562161884</v>
+        <v>-7.698501627390822</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.03231585385448987</v>
+        <v>0.07106972005393519</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.56014928770329</v>
+        <v>-1.410167206323202</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.214737222702038</v>
+        <v>2.304726471530091</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.723484339932286</v>
+        <v>-7.465020405161224</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.06900106387520211</v>
+        <v>0.1723866377836272</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.326668065473691</v>
+        <v>-1.176685984093603</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.362750384877649</v>
+        <v>2.452739633705702</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.573817948924771</v>
+        <v>-7.315354014153709</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1259754099652488</v>
+        <v>0.2293609838736739</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.233764574231155</v>
+        <v>-1.083782492851067</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.415600269310212</v>
+        <v>2.505589518138265</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.441542475293884</v>
+        <v>-7.183078540522822</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1742530861646308</v>
+        <v>0.2776386600730554</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.101489100600269</v>
+        <v>-0.9515070192201804</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.490333040235771</v>
+        <v>2.580322289063824</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.285804142734142</v>
+        <v>-7.02734020796308</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2393634798761641</v>
+        <v>0.3427490537845888</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.9457507680405269</v>
+        <v>-0.7957686866604389</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.586591100459253</v>
+        <v>2.676580349287305</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.036804344050561</v>
+        <v>-6.778340409279499</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3518697405732554</v>
+        <v>0.45525531448168</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.9457507680405269</v>
+        <v>-0.7957686866604389</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.599497441682911</v>
+        <v>2.689486690510964</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.142394333823666</v>
+        <v>-6.883930399052604</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1816578150647947</v>
+        <v>0.2850433889732198</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.051340757813631</v>
+        <v>-0.9013586764335433</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.40816751821983</v>
+        <v>2.498156767047883</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.161129235942263</v>
+        <v>-6.902665301171201</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2227081960944424</v>
+        <v>0.326093770002867</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.056936767473763</v>
+        <v>-0.9069546860936746</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.453354254300837</v>
+        <v>2.54334350312889</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.013189194534664</v>
+        <v>-6.754725259763601</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1620052899693145</v>
+        <v>0.2653908638777391</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.036615851565205</v>
+        <v>-0.886633770185117</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.345667881157804</v>
+        <v>2.435657129985857</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.960219672280675</v>
+        <v>-6.701755737509613</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1744791126174317</v>
+        <v>0.2778646865258567</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8336642479311281</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.36873560825672</v>
+        <v>2.458724857084773</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.916671265509985</v>
+        <v>-6.658207330738922</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1849378632306147</v>
+        <v>0.2883234371390397</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8336642479311281</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.361774996161627</v>
+        <v>2.451764244989679</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.674522872056126</v>
+        <v>-6.416058937285064</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.296259574993301</v>
+        <v>0.3996451489017261</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8336642479311281</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.37623735054277</v>
+        <v>2.466226599370823</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.566263734933605</v>
+        <v>-6.307799800162543</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3340953503015047</v>
+        <v>0.4374809242099298</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.8336642479311281</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.370769471001965</v>
+        <v>2.460758719830018</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.442972600116474</v>
+        <v>-6.184508665345412</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3809098982389338</v>
+        <v>0.4842954721473589</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8603551944940857</v>
+        <v>-0.7103731131139976</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.44224224590282</v>
+        <v>2.532231494730873</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.421823401213031</v>
+        <v>-6.163359466441968</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3970705560376366</v>
+        <v>0.5004561299460613</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.6892239142105543</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.462632743482211</v>
+        <v>2.552621992310264</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.178057959229586</v>
+        <v>-5.919594024458524</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4903574411780647</v>
+        <v>0.5937430150864897</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.6892239142105543</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.458413451829262</v>
+        <v>2.548402700657315</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.076295138952291</v>
+        <v>-5.817831204181229</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.533186883208999</v>
+        <v>0.6365724571174236</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6760048458181256</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.468469206784735</v>
+        <v>2.558458455612788</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.826444745003217</v>
+        <v>-5.567980810232155</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6258691157723311</v>
+        <v>0.7292546896807557</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6760048458181256</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.461211281768437</v>
+        <v>2.55120053059649</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.650552652535785</v>
+        <v>-5.392088717764722</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6998250762799523</v>
+        <v>0.8032106501883778</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6760048458181256</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.464810405289086</v>
+        <v>2.554799654117139</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.479106189513321</v>
+        <v>-5.220642254742258</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7817311675434917</v>
+        <v>0.8851167414519168</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6545404641757505</v>
+        <v>-0.5045583827956625</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.581005789157117</v>
+        <v>2.67099503798517</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.404816623774982</v>
+        <v>-5.146352689003919</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8104674714551243</v>
+        <v>0.9138530453635494</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5802508984374113</v>
+        <v>-0.4302688170573232</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624600006216418</v>
+        <v>2.714589255044471</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.341180881541048</v>
+        <v>-5.082716946769985</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8406165694030152</v>
+        <v>0.9440021433114403</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.3666330748233886</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.667476252611096</v>
+        <v>2.757465501439149</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-4.971290187444064</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8663815319171788</v>
+        <v>0.9697671058256041</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.3666330748233886</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.648670511394891</v>
+        <v>2.738659760222944</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-4.730859690639204</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9642968072640004</v>
+        <v>1.067682381172426</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.1262025780185284</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.794671886102685</v>
+        <v>2.884661134930738</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-4.65861712246801</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9971231483672984</v>
+        <v>1.100508722275724</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.1262025780185284</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.798601199937505</v>
+        <v>2.888590448765558</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.605618800186622</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019001061197194</v>
+        <v>1.122386635105619</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.07086631901658952</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832481539256008</v>
+        <v>2.922470788084061</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.496813914706895</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.059521086609078</v>
+        <v>1.162906660517503</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.07086631901658952</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829479610476002</v>
+        <v>2.919468859304055</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.276793116669884</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.149108442834496</v>
+        <v>1.252494016742921</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.07962855532869739</v>
+        <v>0.07035352605139072</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915790554527404</v>
+        <v>3.005779803355457</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.143925427606606</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.218149701261631</v>
+        <v>1.321535275170056</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.07962855532869739</v>
+        <v>0.07035352605139072</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.931684737329228</v>
+        <v>3.021673986157281</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.023752344242108</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267364779047732</v>
+        <v>1.370750352956157</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.04054452803580155</v>
+        <v>0.1905266094158897</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004934431788229</v>
+        <v>3.094923680616282</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-3.87908019914237</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.335321739649067</v>
+        <v>1.438707313557492</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.185216673135539</v>
+        <v>0.3351987545156271</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.101825821409511</v>
+        <v>3.191815070237564</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-3.938955026500063</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.297409300107416</v>
+        <v>1.400794874015841</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.275323927157935</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.051938416396322</v>
+        <v>3.141927665224375</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-3.819134795589225</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360626561705959</v>
+        <v>1.464012135614384</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.275323927157935</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06722758563053</v>
+        <v>3.157216834458583</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-3.821604502051031</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267282878443678</v>
+        <v>1.370668452352104</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1228721393160407</v>
+        <v>0.2728542206961288</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.973389961075888</v>
+        <v>3.063379209903941</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-3.889974688375041</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.159196665399375</v>
+        <v>1.262582239307801</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2821299197323437</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.898217241982918</v>
+        <v>2.988206490810971</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162226675993152</v>
+        <v>-3.903762741222088</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144118152892448</v>
+        <v>1.247503726800874</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2821299197323437</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88865395061481</v>
+        <v>2.978643199442863</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193219835321857</v>
+        <v>-3.934755900550793</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9564304542013529</v>
+        <v>1.059816028109778</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2821299197323437</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.713363515655197</v>
+        <v>2.803352764483249</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017745575529387</v>
+        <v>-3.759281640758324</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.031187390110128</v>
+        <v>1.134572964018554</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2821299197323437</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717930747646984</v>
+        <v>2.807919996475037</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128681828170636</v>
+        <v>-3.870217893399572</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.962554917814836</v>
+        <v>1.065940491723262</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2821299197323437</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.693672776408191</v>
+        <v>2.783662025236244</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.095018282698354</v>
+        <v>-3.836554347927291</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9791517212236545</v>
+        <v>1.08253729513208</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3157934652046256</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717002288911466</v>
+        <v>2.806991537739519</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.035165663494631</v>
+        <v>-3.776701728723567</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.013265155337276</v>
+        <v>1.116650729245702</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3157934652046256</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727174675343599</v>
+        <v>2.817163924171651</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.948922200468253</v>
+        <v>-3.69045826569719</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.042708811121687</v>
+        <v>1.146094385030113</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3157934652046256</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722120945917459</v>
+        <v>2.812110194745511</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.994229019867233</v>
+        <v>-3.73576508509617</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.016361858806621</v>
+        <v>1.119747432715046</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.2749833021953948</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689410623556446</v>
+        <v>2.779399872384499</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.023262124569534</v>
+        <v>-3.764798189798471</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.005300489958802</v>
+        <v>1.108686063867227</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.2749833021953948</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689962496589547</v>
+        <v>2.7799517454176</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.930451643118675</v>
+        <v>-3.671987708347612</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9716973744305115</v>
+        <v>1.075082948338937</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.217811702266166</v>
+        <v>0.3677937836462541</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674921477351428</v>
+        <v>2.764910726179481</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974841112448102</v>
+        <v>-3.71637717767704</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9558150626233413</v>
+        <v>1.059200636531766</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1734222329367384</v>
+        <v>0.3234043143168265</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650161271678373</v>
+        <v>2.740150520506426</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862169894211852</v>
+        <v>-3.60370595944079</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9959592584295645</v>
+        <v>1.09934483233799</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.4360755325530767</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.712839711131846</v>
+        <v>2.802828959959899</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.74979289302918</v>
+        <v>-3.491328958258117</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.046401354733301</v>
+        <v>1.149786928641726</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.4360755325530767</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.718331006962513</v>
+        <v>2.808320255790566</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777573290930533</v>
+        <v>-3.51910935615947</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.046786397341299</v>
+        <v>1.150171971249724</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2583130532716355</v>
+        <v>0.4082951346517236</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71315996999024</v>
+        <v>2.803149218818293</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.860574571955812</v>
+        <v>-3.602110637184749</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8519416049318402</v>
+        <v>0.9553271788402653</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3897242501245499</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.540373159274589</v>
+        <v>2.630362408102642</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.969188650399143</v>
+        <v>-3.71072471562808</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9286456342737133</v>
+        <v>1.032031208182138</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3897242501245499</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.660522819993795</v>
+        <v>2.750512068821848</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.933779612151</v>
+        <v>-3.675315677379937</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9573222756752935</v>
+        <v>1.060707849583719</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3897242501245499</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.675035846096118</v>
+        <v>2.765025094924171</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.895395949592849</v>
+        <v>-3.636932014821786</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9700951820409225</v>
+        <v>1.073480755949348</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.428107912682701</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.695485484973378</v>
+        <v>2.78547473380143</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.718279619557683</v>
+        <v>-3.45981568478662</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.037670742900291</v>
+        <v>1.141056316808716</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.428107912682701</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.69221451381868</v>
+        <v>2.782203762646732</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.763371864391228</v>
+        <v>-3.504907929620166</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.020317236728786</v>
+        <v>1.123702810637211</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2162297881332231</v>
+        <v>0.3662118695133113</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.655760279678959</v>
+        <v>2.745749528507012</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.58399644315246</v>
+        <v>-3.325532508381398</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.085854380530708</v>
+        <v>1.189239954439133</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3730065463039418</v>
+        <v>0.5229886276840299</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.743613309887805</v>
+        <v>2.833602558715858</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.629010656673067</v>
+        <v>-3.370546721902004</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.048656150454055</v>
+        <v>1.15204172436248</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3426576509893372</v>
+        <v>0.4926397323694253</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.706211428030632</v>
+        <v>2.796200676858684</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.896015166945502</v>
+        <v>-3.63755123217444</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9475459086840265</v>
+        <v>1.050931482592452</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1482946129463886</v>
+        <v>0.2982766943264767</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.595285167543808</v>
+        <v>2.685274416371861</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.997212948382675</v>
+        <v>-3.738749013611613</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9062707180056591</v>
+        <v>1.009656291914084</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.2298678807811575</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553443801313118</v>
+        <v>2.643433050141171</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.990701981768362</v>
+        <v>-3.7322380469973</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9064750662057008</v>
+        <v>1.009860640114126</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.2298678807811575</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551043762867435</v>
+        <v>2.641033011695488</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.971663854061065</v>
+        <v>-3.713199919290003</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9106150364968646</v>
+        <v>1.014000610405289</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.171684269449963</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.512658315276963</v>
+        <v>2.602647564105016</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.002790485211683</v>
+        <v>-3.744326550440621</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.075746252975298</v>
+        <v>1.179131826883723</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.171684269449963</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.690240184215644</v>
+        <v>2.780229433043696</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.0166572465456</v>
+        <v>-3.758193311774538</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.071032877427865</v>
+        <v>1.174418451336289</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.13382635271614</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668358763161483</v>
+        <v>2.758348011989536</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.97185307500567</v>
+        <v>-3.713389140234608</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.094963076440763</v>
+        <v>1.198348650349187</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.13382635271614</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674367293558409</v>
+        <v>2.764356542386462</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.824110104770668</v>
+        <v>-3.565646169999606</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.233212912326785</v>
+        <v>1.33659848623521</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.3016337099510232</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.854204355691361</v>
+        <v>2.944193604519414</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.926124787301889</v>
+        <v>-3.667660852530827</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.195200660845778</v>
+        <v>1.298586234754203</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.3016337099510232</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.856997977222842</v>
+        <v>2.946987226050895</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.919972081249105</v>
+        <v>-3.661508146478043</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.19832409165855</v>
+        <v>1.301709665566975</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1578043346237194</v>
+        <v>0.3077864160038075</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.861351949246171</v>
+        <v>2.951341198074224</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.936781379399606</v>
+        <v>-3.678317444628544</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.19068084913846</v>
+        <v>1.294066423046885</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.2909771178533058</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85034684709598</v>
+        <v>2.940336095924033</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.874483380623484</v>
+        <v>-3.616019445852422</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.281935602445729</v>
+        <v>1.385321176354154</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.2909771178533058</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.916682400892801</v>
+        <v>3.006671649720854</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.681145631965912</v>
+        <v>-3.414229248187264</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.161562703622885</v>
+        <v>1.268329257134344</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.2364178041160324</v>
+        <v>0.4889953100224602</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.776228063192617</v>
+        <v>2.927774566736474</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.607767534877176</v>
+        <v>-3.340851151098528</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.261204174780555</v>
+        <v>1.367970728292014</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.309795901204769</v>
+        <v>0.5623734071111968</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.890545153768034</v>
+        <v>3.042091657311891</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.70550807950215</v>
+        <v>-3.438591695723502</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.236735693046609</v>
+        <v>1.343502246558068</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2939066230717888</v>
+        <v>0.5464841289782165</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.89563932300429</v>
+        <v>3.047185826548146</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.881845839625079</v>
+        <v>-3.614929455846431</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.164736569822109</v>
+        <v>1.271503123333568</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.1175688629488594</v>
+        <v>0.3701463688552871</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.788372647755204</v>
+        <v>2.939919151299061</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.805423793193153</v>
+        <v>-3.538507409414505</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.193797006434808</v>
+        <v>1.300563559946267</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.1175688629488594</v>
+        <v>0.3701463688552871</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.786864265795132</v>
+        <v>2.938410769338989</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.761050661554584</v>
+        <v>-3.494134277775936</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.211409126525672</v>
+        <v>1.318175680037131</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.161941994587428</v>
+        <v>0.4145195004938557</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.81335101221371</v>
+        <v>2.964897515757566</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.638216440667417</v>
+        <v>-3.371300056888769</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.254936609019129</v>
+        <v>1.361703162530588</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.161941994587428</v>
+        <v>0.4145195004938557</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.8077448063523</v>
+        <v>2.959291309896157</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.590560710106361</v>
+        <v>-3.323644326327713</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.280380658271356</v>
+        <v>1.387147211782815</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.2095977251484836</v>
+        <v>0.4621752310549114</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.842720001716738</v>
+        <v>2.994266505260595</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.490042551607607</v>
+        <v>-3.223126167828958</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.325480295045583</v>
+        <v>1.432246848557042</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.3101158836472382</v>
+        <v>0.5626933895536659</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.907923270190716</v>
+        <v>3.059469773734572</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.550709142009996</v>
+        <v>-3.283792758231348</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.287968331360499</v>
+        <v>1.394734884871959</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.2284175669287045</v>
+        <v>0.4809950728351322</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.845658952635468</v>
+        <v>2.997205456179324</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.505870740401598</v>
+        <v>-3.23895435662295</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.310001394614487</v>
+        <v>1.416767948125946</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.232960999873574</v>
+        <v>0.4855385057800017</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.852482715013018</v>
+        <v>3.004029218556875</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.606629376158596</v>
+        <v>-3.339712992379948</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.273858879942766</v>
+        <v>1.380625433454225</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.1441354311465686</v>
+        <v>0.3967129370529963</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.803348313407893</v>
+        <v>2.954894816951749</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.562426539072696</v>
+        <v>-3.295510155294048</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.297419617304963</v>
+        <v>1.404186170816422</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.188338268232469</v>
+        <v>0.4409157741388967</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.83574961818727</v>
+        <v>2.987296121731127</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.599405566736139</v>
+        <v>-3.332489182957491</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.281038006708833</v>
+        <v>1.387804560220292</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.2253121700237996</v>
+        <v>0.4778896759302272</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.856343959731316</v>
+        <v>3.007890463275173</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.441114149196867</v>
+        <v>-3.174197765418219</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.395602338907582</v>
+        <v>1.502368892419041</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.2253121700237996</v>
+        <v>0.4778896759302272</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.907591724914356</v>
+        <v>3.059138228458212</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.401183476018976</v>
+        <v>-3.134267092240328</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.410015312772991</v>
+        <v>1.51678186628445</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.2652428432016899</v>
+        <v>0.5178203491081176</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.929990833415343</v>
+        <v>3.0815373369592</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.350151383296448</v>
+        <v>-3.0832349995178</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.425376378100272</v>
+        <v>1.532142931611732</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.3162749359242178</v>
+        <v>0.5688524418306455</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.95555831728713</v>
+        <v>3.107104820830986</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.284927202169243</v>
+        <v>-3.018010818390595</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.468653454643859</v>
+        <v>1.575420008155319</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.3814991170514235</v>
+        <v>0.6340766229578512</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.011880230056158</v>
+        <v>3.163426733600015</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.247500182098109</v>
+        <v>-2.980583798319461</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.479585234971593</v>
+        <v>1.586351788483052</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.3867506550806051</v>
+        <v>0.6393281609870328</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.010992125172947</v>
+        <v>3.162538628716804</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.267611838132817</v>
+        <v>-3.000695454354169</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.47279736488895</v>
+        <v>1.57956391840041</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.3977780000780243</v>
+        <v>0.650355505984452</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.018865324502639</v>
+        <v>3.170411828046496</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.213867023705613</v>
+        <v>-2.946950639926964</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.654853061681043</v>
+        <v>1.761619615192502</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.4078413095184863</v>
+        <v>0.660418815424914</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.185461081188127</v>
+        <v>3.337007584731984</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.19007545509947</v>
+        <v>-2.923159071320822</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.784482598341317</v>
+        <v>1.891249151852776</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.4316328781246286</v>
+        <v>0.6842103840310563</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.31984893156963</v>
+        <v>3.471395435113486</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.163991370835662</v>
+        <v>-2.897074987057014</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.786624208060699</v>
+        <v>1.893390761572159</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.4316328781246286</v>
+        <v>0.6842103840310563</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.311556907583489</v>
+        <v>3.463103411127345</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.085860189986716</v>
+        <v>-2.818943806208067</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.816069875984057</v>
+        <v>1.922836429495517</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.5058096890083131</v>
+        <v>0.7583871949147408</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.354256189697479</v>
+        <v>3.505802693241336</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.076967728593432</v>
+        <v>-2.810051344814784</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.837181266268162</v>
+        <v>1.943947819779622</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.5058096890083131</v>
+        <v>0.7583871949147408</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.37181059542427</v>
+        <v>3.523357098968127</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.24544384556331</v>
+        <v>-2.978527461784662</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.761645866884795</v>
+        <v>1.868412420396254</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.4778618532917324</v>
+        <v>0.7304393591981601</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.346896941398906</v>
+        <v>3.498443444942763</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.547644316701727</v>
+        <v>-2.280727932923079</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.02203537561729</v>
+        <v>2.128801929128749</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.4075137939213216</v>
+        <v>0.6600912998277493</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.285957802964521</v>
+        <v>3.437504306508378</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.524923213018575</v>
+        <v>-2.258006829239926</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.021787839587455</v>
+        <v>2.128554393098915</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.4075137939213216</v>
+        <v>0.6600912998277493</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.276621825461426</v>
+        <v>3.428168329005282</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.523198169728531</v>
+        <v>-2.256281785949882</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.181383982754642</v>
+        <v>2.288150536266102</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.4092388372113654</v>
+        <v>0.661816343117793</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.436562977286621</v>
+        <v>3.588109480830478</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.677979176506786</v>
+        <v>-2.411062792728138</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.156549402536987</v>
+        <v>2.263315956048446</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.3758711631568893</v>
+        <v>0.6284486690633169</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.453620195347582</v>
+        <v>3.605166698891439</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.626543843122126</v>
+        <v>-2.359627459343478</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.173798891880396</v>
+        <v>2.280565445391855</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.427306496541549</v>
+        <v>0.6798840024479765</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.481156751367923</v>
+        <v>3.632703254911779</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.599592618795638</v>
+        <v>-2.33267623501699</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.194585535255732</v>
+        <v>2.301352088767191</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.4421868425692681</v>
+        <v>0.6947643484756957</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.500091112629296</v>
+        <v>3.651637616173153</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.168530093129822</v>
+        <v>3.418882139232695</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.735545626851954</v>
+        <v>-2.468629243073306</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.073955418075293</v>
+        <v>2.431074017689625</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.4421868425692681</v>
+        <v>0.6947643484756957</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.433842198671383</v>
+        <v>3.835740748318112</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.160646788032815</v>
+        <v>3.410998834135688</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.757953744656827</v>
+        <v>-2.491037360878178</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.057108865856337</v>
+        <v>2.414227465470669</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.4421868425692681</v>
+        <v>0.6947643484756957</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.425958893574376</v>
+        <v>3.827857443221105</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.162700787582452</v>
+        <v>3.413052833685325</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.905959512136226</v>
+        <v>-2.639043128357578</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.999960558414215</v>
+        <v>2.357079158028547</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.3554598337057266</v>
+        <v>0.6080373396121542</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.375976687805888</v>
+        <v>3.777875237452618</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.218954505304299</v>
+        <v>3.469306551407172</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.915400438024756</v>
+        <v>-2.648484054246108</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.05243790578065</v>
+        <v>2.409556505394982</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.4778869512491181</v>
+        <v>0.7304644571555456</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.505686676053771</v>
+        <v>3.9075852257005</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.2218455998496</v>
+        <v>3.472197645952473</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.9141136744852</v>
+        <v>-2.647197290706552</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.055843705741773</v>
+        <v>2.412962305356105</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.4791737147886747</v>
+        <v>0.7317512206951022</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.509349828722805</v>
+        <v>3.911248378369535</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.219957412743375</v>
+        <v>3.470309458846248</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.915670728474491</v>
+        <v>-2.648754344695843</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.053332697039832</v>
+        <v>2.410451296654164</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.4791737147886747</v>
+        <v>0.7317512206951022</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.50746164161658</v>
+        <v>3.90936019126331</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.214777642346238</v>
+        <v>3.465129688449111</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.922942613997956</v>
+        <v>-2.656026230219307</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.045244172433308</v>
+        <v>2.402362772047641</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.4719018292652099</v>
+        <v>0.7244793351716374</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.497918739905364</v>
+        <v>3.899817289552094</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.21321165255639</v>
+        <v>3.463563698659263</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.921101594939704</v>
+        <v>-2.654185211161056</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.044414590266761</v>
+        <v>2.401533189881094</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4731700559366783</v>
+        <v>0.7257475618431058</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.497113686118397</v>
+        <v>3.899012235765127</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647107</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.226285059422309</v>
+        <v>3.476637105525182</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.928010300439385</v>
+        <v>-2.661093916660737</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.054724514932808</v>
+        <v>2.41184311454714</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4731700559366783</v>
+        <v>0.7257475618431058</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.510187092984316</v>
+        <v>3.912085642631046</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.226285059422309</v>
+        <v>3.476637105525182</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.929571943254245</v>
+        <v>-2.662655559475597</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.054099857806864</v>
+        <v>2.411218457421196</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4731700559366783</v>
+        <v>0.7257475618431058</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.510187092984316</v>
+        <v>3.912085642631046</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.224809100549311</v>
+        <v>3.475161146652184</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.957472730363718</v>
+        <v>-2.690556346585069</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.041463584090076</v>
+        <v>2.398582183704408</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4385731317937435</v>
+        <v>0.691150637700171</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.487952979625557</v>
+        <v>3.889851529272287</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.221573544526509</v>
+        <v>3.471925590629382</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.960505727876392</v>
+        <v>-2.693589344097743</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.037014829062206</v>
+        <v>2.394133428676538</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4355401342810696</v>
+        <v>0.6881176401874971</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.482897625095152</v>
+        <v>3.884796174741881</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.288279504117013</v>
+        <v>3.538631550219886</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.980567049152898</v>
+        <v>-2.71365066537425</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.095696260142106</v>
+        <v>2.452814859756439</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4154788130045626</v>
+        <v>0.66805631891099</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.537566791919751</v>
+        <v>3.93946534156648</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.42859122311886</v>
+        <v>3.678943269221733</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.237287867147722</v>
+        <v>-2.970371483369074</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.133319651946024</v>
+        <v>2.490438251560356</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3070642388607478</v>
+        <v>0.5596417447671752</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.612829766435309</v>
+        <v>4.014728316082039</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.4975714922645</v>
+        <v>3.747923538367373</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.391274284923863</v>
+        <v>-3.124357901145215</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.140705353981208</v>
+        <v>2.49782395359554</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3070642388607478</v>
+        <v>0.5596417447671752</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.681810035580949</v>
+        <v>4.083708585227678</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808535</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.483622694384621</v>
+        <v>3.733974740487494</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.340752381096197</v>
+        <v>-3.073835997317549</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.146965317632395</v>
+        <v>2.504083917246727</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3070642388607478</v>
+        <v>0.5596417447671752</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.66786123770107</v>
+        <v>4.069759787347799</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.378158895445228</v>
+        <v>3.882624087613461</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.620213592794636</v>
+        <v>4.012700163877915</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.340752381096197</v>
+        <v>-3.073835997317549</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.146965317632395</v>
+        <v>2.504083917246727</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3070642388607478</v>
+        <v>0.5596417447671752</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.613277389781004</v>
+        <v>4.005763960864282</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.5%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-469.0%</t>
+          <t>-507.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.8%</t>
+          <t>-141.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.8%</t>
+          <t>-121.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-157.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-81.8%</t>
         </is>
       </c>
     </row>
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.499286340927609</v>
+        <v>-9.757750275698671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6175538518518477</v>
+        <v>-0.7209394257602724</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.041116997397713</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.957846910394316</v>
+        <v>1.867857661566263</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.427153165639728</v>
+        <v>-9.68561710041079</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.582966877498059</v>
+        <v>-0.6863524514064832</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.041116997397713</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.963580614632952</v>
+        <v>1.8735913658049</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.355786773030081</v>
+        <v>-9.614250707801142</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5641575828480652</v>
+        <v>-0.6675431567564898</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.969750604788065</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.996663187804876</v>
+        <v>1.906673938976823</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.262327739044856</v>
+        <v>-9.520791673815918</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5366574505668829</v>
+        <v>-0.6400430244753075</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.969750604788065</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.986779706491968</v>
+        <v>1.896790457663916</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.995085938176459</v>
+        <v>-9.25354987294752</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4315952907188976</v>
+        <v>-0.5349808646273222</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.969750604788065</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.984945145992595</v>
+        <v>1.894955897164542</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.897178899499968</v>
+        <v>-9.155642834271029</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3927327902217619</v>
+        <v>-0.4961183641301865</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.901764854927509</v>
+        <v>-2.051746936307596</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.025436280935468</v>
+        <v>1.935447032107415</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.87322535852401</v>
+        <v>-9.131689293295072</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3824828676858854</v>
+        <v>-0.48586844159431</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.877811313951551</v>
+        <v>-2.027793395331639</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.040476911666536</v>
+        <v>1.950487662838483</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.609165420201213</v>
+        <v>-8.867629354972275</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2901192085185187</v>
+        <v>-0.3935047824269433</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.613751375628755</v>
+        <v>-1.763733457008843</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.185652558498461</v>
+        <v>2.095663309670408</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.902085796696375</v>
+        <v>-8.160549731467437</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.01007439277688427</v>
+        <v>-0.1134599666853093</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.613751375628755</v>
+        <v>-1.763733457008843</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.182865524838161</v>
+        <v>2.092876276010108</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.861901498330185</v>
+        <v>-8.120365433101247</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.006342950457433272</v>
+        <v>-0.09704262345099179</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.573567077262564</v>
+        <v>-1.723549158642652</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.207319727745716</v>
+        <v>2.117330478917664</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.698501627390822</v>
+        <v>-7.956965562161884</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.07106972005393519</v>
+        <v>-0.03231585385448987</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.410167206323202</v>
+        <v>-1.56014928770329</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.304726471530091</v>
+        <v>2.214737222702038</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.465020405161224</v>
+        <v>-7.723484339932286</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1723866377836272</v>
+        <v>0.06900106387520211</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.176685984093603</v>
+        <v>-1.326668065473691</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.452739633705702</v>
+        <v>2.362750384877649</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.315354014153709</v>
+        <v>-7.573817948924771</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2293609838736739</v>
+        <v>0.1259754099652488</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.083782492851067</v>
+        <v>-1.233764574231155</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.505589518138265</v>
+        <v>2.415600269310212</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.183078540522822</v>
+        <v>-7.441542475293884</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2776386600730554</v>
+        <v>0.1742530861646308</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9515070192201804</v>
+        <v>-1.101489100600269</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.580322289063824</v>
+        <v>2.490333040235771</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.02734020796308</v>
+        <v>-7.285804142734142</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3427490537845888</v>
+        <v>0.2393634798761641</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7957686866604389</v>
+        <v>-0.9457507680405269</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.676580349287305</v>
+        <v>2.586591100459253</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.778340409279499</v>
+        <v>-7.036804344050561</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.45525531448168</v>
+        <v>0.3518697405732554</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7957686866604389</v>
+        <v>-0.9457507680405269</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.689486690510964</v>
+        <v>2.599497441682911</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.883930399052604</v>
+        <v>-7.142394333823666</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2850433889732198</v>
+        <v>0.1816578150647947</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.9013586764335433</v>
+        <v>-1.051340757813631</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.498156767047883</v>
+        <v>2.40816751821983</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.902665301171201</v>
+        <v>-7.161129235942263</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.326093770002867</v>
+        <v>0.2227081960944424</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9069546860936746</v>
+        <v>-1.056936767473763</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.54334350312889</v>
+        <v>2.453354254300837</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.754725259763601</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2653908638777391</v>
+        <v>0.1620052899693145</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.886633770185117</v>
+        <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.435657129985857</v>
+        <v>2.345667881157804</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.701755737509613</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2778646865258567</v>
+        <v>0.1744791126174317</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8336642479311281</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.458724857084773</v>
+        <v>2.36873560825672</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.658207330738922</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2883234371390397</v>
+        <v>0.1849378632306147</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8336642479311281</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.451764244989679</v>
+        <v>2.361774996161627</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.416058937285064</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3996451489017261</v>
+        <v>0.296259574993301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8336642479311281</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.466226599370823</v>
+        <v>2.37623735054277</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.307799800162543</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4374809242099298</v>
+        <v>0.3340953503015047</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8336642479311281</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.460758719830018</v>
+        <v>2.370769471001965</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.184508665345412</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4842954721473589</v>
+        <v>0.3809098982389338</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7103731131139976</v>
+        <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.532231494730873</v>
+        <v>2.44224224590282</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.163359466441968</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5004561299460613</v>
+        <v>0.3970705560376366</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6892239142105543</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.552621992310264</v>
+        <v>2.462632743482211</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.919594024458524</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5937430150864897</v>
+        <v>0.4903574411780647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6892239142105543</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.548402700657315</v>
+        <v>2.458413451829262</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.817831204181229</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6365724571174236</v>
+        <v>0.533186883208999</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6760048458181256</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.558458455612788</v>
+        <v>2.468469206784735</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.567980810232155</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7292546896807557</v>
+        <v>0.6258691157723311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6760048458181256</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.55120053059649</v>
+        <v>2.461211281768437</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.392088717764722</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8032106501883778</v>
+        <v>0.6998250762799523</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6760048458181256</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.554799654117139</v>
+        <v>2.464810405289086</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.220642254742258</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8851167414519168</v>
+        <v>0.7817311675434917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5045583827956625</v>
+        <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.67099503798517</v>
+        <v>2.581005789157117</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.146352689003919</v>
+        <v>-5.263585023793153</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9138530453635494</v>
+        <v>0.8669601114478556</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4302688170573232</v>
+        <v>-0.4390192984555826</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.714589255044471</v>
+        <v>2.709338966205515</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.082716946769985</v>
+        <v>-5.199949281559219</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9440021433114403</v>
+        <v>0.8971092093957469</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3666330748233886</v>
+        <v>-0.3753835562216481</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.757465501439149</v>
+        <v>2.752215212600193</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.971290187444064</v>
+        <v>-5.088522522233299</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9697671058256041</v>
+        <v>0.9228741719099105</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3666330748233886</v>
+        <v>-0.3753835562216481</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.738659760222944</v>
+        <v>2.733409471383989</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.730859690639204</v>
+        <v>-4.848092025428438</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.067682381172426</v>
+        <v>1.020789447256732</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1262025780185284</v>
+        <v>-0.1349530594167878</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.884661134930738</v>
+        <v>2.879410846091782</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.65861712246801</v>
+        <v>-4.775849457257244</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.100508722275724</v>
+        <v>1.05361578836003</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1262025780185284</v>
+        <v>-0.1349530594167878</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.888590448765558</v>
+        <v>2.883340159926602</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.605618800186622</v>
+        <v>-4.722851134975856</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.122386635105619</v>
+        <v>1.075493701189925</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07086631901658952</v>
+        <v>-0.07961680041484898</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.922470788084061</v>
+        <v>2.917220499245106</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.496813914706895</v>
+        <v>-4.614046249496129</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.162906660517503</v>
+        <v>1.11601372660181</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07086631901658952</v>
+        <v>-0.07961680041484898</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.919468859304055</v>
+        <v>2.914218570465099</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.276793116669884</v>
+        <v>-4.394025451459118</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.252494016742921</v>
+        <v>1.205601082827228</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.07035352605139072</v>
+        <v>0.06160304465313127</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.005779803355457</v>
+        <v>3.000529514516502</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.143925427606606</v>
+        <v>-4.261157762395841</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.321535275170056</v>
+        <v>1.274642341254362</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.07035352605139072</v>
+        <v>0.06160304465313127</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.021673986157281</v>
+        <v>3.016423697318325</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.023752344242108</v>
+        <v>-4.140984679031342</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.370750352956157</v>
+        <v>1.323857419040464</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1905266094158897</v>
+        <v>0.1817761280176302</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.094923680616282</v>
+        <v>3.089673391777326</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.87908019914237</v>
+        <v>-3.996312533931604</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.438707313557492</v>
+        <v>1.391814379641799</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3351987545156271</v>
+        <v>0.3264482731173676</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.191815070237564</v>
+        <v>3.186564781398608</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.938955026500063</v>
+        <v>-4.056187361289297</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.400794874015841</v>
+        <v>1.353901940100147</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.275323927157935</v>
+        <v>0.2665734457596755</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.141927665224375</v>
+        <v>3.136677376385419</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.819134795589225</v>
+        <v>-3.936367130378459</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.464012135614384</v>
+        <v>1.417119201698691</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.275323927157935</v>
+        <v>0.2665734457596755</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157216834458583</v>
+        <v>3.151966545619628</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.821604502051031</v>
+        <v>-3.938836836840265</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.370668452352104</v>
+        <v>1.32377551843641</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2728542206961288</v>
+        <v>0.2641037392978693</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063379209903941</v>
+        <v>3.058128921064985</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.889974688375041</v>
+        <v>-4.007207023164275</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.262582239307801</v>
+        <v>1.215689305392107</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2821299197323437</v>
+        <v>0.2733794383340843</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988206490810971</v>
+        <v>2.982956201972016</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.903762741222088</v>
+        <v>-4.020995076011322</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.247503726800874</v>
+        <v>1.20061079288518</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2821299197323437</v>
+        <v>0.2733794383340843</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.978643199442863</v>
+        <v>2.973392910603907</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.934755900550793</v>
+        <v>-4.051988235340027</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.059816028109778</v>
+        <v>1.012923094194085</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2821299197323437</v>
+        <v>0.2733794383340843</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.803352764483249</v>
+        <v>2.798102475644294</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.759281640758324</v>
+        <v>-3.876513975547558</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.134572964018554</v>
+        <v>1.08768003010286</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2821299197323437</v>
+        <v>0.2733794383340843</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.807919996475037</v>
+        <v>2.802669707636082</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.870217893399572</v>
+        <v>-3.987450228188806</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.065940491723262</v>
+        <v>1.019047557807568</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2821299197323437</v>
+        <v>0.2733794383340843</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.783662025236244</v>
+        <v>2.778411736397289</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.836554347927291</v>
+        <v>-3.953786682716525</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.08253729513208</v>
+        <v>1.035644361216386</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3157934652046256</v>
+        <v>0.3070429838063661</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.806991537739519</v>
+        <v>2.801741248900563</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.776701728723567</v>
+        <v>-3.893934063512801</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.116650729245702</v>
+        <v>1.069757795330008</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3157934652046256</v>
+        <v>0.3070429838063661</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.817163924171651</v>
+        <v>2.811913635332695</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.69045826569719</v>
+        <v>-3.807690600486424</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.146094385030113</v>
+        <v>1.099201451114419</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3157934652046256</v>
+        <v>0.3070429838063661</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.812110194745511</v>
+        <v>2.806859905906556</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.73576508509617</v>
+        <v>-3.852997419885404</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.119747432715046</v>
+        <v>1.072854498799353</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2749833021953948</v>
+        <v>0.2662328207971353</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.779399872384499</v>
+        <v>2.774149583545543</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.764798189798471</v>
+        <v>-3.882030524587706</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.108686063867227</v>
+        <v>1.061793129951534</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2749833021953948</v>
+        <v>0.2662328207971353</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.7799517454176</v>
+        <v>2.774701456578645</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.671987708347612</v>
+        <v>-3.789220043136846</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.075082948338937</v>
+        <v>1.028190014423243</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3677937836462541</v>
+        <v>0.3590433022479947</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.764910726179481</v>
+        <v>2.759660437340526</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.71637717767704</v>
+        <v>-3.833609512466274</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.059200636531766</v>
+        <v>1.012307702616073</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3234043143168265</v>
+        <v>0.314653832918567</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.740150520506426</v>
+        <v>2.73490023166747</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.60370595944079</v>
+        <v>-3.720938294230024</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.09934483233799</v>
+        <v>1.052451898422296</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4360755325530767</v>
+        <v>0.4273250511548172</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.802828959959899</v>
+        <v>2.797578671120943</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.491328958258117</v>
+        <v>-3.608561293047351</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.149786928641726</v>
+        <v>1.102893994726032</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4360755325530767</v>
+        <v>0.4273250511548172</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.808320255790566</v>
+        <v>2.80306996695161</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.51910935615947</v>
+        <v>-3.636341690948704</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.150171971249724</v>
+        <v>1.10327903733403</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4082951346517236</v>
+        <v>0.3995446532534642</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.803149218818293</v>
+        <v>2.797898929979338</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.602110637184749</v>
+        <v>-3.719342971973983</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9553271788402653</v>
+        <v>0.9084342449245715</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3897242501245499</v>
+        <v>0.3809737687262904</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.630362408102642</v>
+        <v>2.625112119263687</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.71072471562808</v>
+        <v>-3.827957050417314</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.032031208182138</v>
+        <v>0.9851382742664447</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3897242501245499</v>
+        <v>0.3809737687262904</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.750512068821848</v>
+        <v>2.745261779982892</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.675315677379937</v>
+        <v>-3.792548012169171</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.060707849583719</v>
+        <v>1.013814915668025</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3897242501245499</v>
+        <v>0.3809737687262904</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.765025094924171</v>
+        <v>2.759774806085215</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.636932014821786</v>
+        <v>-3.75416434961102</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.073480755949348</v>
+        <v>1.026587822033654</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.428107912682701</v>
+        <v>0.4193574312844416</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.78547473380143</v>
+        <v>2.780224444962474</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.45981568478662</v>
+        <v>-3.577048019575854</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.141056316808716</v>
+        <v>1.094163382893023</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.428107912682701</v>
+        <v>0.4193574312844416</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.782203762646732</v>
+        <v>2.776953473807777</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.504907929620166</v>
+        <v>-3.6221402644094</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.123702810637211</v>
+        <v>1.076809876721518</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3662118695133113</v>
+        <v>0.3574613881150518</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.745749528507012</v>
+        <v>2.740499239668056</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.325532508381398</v>
+        <v>-3.442764843170632</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.189239954439133</v>
+        <v>1.142347020523439</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5229886276840299</v>
+        <v>0.5142381462857705</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.833602558715858</v>
+        <v>2.828352269876902</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.370546721902004</v>
+        <v>-3.487779056691239</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.15204172436248</v>
+        <v>1.105148790446786</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4926397323694253</v>
+        <v>0.4838892509711659</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.796200676858684</v>
+        <v>2.790950388019729</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.63755123217444</v>
+        <v>-3.754783566963674</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.050931482592452</v>
+        <v>1.004038548676758</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2982766943264767</v>
+        <v>0.2895262129282173</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.685274416371861</v>
+        <v>2.680024127532906</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.738749013611613</v>
+        <v>-3.855981348400847</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.009656291914084</v>
+        <v>0.9627633579983903</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2298678807811575</v>
+        <v>0.2211173993828981</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.643433050141171</v>
+        <v>2.638182761302216</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.7322380469973</v>
+        <v>-3.849470381786534</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.009860640114126</v>
+        <v>0.9629677061984321</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2298678807811575</v>
+        <v>0.2211173993828981</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.641033011695488</v>
+        <v>2.635782722856532</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.713199919290003</v>
+        <v>-3.830432254079237</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.014000610405289</v>
+        <v>0.9671076764895958</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.171684269449963</v>
+        <v>0.1629337880517036</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.602647564105016</v>
+        <v>2.59739727526606</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.744326550440621</v>
+        <v>-3.861558885229855</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.179131826883723</v>
+        <v>1.132238892968029</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.171684269449963</v>
+        <v>0.1629337880517036</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.780229433043696</v>
+        <v>2.774979144204741</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.758193311774538</v>
+        <v>-3.875425646563772</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.174418451336289</v>
+        <v>1.127525517420596</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.13382635271614</v>
+        <v>0.1250758713178806</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.758348011989536</v>
+        <v>2.753097723150581</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.713389140234608</v>
+        <v>-3.830621475023842</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.198348650349187</v>
+        <v>1.151455716433494</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.13382635271614</v>
+        <v>0.1250758713178806</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764356542386462</v>
+        <v>2.759106253547507</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.565646169999606</v>
+        <v>-3.68287850478884</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.33659848623521</v>
+        <v>1.289705552319516</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3016337099510232</v>
+        <v>0.2928832285527638</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.944193604519414</v>
+        <v>2.938943315680458</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.667660852530827</v>
+        <v>-3.784893187320061</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.298586234754203</v>
+        <v>1.251693300838509</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3016337099510232</v>
+        <v>0.2928832285527638</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.946987226050895</v>
+        <v>2.941736937211939</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.661508146478043</v>
+        <v>-3.778740481267277</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.301709665566975</v>
+        <v>1.254816731651281</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3077864160038075</v>
+        <v>0.2990359346055481</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.951341198074224</v>
+        <v>2.946090909235268</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.678317444628544</v>
+        <v>-3.795549779417778</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.294066423046885</v>
+        <v>1.247173489131191</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2909771178533058</v>
+        <v>0.2822266364550464</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.940336095924033</v>
+        <v>2.935085807085077</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.616019445852422</v>
+        <v>-3.733251780641656</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.385321176354154</v>
+        <v>1.33842824243846</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2909771178533058</v>
+        <v>0.2822266364550464</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.006671649720854</v>
+        <v>3.001421360881898</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.414229248187264</v>
+        <v>-3.531461582976498</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.268329257134344</v>
+        <v>1.221436323218651</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4889953100224602</v>
+        <v>0.4802448286242008</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.927774566736474</v>
+        <v>2.922524277897518</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.340851151098528</v>
+        <v>-3.458083485887762</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.367970728292014</v>
+        <v>1.321077794376321</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5623734071111968</v>
+        <v>0.5536229257129374</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.042091657311891</v>
+        <v>3.036841368472935</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.438591695723502</v>
+        <v>-3.555824030512736</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.343502246558068</v>
+        <v>1.296609312642374</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5464841289782165</v>
+        <v>0.5377336475799572</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.047185826548146</v>
+        <v>3.041935537709191</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.614929455846431</v>
+        <v>-3.732161790635665</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.271503123333568</v>
+        <v>1.224610189417874</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3701463688552871</v>
+        <v>0.3613958874570278</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.939919151299061</v>
+        <v>2.934668862460105</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.538507409414505</v>
+        <v>-3.655739744203739</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.300563559946267</v>
+        <v>1.253670626030574</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3701463688552871</v>
+        <v>0.3613958874570278</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.938410769338989</v>
+        <v>2.933160480500034</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.494134277775936</v>
+        <v>-3.61136661256517</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.318175680037131</v>
+        <v>1.271282746121437</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4145195004938557</v>
+        <v>0.4057690190955964</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.964897515757566</v>
+        <v>2.95964722691861</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.371300056888769</v>
+        <v>-3.488532391678003</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.361703162530588</v>
+        <v>1.314810228614895</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4145195004938557</v>
+        <v>0.4057690190955964</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.959291309896157</v>
+        <v>2.954041021057201</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.323644326327713</v>
+        <v>-3.440876661116947</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.387147211782815</v>
+        <v>1.340254277867122</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4621752310549114</v>
+        <v>0.4534247496566521</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.994266505260595</v>
+        <v>2.989016216421639</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.223126167828958</v>
+        <v>-3.340358502618193</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.432246848557042</v>
+        <v>1.385353914641348</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5626933895536659</v>
+        <v>0.5539429081554066</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.059469773734572</v>
+        <v>3.054219484895617</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.283792758231348</v>
+        <v>-3.401025093020582</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.394734884871959</v>
+        <v>1.347841950956265</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4809950728351322</v>
+        <v>0.4722445914368729</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.997205456179324</v>
+        <v>2.991955167340369</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.23895435662295</v>
+        <v>-3.356186691412184</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.416767948125946</v>
+        <v>1.369875014210253</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4855385057800017</v>
+        <v>0.4767880243817424</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.004029218556875</v>
+        <v>2.998778929717919</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.339712992379948</v>
+        <v>-3.456945327169182</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.380625433454225</v>
+        <v>1.333732499538531</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3967129370529963</v>
+        <v>0.387962455654737</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.954894816951749</v>
+        <v>2.949644528112794</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.295510155294048</v>
+        <v>-3.412742490083282</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.404186170816422</v>
+        <v>1.357293236900729</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4409157741388967</v>
+        <v>0.4321652927406374</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.987296121731127</v>
+        <v>2.982045832892171</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.332489182957491</v>
+        <v>-3.449721517746725</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.387804560220292</v>
+        <v>1.340911626304599</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4778896759302272</v>
+        <v>0.469139194531968</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.007890463275173</v>
+        <v>3.002640174436217</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.174197765418219</v>
+        <v>-3.291430100207453</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.502368892419041</v>
+        <v>1.455475958503347</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4778896759302272</v>
+        <v>0.469139194531968</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.059138228458212</v>
+        <v>3.053887939619257</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.134267092240328</v>
+        <v>-3.251499427029562</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51678186628445</v>
+        <v>1.469888932368757</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5178203491081176</v>
+        <v>0.5090698677098583</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.0815373369592</v>
+        <v>3.076287048120244</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.0832349995178</v>
+        <v>-3.200467334307034</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.532142931611732</v>
+        <v>1.485249997696038</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5688524418306455</v>
+        <v>0.5601019604323862</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.107104820830986</v>
+        <v>3.101854531992031</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.018010818390595</v>
+        <v>-3.135243153179829</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.575420008155319</v>
+        <v>1.528527074239625</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6340766229578512</v>
+        <v>0.6253261415595919</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.163426733600015</v>
+        <v>3.158176444761059</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.980583798319461</v>
+        <v>-3.097816133108695</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.586351788483052</v>
+        <v>1.539458854567359</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6393281609870328</v>
+        <v>0.6305776795887735</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.162538628716804</v>
+        <v>3.157288339877848</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.000695454354169</v>
+        <v>-3.117927789143403</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.57956391840041</v>
+        <v>1.532670984484716</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.650355505984452</v>
+        <v>0.6416050245861927</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.170411828046496</v>
+        <v>3.16516153920754</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.946950639926964</v>
+        <v>-3.064182974716199</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.761619615192502</v>
+        <v>1.714726681276808</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.660418815424914</v>
+        <v>0.6516683340266547</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.337007584731984</v>
+        <v>3.331757295893028</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.923159071320822</v>
+        <v>-3.040391406110056</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.891249151852776</v>
+        <v>1.844356217937083</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.6842103840310563</v>
+        <v>0.675459902632797</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.471395435113486</v>
+        <v>3.466145146274531</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.897074987057014</v>
+        <v>-3.014307321846248</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.893390761572159</v>
+        <v>1.846497827656465</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.6842103840310563</v>
+        <v>0.675459902632797</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.463103411127345</v>
+        <v>3.45785312228839</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.818943806208067</v>
+        <v>-2.936176140997302</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.922836429495517</v>
+        <v>1.875943495579823</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7583871949147408</v>
+        <v>0.7496367135164815</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.505802693241336</v>
+        <v>3.50055240440238</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.810051344814784</v>
+        <v>-2.927283679604018</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.943947819779622</v>
+        <v>1.897054885863928</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7583871949147408</v>
+        <v>0.7496367135164815</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.523357098968127</v>
+        <v>3.518106810129171</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.978527461784662</v>
+        <v>-3.095759796573896</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.868412420396254</v>
+        <v>1.82151948648056</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7304393591981601</v>
+        <v>0.7216888777999008</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.498443444942763</v>
+        <v>3.493193156103807</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.280727932923079</v>
+        <v>-2.463787647100961</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.128801929128749</v>
+        <v>2.055578043457596</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6600912998277493</v>
+        <v>0.7659978235774041</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.437504306508378</v>
+        <v>3.501048220758171</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.258006829239926</v>
+        <v>-2.441066543417809</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.128554393098915</v>
+        <v>2.055330507427762</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6600912998277493</v>
+        <v>0.7659978235774041</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.428168329005282</v>
+        <v>3.491712243255075</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.256281785949882</v>
+        <v>-2.439341500127765</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.288150536266102</v>
+        <v>2.214926650594949</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.661816343117793</v>
+        <v>0.7677228668674478</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.588109480830478</v>
+        <v>3.651653395080271</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.411062792728138</v>
+        <v>-2.59412250690602</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.263315956048446</v>
+        <v>2.190092070377293</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6284486690633169</v>
+        <v>0.7343551928129717</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.605166698891439</v>
+        <v>3.668710613141231</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.359627459343478</v>
+        <v>-2.54268717352136</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.280565445391855</v>
+        <v>2.207341559720702</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6798840024479765</v>
+        <v>0.7857905261976313</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.632703254911779</v>
+        <v>3.696247169161572</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.33267623501699</v>
+        <v>-2.515735949194872</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.301352088767191</v>
+        <v>2.228128203096039</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6947643484756957</v>
+        <v>0.8006708722253505</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.651637616173153</v>
+        <v>3.715181530422945</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.418882139232695</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.468629243073306</v>
+        <v>-2.651688957251189</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.431074017689625</v>
+        <v>2.357850132018472</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6947643484756957</v>
+        <v>0.8006708722253505</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.835740748318112</v>
+        <v>3.899284662567905</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.410998834135688</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.491037360878178</v>
+        <v>-2.674097075056061</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.414227465470669</v>
+        <v>2.341003579799517</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6947643484756957</v>
+        <v>0.8006708722253505</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.827857443221105</v>
+        <v>3.891401357470898</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.413052833685325</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.639043128357578</v>
+        <v>-2.82210284253546</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.357079158028547</v>
+        <v>2.283855272357394</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6080373396121542</v>
+        <v>0.713943863361809</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.777875237452618</v>
+        <v>3.841419151702411</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.469306551407172</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.648484054246108</v>
+        <v>-2.83154376842399</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.409556505394982</v>
+        <v>2.336332619723829</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7304644571555456</v>
+        <v>0.8363709809052005</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.9075852257005</v>
+        <v>3.971129139950293</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.472197645952473</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.647197290706552</v>
+        <v>-2.830257004884434</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.412962305356105</v>
+        <v>2.339738419684952</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7317512206951022</v>
+        <v>0.837657744444757</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.911248378369535</v>
+        <v>3.974792292619328</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.470309458846248</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.648754344695843</v>
+        <v>-2.831814058873725</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.410451296654164</v>
+        <v>2.337227410983011</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7317512206951022</v>
+        <v>0.837657744444757</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.90936019126331</v>
+        <v>3.972904105513103</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.465129688449111</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.656026230219307</v>
+        <v>-2.83908594439719</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.402362772047641</v>
+        <v>2.329138886376488</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7244793351716374</v>
+        <v>0.8303858589212922</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.899817289552094</v>
+        <v>3.963361203801886</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.463563698659263</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.654185211161056</v>
+        <v>-2.837244925338938</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.401533189881094</v>
+        <v>2.328309304209941</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7257475618431058</v>
+        <v>0.8316540855927607</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.899012235765127</v>
+        <v>3.96255615001492</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.476637105525182</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.661093916660737</v>
+        <v>-2.844153630838619</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.41184311454714</v>
+        <v>2.338619228875987</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7257475618431058</v>
+        <v>0.8316540855927607</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.912085642631046</v>
+        <v>3.975629556880838</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.476637105525182</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.662655559475597</v>
+        <v>-2.845715273653479</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.411218457421196</v>
+        <v>2.337994571750043</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7257475618431058</v>
+        <v>0.8316540855927607</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.912085642631046</v>
+        <v>3.975629556880838</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.475161146652184</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.690556346585069</v>
+        <v>-2.873616060762952</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.398582183704408</v>
+        <v>2.325358298033255</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.691150637700171</v>
+        <v>0.7970571614498259</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.889851529272287</v>
+        <v>3.953395443522079</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.471925590629382</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.693589344097743</v>
+        <v>-2.876649058275626</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.394133428676538</v>
+        <v>2.320909543005385</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6881176401874971</v>
+        <v>0.7940241639371519</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.884796174741881</v>
+        <v>3.948340088991674</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.538631550219886</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.71365066537425</v>
+        <v>-2.896710379552133</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.452814859756439</v>
+        <v>2.379590974085286</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.66805631891099</v>
+        <v>0.7739628426606449</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.93946534156648</v>
+        <v>4.003009255816274</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.678943269221733</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.970371483369074</v>
+        <v>-3.153431197546956</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.490438251560356</v>
+        <v>2.417214365889203</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5596417447671752</v>
+        <v>0.66554826851683</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.014728316082039</v>
+        <v>4.078272230331831</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.747923538367373</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.124357901145215</v>
+        <v>-3.307417615323097</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.49782395359554</v>
+        <v>2.424600067924387</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5596417447671752</v>
+        <v>0.66554826851683</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.083708585227678</v>
+        <v>4.147252499477471</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.61993717680853</v>
       </c>
       <c r="C2018" t="n">
         <v>3.733974740487494</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.073835997317549</v>
+        <v>-3.461717548745457</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.504083917246727</v>
+        <v>2.348931296675564</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5596417447671752</v>
+        <v>0.66554826851683</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.069759787347799</v>
+        <v>4.133303701597592</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.882624087613461</v>
+        <v>3.383545407410415</v>
       </c>
       <c r="C2019" t="n">
-        <v>4.012700163877915</v>
+        <v>3.649130140888486</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.073835997317549</v>
+        <v>-3.461717548745457</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.504083917246727</v>
+        <v>2.348931296675564</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5596417447671752</v>
+        <v>0.66554826851683</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.005763960864282</v>
+        <v>3.642193937874854</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>458.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.7%</t>
+          <t>-484.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-141.3%</t>
+          <t>-116.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.2%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-183.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-81.8%</t>
+          <t>-32.4%</t>
         </is>
       </c>
     </row>
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.263585023793153</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8669601114478556</v>
+        <v>0.8104674714551243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4390192984555826</v>
+        <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.709338966205515</v>
+        <v>2.624600006216418</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.199949281559219</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8971092093957469</v>
+        <v>0.8406165694030152</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3753835562216481</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.752215212600193</v>
+        <v>2.667476252611096</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.088522522233299</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9228741719099105</v>
+        <v>0.8663815319171788</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3753835562216481</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.733409471383989</v>
+        <v>2.648670511394891</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.848092025428438</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.020789447256732</v>
+        <v>0.9642968072640004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1349530594167878</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.879410846091782</v>
+        <v>2.794671886102685</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.775849457257244</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.05361578836003</v>
+        <v>0.9971231483672984</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1349530594167878</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.883340159926602</v>
+        <v>2.798601199937505</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.722851134975856</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.075493701189925</v>
+        <v>1.019001061197194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07961680041484898</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.917220499245106</v>
+        <v>2.832481539256008</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.614046249496129</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.11601372660181</v>
+        <v>1.059521086609078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07961680041484898</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.914218570465099</v>
+        <v>2.829479610476002</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.394025451459118</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.205601082827228</v>
+        <v>1.149108442834496</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06160304465313127</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.000529514516502</v>
+        <v>2.915790554527404</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.261157762395841</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.274642341254362</v>
+        <v>1.218149701261631</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06160304465313127</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.016423697318325</v>
+        <v>2.931684737329228</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.140984679031342</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.323857419040464</v>
+        <v>1.267364779047732</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1817761280176302</v>
+        <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.089673391777326</v>
+        <v>3.004934431788229</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.996312533931604</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.391814379641799</v>
+        <v>1.335321739649067</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3264482731173676</v>
+        <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.186564781398608</v>
+        <v>3.101825821409511</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.056187361289297</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.353901940100147</v>
+        <v>1.297409300107416</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2665734457596755</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.136677376385419</v>
+        <v>3.051938416396322</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.936367130378459</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.417119201698691</v>
+        <v>1.360626561705959</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2665734457596755</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.151966545619628</v>
+        <v>3.06722758563053</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.938836836840265</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.32377551843641</v>
+        <v>1.267282878443678</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2641037392978693</v>
+        <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.058128921064985</v>
+        <v>2.973389961075888</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.007207023164275</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.215689305392107</v>
+        <v>1.159196665399375</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2733794383340843</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.982956201972016</v>
+        <v>2.898217241982918</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.020995076011322</v>
+        <v>-4.162226675993152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.20061079288518</v>
+        <v>1.144118152892448</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2733794383340843</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.973392910603907</v>
+        <v>2.88865395061481</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.051988235340027</v>
+        <v>-4.193219835321857</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.012923094194085</v>
+        <v>0.9564304542013529</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2733794383340843</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.798102475644294</v>
+        <v>2.713363515655197</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.876513975547558</v>
+        <v>-4.017745575529387</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.08768003010286</v>
+        <v>1.031187390110128</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2733794383340843</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.802669707636082</v>
+        <v>2.717930747646984</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.987450228188806</v>
+        <v>-4.128681828170636</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.019047557807568</v>
+        <v>0.962554917814836</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2733794383340843</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.778411736397289</v>
+        <v>2.693672776408191</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.953786682716525</v>
+        <v>-4.095018282698354</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.035644361216386</v>
+        <v>0.9791517212236545</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3070429838063661</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.801741248900563</v>
+        <v>2.717002288911466</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.893934063512801</v>
+        <v>-4.035165663494631</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.069757795330008</v>
+        <v>1.013265155337276</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3070429838063661</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.811913635332695</v>
+        <v>2.727174675343599</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.807690600486424</v>
+        <v>-3.948922200468253</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.099201451114419</v>
+        <v>1.042708811121687</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3070429838063661</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.806859905906556</v>
+        <v>2.722120945917459</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.852997419885404</v>
+        <v>-3.994229019867233</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.072854498799353</v>
+        <v>1.016361858806621</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2662328207971353</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.774149583545543</v>
+        <v>2.689410623556446</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.882030524587706</v>
+        <v>-4.023262124569534</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.061793129951534</v>
+        <v>1.005300489958802</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2662328207971353</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.774701456578645</v>
+        <v>2.689962496589547</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.789220043136846</v>
+        <v>-3.930451643118675</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.028190014423243</v>
+        <v>0.9716973744305115</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3590433022479947</v>
+        <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.759660437340526</v>
+        <v>2.674921477351428</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.833609512466274</v>
+        <v>-3.974841112448102</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.012307702616073</v>
+        <v>0.9558150626233413</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.314653832918567</v>
+        <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.73490023166747</v>
+        <v>2.650161271678373</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.720938294230024</v>
+        <v>-3.862169894211852</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.052451898422296</v>
+        <v>0.9959592584295645</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4273250511548172</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.797578671120943</v>
+        <v>2.712839711131846</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.608561293047351</v>
+        <v>-3.74979289302918</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.102893994726032</v>
+        <v>1.046401354733301</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4273250511548172</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.80306996695161</v>
+        <v>2.718331006962513</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.636341690948704</v>
+        <v>-3.777573290930533</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.10327903733403</v>
+        <v>1.046786397341299</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3995446532534642</v>
+        <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.797898929979338</v>
+        <v>2.71315996999024</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.719342971973983</v>
+        <v>-3.860574571955812</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9084342449245715</v>
+        <v>0.8519416049318402</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3809737687262904</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.625112119263687</v>
+        <v>2.540373159274589</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.827957050417314</v>
+        <v>-3.969188650399143</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9851382742664447</v>
+        <v>0.9286456342737133</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3809737687262904</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.745261779982892</v>
+        <v>2.660522819993795</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.792548012169171</v>
+        <v>-3.802635524265488</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.013814915668025</v>
+        <v>1.009779910829498</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3809737687262904</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.759774806085215</v>
+        <v>2.675035846096118</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.75416434961102</v>
+        <v>-3.764251861707337</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.026587822033654</v>
+        <v>1.022552817195127</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4193574312844416</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.780224444962474</v>
+        <v>2.695485484973378</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.577048019575854</v>
+        <v>-3.587135531672171</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.094163382893023</v>
+        <v>1.090128378054496</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4193574312844416</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.776953473807777</v>
+        <v>2.69221451381868</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.6221402644094</v>
+        <v>-3.632227776505716</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.076809876721518</v>
+        <v>1.072774871882991</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3574613881150518</v>
+        <v>0.2162297881332231</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.740499239668056</v>
+        <v>2.655760279678959</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.442764843170632</v>
+        <v>-3.452852355266948</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.142347020523439</v>
+        <v>1.138312015684913</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5142381462857705</v>
+        <v>0.3730065463039418</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.828352269876902</v>
+        <v>2.743613309887805</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.487779056691239</v>
+        <v>-3.497866568787555</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.105148790446786</v>
+        <v>1.10111378560826</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4838892509711659</v>
+        <v>0.3426576509893372</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.790950388019729</v>
+        <v>2.706211428030632</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.754783566963674</v>
+        <v>-3.76487107905999</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.004038548676758</v>
+        <v>1.000003543838232</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2895262129282173</v>
+        <v>0.1482946129463886</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.680024127532906</v>
+        <v>2.595285167543808</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.855981348400847</v>
+        <v>-3.866068860497163</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9627633579983903</v>
+        <v>0.9587283531598638</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2211173993828981</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.638182761302216</v>
+        <v>2.553443801313118</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.849470381786534</v>
+        <v>-3.85955789388285</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9629677061984321</v>
+        <v>0.9589327013599056</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2211173993828981</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.635782722856532</v>
+        <v>2.551043762867435</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.830432254079237</v>
+        <v>-3.840519766175553</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9671076764895958</v>
+        <v>0.9630726716510694</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1629337880517036</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.59739727526606</v>
+        <v>2.512658315276963</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.861558885229855</v>
+        <v>-3.871646397326171</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.132238892968029</v>
+        <v>1.128203888129503</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1629337880517036</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.774979144204741</v>
+        <v>2.690240184215644</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.875425646563772</v>
+        <v>-3.885513158660088</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.127525517420596</v>
+        <v>1.123490512582069</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1250758713178806</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.753097723150581</v>
+        <v>2.668358763161483</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.830621475023842</v>
+        <v>-3.840708987120158</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.151455716433494</v>
+        <v>1.147420711594967</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1250758713178806</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.759106253547507</v>
+        <v>2.674367293558409</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.68287850478884</v>
+        <v>-3.692966016885156</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.289705552319516</v>
+        <v>1.28567054748099</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2928832285527638</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.938943315680458</v>
+        <v>2.854204355691361</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.784893187320061</v>
+        <v>-3.794980699416377</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.251693300838509</v>
+        <v>1.247658295999983</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2928832285527638</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.941736937211939</v>
+        <v>2.856997977222842</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.778740481267277</v>
+        <v>-3.788827993363593</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.254816731651281</v>
+        <v>1.250781726812755</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2990359346055481</v>
+        <v>0.1578043346237194</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.946090909235268</v>
+        <v>2.861351949246171</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.795549779417778</v>
+        <v>-3.805637291514094</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.247173489131191</v>
+        <v>1.243138484292664</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2822266364550464</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.935085807085077</v>
+        <v>2.85034684709598</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.733251780641656</v>
+        <v>-3.743339292737972</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.33842824243846</v>
+        <v>1.334393237599934</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2822266364550464</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.001421360881898</v>
+        <v>2.916682400892801</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.531461582976498</v>
+        <v>-3.541549095072814</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.221436323218651</v>
+        <v>1.217401318380124</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4802448286242008</v>
+        <v>0.3390132286423722</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.922524277897518</v>
+        <v>2.837785317908421</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.458083485887762</v>
+        <v>-3.468170997984078</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.321077794376321</v>
+        <v>1.317042789537794</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5536229257129374</v>
+        <v>0.4123913257311087</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.036841368472935</v>
+        <v>2.952102408483838</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.555824030512736</v>
+        <v>-3.565911542609052</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.296609312642374</v>
+        <v>1.292574307803848</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5377336475799572</v>
+        <v>0.3965020475981285</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.041935537709191</v>
+        <v>2.957196577720094</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.732161790635665</v>
+        <v>-3.742249302731981</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.224610189417874</v>
+        <v>1.220575184579348</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3613958874570278</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.934668862460105</v>
+        <v>2.849929902471008</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.655739744203739</v>
+        <v>-3.665827256300055</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.253670626030574</v>
+        <v>1.249635621192047</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3613958874570278</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.933160480500034</v>
+        <v>2.848421520510936</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.61136661256517</v>
+        <v>-3.621454124661486</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.271282746121437</v>
+        <v>1.267247741282911</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4057690190955964</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.95964722691861</v>
+        <v>2.874908266929514</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.488532391678003</v>
+        <v>-3.498619903774319</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.314810228614895</v>
+        <v>1.310775223776368</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4057690190955964</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.954041021057201</v>
+        <v>2.869302061068104</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.440876661116947</v>
+        <v>-3.450964173213263</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.340254277867122</v>
+        <v>1.336219273028595</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4534247496566521</v>
+        <v>0.3121931496748234</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.989016216421639</v>
+        <v>2.904277256432542</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.340358502618193</v>
+        <v>-3.350446014714509</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.385353914641348</v>
+        <v>1.381318909802822</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5539429081554066</v>
+        <v>0.4127113081735779</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.054219484895617</v>
+        <v>2.969480524906519</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.401025093020582</v>
+        <v>-3.411112605116898</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.347841950956265</v>
+        <v>1.343806946117738</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4722445914368729</v>
+        <v>0.3310129914550443</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.991955167340369</v>
+        <v>2.907216207351272</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.356186691412184</v>
+        <v>-3.3662742035085</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.369875014210253</v>
+        <v>1.365840009371726</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4767880243817424</v>
+        <v>0.3355564243999137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.998778929717919</v>
+        <v>2.914039969728822</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.456945327169182</v>
+        <v>-3.467032839265498</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.333732499538531</v>
+        <v>1.329697494700005</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.387962455654737</v>
+        <v>0.2467308556729083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.949644528112794</v>
+        <v>2.864905568123697</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.412742490083282</v>
+        <v>-3.422830002179598</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.357293236900729</v>
+        <v>1.353258232062202</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4321652927406374</v>
+        <v>0.2909336927588088</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.982045832892171</v>
+        <v>2.897306872903074</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.449721517746725</v>
+        <v>-3.459809029843041</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.340911626304599</v>
+        <v>1.336876621466073</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.469139194531968</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.002640174436217</v>
+        <v>2.91790121444712</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.291430100207453</v>
+        <v>-3.301517612303769</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.455475958503347</v>
+        <v>1.451440953664821</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.469139194531968</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.053887939619257</v>
+        <v>2.96914897963016</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.251499427029562</v>
+        <v>-3.261586939125878</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.469888932368757</v>
+        <v>1.46585392753023</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5090698677098583</v>
+        <v>0.3678382677280296</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.076287048120244</v>
+        <v>2.991548088131147</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.200467334307034</v>
+        <v>-3.21055484640335</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.485249997696038</v>
+        <v>1.481214992857512</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5601019604323862</v>
+        <v>0.4188703604505576</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.101854531992031</v>
+        <v>3.017115572002933</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.135243153179829</v>
+        <v>-3.145330665276145</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.528527074239625</v>
+        <v>1.524492069401099</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6253261415595919</v>
+        <v>0.4840945415777632</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.158176444761059</v>
+        <v>3.073437484771962</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.097816133108695</v>
+        <v>-3.107903645205011</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.539458854567359</v>
+        <v>1.535423849728832</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6305776795887735</v>
+        <v>0.4893460796069449</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.157288339877848</v>
+        <v>3.072549379888752</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.117927789143403</v>
+        <v>-3.128015301239719</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.532670984484716</v>
+        <v>1.528635979646189</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6416050245861927</v>
+        <v>0.5003734246043641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.16516153920754</v>
+        <v>3.080422579218443</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.064182974716199</v>
+        <v>-3.074270486812515</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.714726681276808</v>
+        <v>1.710691676438282</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6516683340266547</v>
+        <v>0.510436734044826</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.331757295893028</v>
+        <v>3.247018335903931</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.040391406110056</v>
+        <v>-3.050478918206372</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.844356217937083</v>
+        <v>1.840321213098556</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.675459902632797</v>
+        <v>0.5342283026509683</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.466145146274531</v>
+        <v>3.381406186285434</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.014307321846248</v>
+        <v>-3.024394833942564</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.846497827656465</v>
+        <v>1.842462822817938</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.675459902632797</v>
+        <v>0.5342283026509683</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.45785312228839</v>
+        <v>3.373114162299293</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.936176140997302</v>
+        <v>-2.946263653093617</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.875943495579823</v>
+        <v>1.871908490741297</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7496367135164815</v>
+        <v>0.6084051135346529</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.50055240440238</v>
+        <v>3.415813444413283</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.927283679604018</v>
+        <v>-2.937371191700334</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.897054885863928</v>
+        <v>1.893019881025401</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7496367135164815</v>
+        <v>0.6084051135346529</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.518106810129171</v>
+        <v>3.433367850140074</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.095759796573896</v>
+        <v>-3.105847308670212</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.82151948648056</v>
+        <v>1.817484481642034</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7216888777999008</v>
+        <v>0.5804572778180721</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.493193156103807</v>
+        <v>3.40845419611471</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.463787647100961</v>
+        <v>-2.408047779808629</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.055578043457596</v>
+        <v>2.077873990374529</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.7659978235774041</v>
+        <v>0.5101092184476614</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.501048220758171</v>
+        <v>3.347515057680325</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.441066543417809</v>
+        <v>-2.385326676125477</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.055330507427762</v>
+        <v>2.077626454344695</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.7659978235774041</v>
+        <v>0.5101092184476614</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.491712243255075</v>
+        <v>3.33817908017723</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.439341500127765</v>
+        <v>-2.383601632835433</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.214926650594949</v>
+        <v>2.237222597511881</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7677228668674478</v>
+        <v>0.5118342617377052</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.651653395080271</v>
+        <v>3.498120232002425</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.59412250690602</v>
+        <v>-2.538382639613688</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.190092070377293</v>
+        <v>2.212388017294226</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7343551928129717</v>
+        <v>0.4784665876832291</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.668710613141231</v>
+        <v>3.515177450063386</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.54268717352136</v>
+        <v>-2.486947306229028</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.207341559720702</v>
+        <v>2.229637506637635</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7857905261976313</v>
+        <v>0.5299019210678888</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.696247169161572</v>
+        <v>3.542714006083727</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.515735949194872</v>
+        <v>-2.45999608190254</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.228128203096039</v>
+        <v>2.250424150012972</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8006708722253505</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.715181530422945</v>
+        <v>3.5616483673451</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.418882139232695</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.651688957251189</v>
+        <v>-2.343025051192805</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.357850132018472</v>
+        <v>2.481315694441826</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8006708722253505</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.899284662567905</v>
+        <v>3.74575149949006</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.410998834135688</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.674097075056061</v>
+        <v>-2.365433168997677</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.341003579799517</v>
+        <v>2.46446914222287</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8006708722253505</v>
+        <v>0.544782267095608</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.891401357470898</v>
+        <v>3.737868194393053</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.413052833685325</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.82210284253546</v>
+        <v>-2.513438936477076</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.283855272357394</v>
+        <v>2.407320834780748</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.713943863361809</v>
+        <v>0.4580552582320665</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.841419151702411</v>
+        <v>3.687885988624565</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.469306551407172</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.83154376842399</v>
+        <v>-2.522879862365606</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.336332619723829</v>
+        <v>2.459798182147183</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8363709809052005</v>
+        <v>0.5804823757754579</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.971129139950293</v>
+        <v>3.817595976872447</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.472197645952473</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.830257004884434</v>
+        <v>-2.52159309882605</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.339738419684952</v>
+        <v>2.463203982108306</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.837657744444757</v>
+        <v>0.5817691393150145</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.974792292619328</v>
+        <v>3.821259129541482</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.470309458846248</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.831814058873725</v>
+        <v>-2.523150152815341</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.337227410983011</v>
+        <v>2.460692973406365</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.837657744444757</v>
+        <v>0.5817691393150145</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.972904105513103</v>
+        <v>3.819370942435258</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.465129688449111</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.83908594439719</v>
+        <v>-2.530422038338806</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.329138886376488</v>
+        <v>2.452604448799841</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8303858589212922</v>
+        <v>0.5744972537915498</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.963361203801886</v>
+        <v>3.809828040724041</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.463563698659263</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.837244925338938</v>
+        <v>-2.528581019280554</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.328309304209941</v>
+        <v>2.451774866633294</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8316540855927607</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.96255615001492</v>
+        <v>3.809022986937074</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.476637105525182</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.844153630838619</v>
+        <v>-2.535489724780235</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.338619228875987</v>
+        <v>2.462084791299341</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8316540855927607</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.975629556880838</v>
+        <v>3.822096393802993</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.476637105525182</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.845715273653479</v>
+        <v>-2.537051367595095</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.337994571750043</v>
+        <v>2.461460134173397</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8316540855927607</v>
+        <v>0.5757654804630182</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.975629556880838</v>
+        <v>3.822096393802993</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.475161146652184</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.873616060762952</v>
+        <v>-2.564952154704568</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.325358298033255</v>
+        <v>2.448823860456609</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7970571614498259</v>
+        <v>0.5411685563200834</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.953395443522079</v>
+        <v>3.799862280444234</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.471925590629382</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.876649058275626</v>
+        <v>-2.567985152217242</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.320909543005385</v>
+        <v>2.444375105428739</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7940241639371519</v>
+        <v>0.5381355588074095</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.948340088991674</v>
+        <v>3.794806925913829</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.538631550219886</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.896710379552133</v>
+        <v>-2.588046473493749</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.379590974085286</v>
+        <v>2.503056536508639</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7739628426606449</v>
+        <v>0.5180742375309024</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.003009255816274</v>
+        <v>3.849476092738428</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.678943269221733</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.153431197546956</v>
+        <v>-2.844767291488572</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.417214365889203</v>
+        <v>2.540679928312557</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.66554826851683</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.078272230331831</v>
+        <v>3.924739067253986</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.747923538367373</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.307417615323097</v>
+        <v>-2.998753709264713</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.424600067924387</v>
+        <v>2.54806563034774</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.66554826851683</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.147252499477471</v>
+        <v>3.993719336399626</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.733974740487494</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.461717548745457</v>
+        <v>-2.948231805437047</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.348931296675564</v>
+        <v>2.554325593998928</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.66554826851683</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.133303701597592</v>
+        <v>3.979770538519746</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.383545407410415</v>
+        <v>3.764135327642467</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.649130140888486</v>
+        <v>3.890183167333197</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.461717548745457</v>
+        <v>-3.228501825877023</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.348931296675564</v>
+        <v>2.598426012668641</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.66554826851683</v>
+        <v>0.4096596633870876</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.642193937874854</v>
+        <v>4.13597896536545</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240708.xlsx
+++ b/tame_output/ON/bt/strategyON_20240708.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.1%</t>
+          <t>458.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-484.4%</t>
+          <t>-496.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-116.4%</t>
+          <t>-135.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.802635524265488</v>
+        <v>-3.933779612151</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.009779910829498</v>
+        <v>0.9573222756752935</v>
       </c>
       <c r="F1953" t="n">
         <v>0.2397421687444617</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.764251861707337</v>
+        <v>-3.895395949592849</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.022552817195127</v>
+        <v>0.9700951820409225</v>
       </c>
       <c r="F1954" t="n">
         <v>0.2781258313026129</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.587135531672171</v>
+        <v>-3.718279619557683</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.090128378054496</v>
+        <v>1.037670742900291</v>
       </c>
       <c r="F1955" t="n">
         <v>0.2781258313026129</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.632227776505716</v>
+        <v>-3.763371864391228</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.072774871882991</v>
+        <v>1.020317236728786</v>
       </c>
       <c r="F1956" t="n">
         <v>0.2162297881332231</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.452852355266948</v>
+        <v>-3.58399644315246</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.138312015684913</v>
+        <v>1.085854380530708</v>
       </c>
       <c r="F1957" t="n">
         <v>0.3730065463039418</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.497866568787555</v>
+        <v>-3.629010656673067</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.10111378560826</v>
+        <v>1.048656150454055</v>
       </c>
       <c r="F1958" t="n">
         <v>0.3426576509893372</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.76487107905999</v>
+        <v>-3.896015166945502</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.000003543838232</v>
+        <v>0.9475459086840265</v>
       </c>
       <c r="F1959" t="n">
         <v>0.1482946129463886</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.866068860497163</v>
+        <v>-3.997212948382675</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9587283531598638</v>
+        <v>0.9062707180056591</v>
       </c>
       <c r="F1960" t="n">
         <v>0.07988579940106943</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.85955789388285</v>
+        <v>-3.990701981768362</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9589327013599056</v>
+        <v>0.9064750662057008</v>
       </c>
       <c r="F1961" t="n">
         <v>0.07988579940106943</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.840519766175553</v>
+        <v>-3.971663854061065</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9630726716510694</v>
+        <v>0.9106150364968646</v>
       </c>
       <c r="F1962" t="n">
         <v>0.02170218806987489</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.871646397326171</v>
+        <v>-4.002790485211683</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.128203888129503</v>
+        <v>1.075746252975298</v>
       </c>
       <c r="F1963" t="n">
         <v>0.02170218806987489</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.885513158660088</v>
+        <v>-4.0166572465456</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.123490512582069</v>
+        <v>1.071032877427865</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.01615572866394804</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.840708987120158</v>
+        <v>-3.97185307500567</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.147420711594967</v>
+        <v>1.094963076440763</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.01615572866394804</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519914</v>
       </c>
       <c r="C1966" t="n">
         <v>2.7632133785488</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.692966016885156</v>
+        <v>-3.824110104770668</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.28567054748099</v>
+        <v>1.233212912326785</v>
       </c>
       <c r="F1966" t="n">
         <v>0.1516516285709351</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181176</v>
       </c>
       <c r="C1967" t="n">
         <v>2.766007000080281</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.794980699416377</v>
+        <v>-3.926124787301889</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.247658295999983</v>
+        <v>1.195200660845778</v>
       </c>
       <c r="F1967" t="n">
         <v>0.1516516285709351</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394735</v>
       </c>
       <c r="C1968" t="n">
         <v>2.766669348471939</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.788827993363593</v>
+        <v>-3.919972081249105</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.250781726812755</v>
+        <v>1.19832409165855</v>
       </c>
       <c r="F1968" t="n">
         <v>0.1578043346237194</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.765749825212049</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.805637291514094</v>
+        <v>-3.936781379399606</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.243138484292664</v>
+        <v>1.19068084913846</v>
       </c>
       <c r="F1969" t="n">
         <v>0.1409950364732178</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>2.83208537900887</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.743339292737972</v>
+        <v>-3.874483380623484</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.334393237599934</v>
+        <v>1.281935602445729</v>
       </c>
       <c r="F1970" t="n">
         <v>0.1409950364732178</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
         <v>2.634377380722997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.541549095072814</v>
+        <v>-3.672693182958326</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.217401318380124</v>
+        <v>1.164943683225919</v>
       </c>
       <c r="F1971" t="n">
         <v>0.3390132286423722</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.704667613045173</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.468170997984078</v>
+        <v>-3.59931508586959</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.317042789537794</v>
+        <v>1.264585154383589</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4123913257311087</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.719295349161216</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.565911542609052</v>
+        <v>-3.697055630494564</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.292574307803848</v>
+        <v>1.240116672649643</v>
       </c>
       <c r="F1973" t="n">
         <v>0.3965020475981285</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.717831329985888</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.742249302731981</v>
+        <v>-3.873393390617494</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.220575184579348</v>
+        <v>1.168117549425143</v>
       </c>
       <c r="F1974" t="n">
         <v>0.2201642874751991</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.716322948025816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.665827256300055</v>
+        <v>-3.796971344185567</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.249635621192047</v>
+        <v>1.197177986037842</v>
       </c>
       <c r="F1975" t="n">
         <v>0.2201642874751991</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
         <v>2.716185815461253</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.621454124661486</v>
+        <v>-3.752598212546998</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.267247741282911</v>
+        <v>1.214790106128706</v>
       </c>
       <c r="F1976" t="n">
         <v>0.2645374191137677</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.710579609599843</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.498619903774319</v>
+        <v>-3.629763991659831</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.310775223776368</v>
+        <v>1.258317588622164</v>
       </c>
       <c r="F1977" t="n">
         <v>0.2645374191137677</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.716961366627648</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.450964173213263</v>
+        <v>-3.582108261098775</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.336219273028595</v>
+        <v>1.28376163787439</v>
       </c>
       <c r="F1978" t="n">
         <v>0.3121931496748234</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.721853740002373</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.350446014714509</v>
+        <v>-3.481590102600021</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.381318909802822</v>
+        <v>1.328861274648617</v>
       </c>
       <c r="F1979" t="n">
         <v>0.4127113081735779</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.708608412478245</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.411112605116898</v>
+        <v>-3.54225669300241</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.343806946117738</v>
+        <v>1.291349310963534</v>
       </c>
       <c r="F1980" t="n">
         <v>0.3310129914550443</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.712706115088873</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.3662742035085</v>
+        <v>-3.497418291394012</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.365840009371726</v>
+        <v>1.313382374217521</v>
       </c>
       <c r="F1981" t="n">
         <v>0.3355564243999137</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917052</v>
       </c>
       <c r="C1982" t="n">
         <v>2.716867054719951</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.467032839265498</v>
+        <v>-3.59817692715101</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.329697494700005</v>
+        <v>1.2772398595458</v>
       </c>
       <c r="F1982" t="n">
         <v>0.2467308556729083</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.722746657247789</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.422830002179598</v>
+        <v>-3.55397409006511</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.353258232062202</v>
+        <v>1.300800596907997</v>
       </c>
       <c r="F1983" t="n">
         <v>0.2909336927588088</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.721156657717036</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.459809029843041</v>
+        <v>-3.590953117728553</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.336876621466073</v>
+        <v>1.284418986311868</v>
       </c>
       <c r="F1984" t="n">
         <v>0.3279075945501393</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.772404422900076</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.301517612303769</v>
+        <v>-3.432661700189281</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.451440953664821</v>
+        <v>1.398983318510616</v>
       </c>
       <c r="F1985" t="n">
         <v>0.3279075945501393</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.770845127494329</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.261586939125878</v>
+        <v>-3.39273102701139</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.46585392753023</v>
+        <v>1.413396292376025</v>
       </c>
       <c r="F1986" t="n">
         <v>0.3678382677280296</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.765793355732599</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.21055484640335</v>
+        <v>-3.341698934288862</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.481214992857512</v>
+        <v>1.428757357703307</v>
       </c>
       <c r="F1987" t="n">
         <v>0.4188703604505576</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
         <v>2.782980759825304</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.145330665276145</v>
+        <v>-3.276474753161657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.524492069401099</v>
+        <v>1.472034434246894</v>
       </c>
       <c r="F1988" t="n">
         <v>0.4840945415777632</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.778941732124584</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.107903645205011</v>
+        <v>-3.239047733090523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.535423849728832</v>
+        <v>1.482966214574628</v>
       </c>
       <c r="F1989" t="n">
         <v>0.4893460796069449</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.780198524455824</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.128015301239719</v>
+        <v>-3.259159389125232</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.528635979646189</v>
+        <v>1.476178344491985</v>
       </c>
       <c r="F1990" t="n">
         <v>0.5003734246043641</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.940756295477035</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.074270486812515</v>
+        <v>-3.205414574698027</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.710691676438282</v>
+        <v>1.658234041284077</v>
       </c>
       <c r="F1991" t="n">
         <v>0.510436734044826</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>3.060869204694852</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.050478918206372</v>
+        <v>-3.181623006091884</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.840321213098556</v>
+        <v>1.787863577944351</v>
       </c>
       <c r="F1992" t="n">
         <v>0.5342283026509683</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.052577180708711</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.024394833942564</v>
+        <v>-3.155538921828076</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.842462822817938</v>
+        <v>1.790005187663734</v>
       </c>
       <c r="F1993" t="n">
         <v>0.5342283026509683</v>
@@ -47413,10 +47413,10 @@
         <v>3.050770376292491</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.946263653093617</v>
+        <v>-3.07740774097913</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.871908490741297</v>
+        <v>1.819450855587092</v>
       </c>
       <c r="F1994" t="n">
         <v>0.6084051135346529</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.068324782019282</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.937371191700334</v>
+        <v>-3.068515279585847</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.893019881025401</v>
+        <v>1.840562245871196</v>
       </c>
       <c r="F1995" t="n">
         <v>0.6084051135346529</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>3.060179829423866</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.105847308670212</v>
+        <v>-3.236991396555724</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.817484481642034</v>
+        <v>1.765026846487829</v>
       </c>
       <c r="F1996" t="n">
         <v>0.5804572778180721</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.041449526611728</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.408047779808629</v>
+        <v>-2.539191867694141</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.077873990374529</v>
+        <v>2.025416355220324</v>
       </c>
       <c r="F1997" t="n">
         <v>0.5101092184476614</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.032113549108633</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.385326676125477</v>
+        <v>-2.516470764010989</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.077626454344695</v>
+        <v>2.02516881919049</v>
       </c>
       <c r="F1998" t="n">
         <v>0.5101092184476614</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
         <v>3.191019674959802</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.383601632835433</v>
+        <v>-2.514745720720945</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.237222597511881</v>
+        <v>2.184764962357677</v>
       </c>
       <c r="F1999" t="n">
         <v>0.5118342617377052</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.228097497453448</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.538382639613688</v>
+        <v>-2.6695267274992</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.212388017294226</v>
+        <v>2.159930382140021</v>
       </c>
       <c r="F2000" t="n">
         <v>0.4784665876832291</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.224772853442993</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.486947306229028</v>
+        <v>-2.61809139411454</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.229637506637635</v>
+        <v>2.17717987148343</v>
       </c>
       <c r="F2001" t="n">
         <v>0.5299019210678888</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>3.234779007087735</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.45999608190254</v>
+        <v>-2.591140169788052</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.250424150012972</v>
+        <v>2.197966514858767</v>
       </c>
       <c r="F2002" t="n">
         <v>0.544782267095608</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.418882139232695</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.343025051192805</v>
+        <v>-2.458137126796474</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.481315694441826</v>
+        <v>2.435270864200358</v>
       </c>
       <c r="F2003" t="n">
         <v>0.544782267095608</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.410998834135688</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.365433168997677</v>
+        <v>-2.480545244601346</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.46446914222287</v>
+        <v>2.418424311981402</v>
       </c>
       <c r="F2004" t="n">
         <v>0.544782267095608</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155036</v>
       </c>
       <c r="C2005" t="n">
         <v>3.413052833685325</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.513438936477076</v>
+        <v>-2.628551012080745</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.407320834780748</v>
+        <v>2.36127600453928</v>
       </c>
       <c r="F2005" t="n">
         <v>0.4580552582320665</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.469306551407172</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.522879862365606</v>
+        <v>-2.637991937969275</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.459798182147183</v>
+        <v>2.413753351905715</v>
       </c>
       <c r="F2006" t="n">
         <v>0.5804823757754579</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.472197645952473</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.52159309882605</v>
+        <v>-2.636705174429719</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.463203982108306</v>
+        <v>2.417159151866838</v>
       </c>
       <c r="F2007" t="n">
         <v>0.5817691393150145</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
         <v>3.470309458846248</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.523150152815341</v>
+        <v>-2.63826222841901</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.460692973406365</v>
+        <v>2.414648143164897</v>
       </c>
       <c r="F2008" t="n">
         <v>0.5817691393150145</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.465129688449111</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.530422038338806</v>
+        <v>-2.645534113942475</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.452604448799841</v>
+        <v>2.406559618558374</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5744972537915498</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.463563698659263</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.528581019280554</v>
+        <v>-2.643693094884223</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.451774866633294</v>
+        <v>2.405730036391827</v>
       </c>
       <c r="F2010" t="n">
         <v>0.5757654804630182</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647109</v>
       </c>
       <c r="C2011" t="n">
         <v>3.476637105525182</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.535489724780235</v>
+        <v>-2.650601800383904</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.462084791299341</v>
+        <v>2.416039961057873</v>
       </c>
       <c r="F2011" t="n">
         <v>0.5757654804630182</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763535</v>
       </c>
       <c r="C2012" t="n">
         <v>3.476637105525182</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.537051367595095</v>
+        <v>-2.652163443198764</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.461460134173397</v>
+        <v>2.415415303931929</v>
       </c>
       <c r="F2012" t="n">
         <v>0.5757654804630182</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
         <v>3.475161146652184</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.564952154704568</v>
+        <v>-2.680064230308237</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.448823860456609</v>
+        <v>2.402779030215142</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5411685563200834</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.68490993917253</v>
       </c>
       <c r="C2014" t="n">
         <v>3.471925590629382</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.567985152217242</v>
+        <v>-2.683097227820911</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.444375105428739</v>
+        <v>2.398330275187271</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5381355588074095</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971082</v>
       </c>
       <c r="C2015" t="n">
         <v>3.538631550219886</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.588046473493749</v>
+        <v>-2.703158549097417</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.503056536508639</v>
+        <v>2.457011706267172</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5180742375309024</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199809</v>
       </c>
       <c r="C2016" t="n">
         <v>3.678943269221733</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.844767291488572</v>
+        <v>-2.959879367092241</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.540679928312557</v>
+        <v>2.49463509807109</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4096596633870876</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.66830316462224</v>
       </c>
       <c r="C2017" t="n">
         <v>3.747923538367373</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.998753709264713</v>
+        <v>-3.113865784868382</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.54806563034774</v>
+        <v>2.502020800106273</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4096596633870876</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61993717680853</v>
+        <v>3.619937176808534</v>
       </c>
       <c r="C2018" t="n">
         <v>3.733974740487494</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.948231805437047</v>
+        <v>-3.063343881040716</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.554325593998928</v>
+        <v>2.50828076375746</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4096596633870876</v>
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.764135327642467</v>
+        <v>3.764135327642472</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.890183167333197</v>
+        <v>3.745845229542908</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.228501825877023</v>
+        <v>-3.344258257319895</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.598426012668641</v>
+        <v>2.407785502301203</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4096596633870876</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.13597896536545</v>
+        <v>3.99164102757516</v>
       </c>
     </row>
   </sheetData>
